--- a/카드_아키타입/05_로션.xlsx
+++ b/카드_아키타입/05_로션.xlsx
@@ -631,7 +631,7 @@
       <row>53</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="790575"/>
+    <ext cx="1047750" cy="781050"/>
     <pic>
       <nvPicPr>
         <cNvPr id="18" name="Image 18" descr="Picture"/>
@@ -1131,7 +1131,7 @@
       <row>90</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="790575"/>
+    <ext cx="1047750" cy="781050"/>
     <pic>
       <nvPicPr>
         <cNvPr id="38" name="Image 38" descr="Picture"/>
@@ -1506,7 +1506,7 @@
       <row>108</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="971550"/>
+    <ext cx="1047750" cy="962025"/>
     <pic>
       <nvPicPr>
         <cNvPr id="53" name="Image 53" descr="Picture"/>
@@ -5256,7 +5256,7 @@
       <row>333</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="790575"/>
+    <ext cx="1047750" cy="781050"/>
     <pic>
       <nvPicPr>
         <cNvPr id="203" name="Image 203" descr="Picture"/>
@@ -7256,7 +7256,7 @@
       <row>505</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="904875"/>
+    <ext cx="1047750" cy="895350"/>
     <pic>
       <nvPicPr>
         <cNvPr id="283" name="Image 283" descr="Picture"/>
@@ -7306,7 +7306,7 @@
       <row>505</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="323850"/>
+    <ext cx="1047750" cy="333375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="285" name="Image 285" descr="Picture"/>

--- a/카드_아키타입/05_로션.xlsx
+++ b/카드_아키타입/05_로션.xlsx
@@ -199,13 +199,8 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
+  <absoluteAnchor>
+    <pos x="6162675" y="0"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -223,14 +218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="0"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -248,14 +238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="0"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -273,14 +258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="0"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -298,14 +278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="1847850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -323,14 +298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>0</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="1847850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -348,14 +318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>0</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="1847850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -373,14 +338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>0</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="1847850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -398,14 +358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="3695700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -423,14 +378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>0</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="3695700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -448,14 +398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>18</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="10858500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -473,14 +418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>18</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="10858500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -498,14 +438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>18</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="10858500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -523,14 +458,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>18</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="10858500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -548,14 +478,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>18</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="12706350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -573,14 +498,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>18</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="12706350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -598,14 +518,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>18</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="12706350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -623,14 +538,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>36</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="20497800"/>
     <ext cx="1809750" cy="1352550"/>
     <pic>
       <nvPicPr>
@@ -648,14 +558,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>36</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="20497800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -673,14 +578,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>36</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="20497800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -698,14 +598,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>36</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="20497800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -723,14 +618,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>36</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="22345650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -748,14 +638,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>36</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="22345650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -773,14 +658,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>36</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="22345650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -798,14 +678,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>49</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="27114500"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -823,14 +698,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>49</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="27114500"/>
     <ext cx="1390650" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -848,14 +718,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>49</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="27114500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -873,14 +738,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>49</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="27114500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -898,14 +758,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>49</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="28962350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -923,14 +778,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>49</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="28962350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -948,14 +798,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>49</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="28962350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -973,14 +818,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>49</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="28962350"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -998,14 +838,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>49</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="30810200"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1023,14 +858,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>49</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="30810200"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1048,14 +878,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>49</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="30810200"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1073,14 +898,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>49</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="30810200"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1098,14 +918,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>65</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="38989000"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1123,14 +938,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>65</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="38989000"/>
     <ext cx="1809750" cy="1352550"/>
     <pic>
       <nvPicPr>
@@ -1148,14 +958,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>65</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="38989000"/>
     <ext cx="1809750" cy="800100"/>
     <pic>
       <nvPicPr>
@@ -1173,14 +978,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>65</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="38989000"/>
     <ext cx="1809750" cy="600075"/>
     <pic>
       <nvPicPr>
@@ -1198,14 +998,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>65</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="40836850"/>
     <ext cx="1809750" cy="1685925"/>
     <pic>
       <nvPicPr>
@@ -1223,14 +1018,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>65</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="40836850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1248,14 +1038,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>65</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="40836850"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1273,14 +1058,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>65</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="40836850"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1298,14 +1078,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>65</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="42684700"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1323,14 +1098,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>65</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="42684700"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1348,14 +1118,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>65</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="42684700"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1373,14 +1138,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>65</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="42684700"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1398,14 +1158,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>65</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="44532550"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1423,14 +1178,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>65</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="44532550"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1448,14 +1198,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>65</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="44532550"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1473,14 +1218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>82</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="52692300"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1498,14 +1238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>82</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="52692300"/>
     <ext cx="1809750" cy="1666875"/>
     <pic>
       <nvPicPr>
@@ -1523,14 +1258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>82</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="52692300"/>
     <ext cx="1809750" cy="904875"/>
     <pic>
       <nvPicPr>
@@ -1548,14 +1278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>82</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="52692300"/>
     <ext cx="1809750" cy="800100"/>
     <pic>
       <nvPicPr>
@@ -1573,14 +1298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>82</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="54540150"/>
     <ext cx="1809750" cy="600075"/>
     <pic>
       <nvPicPr>
@@ -1598,14 +1318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>82</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="54540150"/>
     <ext cx="1809750" cy="1685925"/>
     <pic>
       <nvPicPr>
@@ -1623,14 +1338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>82</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="54540150"/>
     <ext cx="1809750" cy="1333500"/>
     <pic>
       <nvPicPr>
@@ -1648,14 +1358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>82</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="54540150"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1673,14 +1378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>82</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="56388000"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1698,14 +1398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>82</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="56388000"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1723,14 +1418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>82</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="56388000"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1748,14 +1438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>82</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="56388000"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1773,14 +1458,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>82</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="58235850"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1798,14 +1478,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>82</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="58235850"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1823,14 +1498,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>82</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="58235850"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1848,14 +1518,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>82</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="58235850"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1873,14 +1538,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>99</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="69646800"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1898,14 +1558,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>99</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="69646800"/>
     <ext cx="1809750" cy="1419225"/>
     <pic>
       <nvPicPr>
@@ -1923,14 +1578,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>99</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="69646800"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -1948,14 +1598,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>99</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="69646800"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1973,14 +1618,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>99</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="71494650"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1998,14 +1638,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>99</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="71494650"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2023,14 +1658,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>99</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="71494650"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2048,14 +1678,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>99</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="71494650"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2073,14 +1698,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>99</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="73342500"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2098,14 +1718,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>99</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="73342500"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2123,14 +1738,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>99</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="73342500"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2148,14 +1758,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>116</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="82740500"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2173,14 +1778,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>116</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="82740500"/>
     <ext cx="1809750" cy="1533525"/>
     <pic>
       <nvPicPr>
@@ -2198,14 +1798,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>116</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="82740500"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -2223,14 +1818,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>116</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="82740500"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2248,14 +1838,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>116</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="84588350"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2273,14 +1858,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>116</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="84588350"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2298,14 +1878,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>116</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="84588350"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2323,14 +1898,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>116</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="84588350"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2348,14 +1918,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>116</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="86436200"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2373,14 +1938,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>116</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="86436200"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2398,14 +1958,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>116</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="86436200"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2423,14 +1978,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>116</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="86436200"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2448,14 +1998,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>133</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="94818200"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2473,14 +2018,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>133</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="94818200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2498,14 +2038,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>133</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="94818200"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -2523,14 +2058,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>133</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="94818200"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2548,14 +2078,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>133</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="96666050"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2573,14 +2098,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>133</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="96666050"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2598,14 +2118,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>133</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="96666050"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2623,14 +2138,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>133</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="96666050"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2648,14 +2158,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>133</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="98513900"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2673,14 +2178,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>133</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="98513900"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2698,14 +2198,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>133</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="98513900"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2723,14 +2218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>133</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="98513900"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2748,14 +2238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>133</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="100361750"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2773,14 +2258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>133</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="100361750"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2798,14 +2278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>151</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="110756700"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2823,14 +2298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>151</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="110756700"/>
     <ext cx="1419225" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2848,14 +2318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>151</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="110756700"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -2873,14 +2338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>151</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="110756700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2898,14 +2358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>151</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="112604550"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2923,14 +2378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>151</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="112604550"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2948,14 +2398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>151</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="112604550"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2973,14 +2418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>151</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="112604550"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2998,14 +2438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>151</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="114452400"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3023,14 +2458,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>151</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="114452400"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3048,14 +2478,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>151</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="114452400"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3073,14 +2498,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>151</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="114452400"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3098,14 +2518,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>169</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="124460000"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3123,14 +2538,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>169</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="124460000"/>
     <ext cx="1809750" cy="1657350"/>
     <pic>
       <nvPicPr>
@@ -3148,14 +2558,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>169</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="124460000"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -3173,14 +2578,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>169</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="124460000"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3198,14 +2598,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>169</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="126307850"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3223,14 +2618,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>169</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="126307850"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3248,14 +2638,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>169</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="126307850"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3273,14 +2658,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>169</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="126307850"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3298,14 +2678,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>169</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="128155700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3323,14 +2698,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>169</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="128155700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3348,14 +2718,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>169</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="128155700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3373,14 +2738,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>169</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="128155700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3398,14 +2758,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>186</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="138163300"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3423,14 +2778,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>186</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="138163300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3448,14 +2798,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>186</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="138163300"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3473,14 +2818,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>186</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="138163300"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3498,14 +2838,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>186</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="140011150"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3523,14 +2858,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>186</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="140011150"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3548,14 +2878,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>186</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="140011150"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3573,14 +2898,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>186</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="140011150"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3598,14 +2918,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>186</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="141859000"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3623,14 +2938,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>186</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="141859000"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3648,14 +2958,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>186</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="141859000"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3673,14 +2978,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>201</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="150241000"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3698,14 +2998,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>201</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="150241000"/>
     <ext cx="1809750" cy="1657350"/>
     <pic>
       <nvPicPr>
@@ -3723,14 +3018,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>201</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="150241000"/>
     <ext cx="1809750" cy="857250"/>
     <pic>
       <nvPicPr>
@@ -3748,14 +3038,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>201</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="150241000"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3773,14 +3058,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>201</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="152088850"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3798,14 +3078,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>201</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="152088850"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3823,14 +3098,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>201</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="152088850"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3848,14 +3118,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>201</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="152088850"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3873,14 +3138,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>201</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="153936700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3898,14 +3158,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>201</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="153936700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3923,14 +3178,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>201</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="153936700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3948,14 +3198,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>201</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="153936700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3973,14 +3218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>215</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="158457900"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3998,14 +3238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>215</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="158457900"/>
     <ext cx="1562100" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4023,14 +3258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>215</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="158457900"/>
     <ext cx="1809750" cy="904875"/>
     <pic>
       <nvPicPr>
@@ -4048,14 +3278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>215</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="158457900"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4073,14 +3298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>215</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="160305750"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4098,14 +3318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>215</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="160305750"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4123,14 +3338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>215</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="160305750"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4148,14 +3358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>215</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="160305750"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4173,14 +3378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>215</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="162153600"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4198,14 +3398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>215</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="162153600"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4223,14 +3418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>215</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="162153600"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4248,14 +3438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>215</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="162153600"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4273,14 +3458,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>215</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="164001450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4298,14 +3478,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>215</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="164001450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4323,14 +3498,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>227</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="168097200"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -4348,14 +3518,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>227</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="168097200"/>
     <ext cx="1447800" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4373,14 +3538,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>227</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="168097200"/>
     <ext cx="1809750" cy="866775"/>
     <pic>
       <nvPicPr>
@@ -4398,14 +3558,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>227</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="168097200"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4423,14 +3578,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>227</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="169945050"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4448,14 +3598,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>227</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="169945050"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4473,14 +3618,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>227</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="169945050"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4498,14 +3638,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>227</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="169945050"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4523,14 +3658,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>227</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="171792900"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4548,14 +3678,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>243</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="176314100"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -4573,14 +3698,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>243</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="176314100"/>
     <ext cx="1209675" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4598,14 +3718,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>243</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="176314100"/>
     <ext cx="1809750" cy="1314450"/>
     <pic>
       <nvPicPr>
@@ -4623,14 +3738,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>243</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="176314100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4648,14 +3758,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>243</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="178161950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4673,14 +3778,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>243</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="178161950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4698,14 +3798,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>243</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="178161950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4723,14 +3818,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>243</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="178161950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4748,14 +3838,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>243</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="180009800"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4773,14 +3858,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>258</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="184531000"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -4798,14 +3878,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>258</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="184531000"/>
     <ext cx="1352550" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4823,14 +3898,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>258</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="184531000"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4848,14 +3918,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>258</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="184531000"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4873,14 +3938,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>258</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="186378850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4898,14 +3958,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>258</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="186378850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4923,14 +3978,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>258</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="186378850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4948,14 +3998,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>258</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="186378850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4973,14 +4018,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>258</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="188226700"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4998,14 +4038,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>258</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="188226700"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5023,14 +4058,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>275</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="196811900"/>
     <ext cx="1647825" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5048,14 +4078,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>275</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="196811900"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5073,14 +4098,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>275</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="196811900"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5098,14 +4118,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>275</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="196811900"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5123,14 +4138,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>275</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="198659750"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5148,14 +4158,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>275</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="198659750"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5173,14 +4178,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>275</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="198659750"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5198,14 +4198,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>275</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="198659750"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5223,14 +4218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>275</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="200507600"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5248,14 +4238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>294</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="205841600"/>
     <ext cx="1809750" cy="1352550"/>
     <pic>
       <nvPicPr>
@@ -5273,14 +4258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>294</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="205841600"/>
     <ext cx="1809750" cy="523875"/>
     <pic>
       <nvPicPr>
@@ -5298,14 +4278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>294</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="205841600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5323,14 +4298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>294</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="205841600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5348,14 +4318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>294</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="207689450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5373,14 +4338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>294</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="207689450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5398,14 +4358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>294</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="207689450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5423,14 +4378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>294</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="207689450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5448,14 +4398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>294</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="209537300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5473,14 +4418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>294</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="209537300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5498,14 +4438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>294</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="209537300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5523,14 +4458,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>294</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="209537300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5548,14 +4478,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>294</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="211385150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5573,14 +4498,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>294</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="211385150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5598,14 +4518,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>303</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="216700100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5623,14 +4538,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>303</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="216700100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5648,14 +4558,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>303</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="216700100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5673,14 +4578,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>303</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="216700100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5698,14 +4598,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>303</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="218547950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5723,14 +4618,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>303</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="218547950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5748,14 +4638,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>303</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="218547950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5773,14 +4658,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>303</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="218547950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -5798,14 +4678,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>321</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="226339400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5823,14 +4698,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>321</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="226339400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5848,14 +4718,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>321</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="226339400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5873,14 +4738,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>321</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="226339400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5898,14 +4758,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>321</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="228187250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5923,14 +4778,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>321</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="228187250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5948,14 +4798,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>321</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="228187250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5973,14 +4818,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>338</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="233133900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5998,14 +4838,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>338</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="233133900"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -6023,14 +4858,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>338</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="233133900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6048,14 +4878,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>338</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="233133900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6073,14 +4898,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>338</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="234981750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6098,14 +4918,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>338</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="234981750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6123,14 +4938,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>338</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="234981750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6148,14 +4958,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>338</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="234981750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6173,14 +4978,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>355</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="240741200"/>
     <ext cx="1809750" cy="1457325"/>
     <pic>
       <nvPicPr>
@@ -6198,14 +4998,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>355</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="240741200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6223,14 +5018,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>355</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="240741200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6248,14 +5038,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>355</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="240741200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6273,14 +5058,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>355</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="242589050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6298,14 +5078,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>355</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="242589050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6323,14 +5098,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>355</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="242589050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6348,14 +5118,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>374</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="249567700"/>
     <ext cx="1809750" cy="1800225"/>
     <pic>
       <nvPicPr>
@@ -6373,14 +5138,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>374</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="249567700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6398,14 +5158,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>374</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="249567700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6423,14 +5178,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>374</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="249567700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6448,14 +5198,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>374</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="251415550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6473,14 +5218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>374</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="251415550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6498,14 +5238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>374</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="251415550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6523,14 +5258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>391</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="256590800"/>
     <ext cx="1400175" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6548,14 +5278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>391</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="256590800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6573,14 +5298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>391</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="256590800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6598,14 +5318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>391</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="256590800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6623,14 +5338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>391</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="258438650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6648,14 +5358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>391</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="258438650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6673,14 +5378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>391</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="258438650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6698,14 +5398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>406</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="263994900"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -6723,14 +5418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>406</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="263994900"/>
     <ext cx="1809750" cy="1533525"/>
     <pic>
       <nvPicPr>
@@ -6748,14 +5438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>406</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="263994900"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -6773,14 +5458,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>406</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="263994900"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6798,14 +5478,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>406</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="265842750"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6823,14 +5498,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>406</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="265842750"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6848,14 +5518,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>406</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="265842750"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6873,14 +5538,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>406</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="265842750"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6898,14 +5558,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>406</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="267690600"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6923,14 +5578,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>406</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="267690600"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6948,14 +5598,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>406</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="267690600"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6973,14 +5618,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>406</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="267690600"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6998,14 +5638,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>423</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="276275800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7023,14 +5658,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>423</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="276275800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7048,14 +5678,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>423</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="276275800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7073,14 +5698,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>423</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="276275800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7098,14 +5718,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>423</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="278123650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7123,14 +5738,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>423</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="278123650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7148,14 +5758,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>423</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="278123650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7173,14 +5778,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>423</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="278123650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7198,14 +5798,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>423</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="279971500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7223,14 +5818,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>423</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="279971500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7248,14 +5838,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>440</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="287337500"/>
     <ext cx="1809750" cy="1552575"/>
     <pic>
       <nvPicPr>
@@ -7273,14 +5858,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>440</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="287337500"/>
     <ext cx="1809750" cy="1171575"/>
     <pic>
       <nvPicPr>
@@ -7298,14 +5878,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>440</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="287337500"/>
     <ext cx="1809750" cy="561975"/>
     <pic>
       <nvPicPr>
@@ -7323,14 +5898,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>458</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="302260000"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -7348,14 +5918,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>458</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="302260000"/>
     <ext cx="1476375" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7373,14 +5938,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>458</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="302260000"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -7398,14 +5958,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>458</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="302260000"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7423,14 +5978,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>458</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="304107850"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7448,14 +5998,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>458</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="304107850"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7473,14 +6018,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>458</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="304107850"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7498,14 +6038,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>458</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="304107850"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7523,14 +6058,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>458</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="305955700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7548,14 +6078,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>458</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="305955700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7573,14 +6098,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>458</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="305955700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7598,14 +6118,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>458</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="305955700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7623,14 +6138,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>476</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="318401700"/>
     <ext cx="1809750" cy="1419225"/>
     <pic>
       <nvPicPr>
@@ -7648,14 +6158,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>476</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="318401700"/>
     <ext cx="1428750" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -7673,14 +6178,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>476</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="318401700"/>
     <ext cx="1428750" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -7698,14 +6198,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>476</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="318401700"/>
     <ext cx="1428750" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -7723,14 +6218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>476</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="320249550"/>
     <ext cx="1428750" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -7748,14 +6238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>476</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="320249550"/>
     <ext cx="1809750" cy="1619250"/>
     <pic>
       <nvPicPr>
@@ -7773,14 +6258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>476</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="320249550"/>
     <ext cx="1428750" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -7798,14 +6278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>476</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="320249550"/>
     <ext cx="1428750" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -7823,14 +6298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>492</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="328447400"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -7848,14 +6318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>492</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="328447400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7873,14 +6338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>492</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="328447400"/>
     <ext cx="1714500" cy="1533525"/>
     <pic>
       <nvPicPr>
@@ -7898,14 +6358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>492</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="328447400"/>
     <ext cx="1714500" cy="1533525"/>
     <pic>
       <nvPicPr>
@@ -7923,14 +6378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>492</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="330295250"/>
     <ext cx="1714500" cy="1533525"/>
     <pic>
       <nvPicPr>
@@ -7948,14 +6398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>492</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="330295250"/>
     <ext cx="1714500" cy="1533525"/>
     <pic>
       <nvPicPr>
@@ -7973,14 +6418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>492</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="330295250"/>
     <ext cx="1714500" cy="1533525"/>
     <pic>
       <nvPicPr>
@@ -7998,14 +6438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>492</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="330295250"/>
     <ext cx="1714500" cy="1533525"/>
     <pic>
       <nvPicPr>
@@ -8023,14 +6458,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>507</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="336257900"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -8048,14 +6478,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>507</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="336257900"/>
     <ext cx="1809750" cy="1628775"/>
     <pic>
       <nvPicPr>
@@ -8073,14 +6498,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>507</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="336257900"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -8098,14 +6518,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>507</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="336257900"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -8123,14 +6538,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>507</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="338105750"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -8148,14 +6558,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>507</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="338105750"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -8173,14 +6578,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>507</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="338105750"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -8198,14 +6598,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>507</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="338105750"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -8223,14 +6618,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>523</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="343458800"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -8248,14 +6638,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>523</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="343458800"/>
     <ext cx="1809750" cy="1371600"/>
     <pic>
       <nvPicPr>
@@ -8273,14 +6658,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>523</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="343458800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -8298,14 +6678,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>523</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="343458800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -8323,14 +6698,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>523</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="345306650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -8348,14 +6718,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>523</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="345306650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -8373,14 +6738,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>523</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="345306650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -8398,14 +6758,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>523</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="345306650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -8423,14 +6778,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>540</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="355942900"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -8448,14 +6798,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>540</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="355942900"/>
     <ext cx="1809750" cy="1504950"/>
     <pic>
       <nvPicPr>
@@ -8473,14 +6818,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>540</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="355942900"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -8498,14 +6838,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>540</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="355942900"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -8523,14 +6858,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>540</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="357790750"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -8548,14 +6878,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>540</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="357790750"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -8573,14 +6898,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>540</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="357790750"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -8598,14 +6918,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>540</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="357790750"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -8623,14 +6938,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>556</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="365988600"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -8648,14 +6958,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>556</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="365988600"/>
     <ext cx="1809750" cy="1552575"/>
     <pic>
       <nvPicPr>
@@ -8673,14 +6978,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>556</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="365988600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -8698,14 +6998,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>556</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="365988600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -8723,14 +7018,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>556</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="367836450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -8748,14 +7038,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>556</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="367836450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -8773,14 +7058,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>556</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="367836450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -8798,14 +7078,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>556</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="367836450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -8823,14 +7098,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>572</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="378269500"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -8848,14 +7118,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>572</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="378269500"/>
     <ext cx="1809750" cy="1552575"/>
     <pic>
       <nvPicPr>
@@ -8873,14 +7138,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>572</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="378269500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -8898,14 +7158,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>572</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="378269500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -8923,14 +7178,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>572</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="380117350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -8948,14 +7198,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>572</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="380117350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -8973,14 +7218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>572</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="380117350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -8998,14 +7238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>572</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="380117350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -9023,14 +7258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>588</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="394004800"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -9048,14 +7278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>588</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="394004800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9073,14 +7298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>588</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="394004800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -9098,14 +7318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>588</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="394004800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -9123,14 +7338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>588</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="395852650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -9148,14 +7358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>588</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="395852650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -9173,14 +7378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>588</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="395852650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -9198,14 +7398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>588</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="395852650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -9223,14 +7418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>603</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="404050500"/>
     <ext cx="1123950" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9248,14 +7438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>622</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="415721800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9273,14 +7458,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>622</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="415721800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9298,14 +7478,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>622</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="415721800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9323,14 +7498,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>622</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="415721800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9348,14 +7518,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>622</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="417569650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9373,14 +7538,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>622</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="417569650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9398,14 +7558,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>622</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="417569650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9423,14 +7578,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>639</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="425361100"/>
     <ext cx="1809750" cy="1228725"/>
     <pic>
       <nvPicPr>
@@ -9448,14 +7598,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>639</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="425361100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9473,14 +7618,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>639</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="425361100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9498,14 +7638,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>639</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="425361100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9523,14 +7658,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>639</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="427208950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9548,14 +7678,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>639</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="427208950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9573,14 +7698,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>639</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="427208950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9598,14 +7718,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>652</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="430961800"/>
     <ext cx="1190625" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9623,14 +7738,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>665</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="438594500"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -9648,14 +7758,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>665</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="438594500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9673,14 +7778,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>665</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="438594500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9698,14 +7798,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>665</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="438594500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -9723,14 +7818,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>665</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="440442350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -9748,14 +7838,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>665</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="440442350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -9773,14 +7858,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>665</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="440442350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -9798,14 +7878,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>665</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="440442350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -9823,14 +7898,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>665</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="442290200"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -9848,14 +7918,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>665</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="442290200"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -9873,14 +7938,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>665</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="442290200"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -9898,14 +7958,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>665</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="442290200"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -9923,14 +7978,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>684</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="454736200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9948,14 +7998,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>684</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="454736200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9973,14 +8018,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>684</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="454736200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9998,14 +8038,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>684</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="454736200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10023,14 +8058,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>684</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="456584050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10048,14 +8078,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>684</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="456584050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10073,14 +8098,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>684</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="456584050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10098,14 +8118,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>684</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="456584050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10123,14 +8138,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>684</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="458431900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10148,14 +8158,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>684</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="458431900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10173,14 +8178,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>700</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="465391500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10198,14 +8198,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>700</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="465391500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10223,14 +8218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>700</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="465391500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10248,14 +8238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>700</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="465391500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10273,14 +8258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>700</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="467239350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10298,14 +8278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>700</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="467239350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10323,14 +8298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>700</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="467239350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10348,14 +8318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>718</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="477672400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10373,14 +8338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>718</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="477672400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10398,14 +8358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>718</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="477672400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10423,14 +8378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>718</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="477672400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10448,14 +8398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>718</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="479520250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10473,14 +8418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>718</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="479520250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10498,14 +8438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>718</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="479520250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -10523,7 +8458,7 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
+  </absoluteAnchor>
 </wsDr>
 </file>
 

--- a/카드_아키타입/05_로션.xlsx
+++ b/카드_아키타입/05_로션.xlsx
@@ -200,7 +200,7 @@
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <absoluteAnchor>
-    <pos x="6162675" y="0"/>
+    <pos x="7391400" y="0"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -220,7 +220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="0"/>
+    <pos x="9239250" y="0"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -240,7 +240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="0"/>
+    <pos x="11087100" y="0"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -260,7 +260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="0"/>
+    <pos x="12934950" y="0"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -280,7 +280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="1847850"/>
+    <pos x="7391400" y="1847850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -300,7 +300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="1847850"/>
+    <pos x="9239250" y="1847850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -320,7 +320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="1847850"/>
+    <pos x="11087100" y="1847850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -340,7 +340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="1847850"/>
+    <pos x="12934950" y="1847850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -360,7 +360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="3695700"/>
+    <pos x="7391400" y="3695700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -380,7 +380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="3695700"/>
+    <pos x="9239250" y="3695700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -400,7 +400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="10858500"/>
+    <pos x="7391400" y="10858500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -420,7 +420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="10858500"/>
+    <pos x="9239250" y="10858500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -440,7 +440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="10858500"/>
+    <pos x="11087100" y="10858500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -460,7 +460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="10858500"/>
+    <pos x="12934950" y="10858500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -480,7 +480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="12706350"/>
+    <pos x="7391400" y="12706350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -500,7 +500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="12706350"/>
+    <pos x="9239250" y="12706350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -520,7 +520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="12706350"/>
+    <pos x="11087100" y="12706350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -540,7 +540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="20497800"/>
+    <pos x="7391400" y="20497800"/>
     <ext cx="1809750" cy="1352550"/>
     <pic>
       <nvPicPr>
@@ -560,7 +560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="20497800"/>
+    <pos x="9239250" y="20497800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -580,7 +580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="20497800"/>
+    <pos x="11087100" y="20497800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -600,7 +600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="20497800"/>
+    <pos x="12934950" y="20497800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -620,7 +620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="22345650"/>
+    <pos x="7391400" y="22345650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -640,7 +640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="22345650"/>
+    <pos x="9239250" y="22345650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -660,7 +660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="22345650"/>
+    <pos x="11087100" y="22345650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -680,7 +680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="27114500"/>
+    <pos x="7391400" y="27114500"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -700,7 +700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="27114500"/>
+    <pos x="9239250" y="27114500"/>
     <ext cx="1390650" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -720,7 +720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="27114500"/>
+    <pos x="11087100" y="27114500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -740,7 +740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="27114500"/>
+    <pos x="12934950" y="27114500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -760,7 +760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="28962350"/>
+    <pos x="7391400" y="28962350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -780,7 +780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="28962350"/>
+    <pos x="9239250" y="28962350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -800,7 +800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="28962350"/>
+    <pos x="11087100" y="28962350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -820,7 +820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="28962350"/>
+    <pos x="12934950" y="28962350"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -840,7 +840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="30810200"/>
+    <pos x="7391400" y="30810200"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -860,7 +860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="30810200"/>
+    <pos x="9239250" y="30810200"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -880,7 +880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="30810200"/>
+    <pos x="11087100" y="30810200"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -900,7 +900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="30810200"/>
+    <pos x="12934950" y="30810200"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -920,7 +920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="38989000"/>
+    <pos x="7391400" y="38989000"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -940,7 +940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="38989000"/>
+    <pos x="9239250" y="38989000"/>
     <ext cx="1809750" cy="1352550"/>
     <pic>
       <nvPicPr>
@@ -960,7 +960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="38989000"/>
+    <pos x="11087100" y="38989000"/>
     <ext cx="1809750" cy="800100"/>
     <pic>
       <nvPicPr>
@@ -980,7 +980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="38989000"/>
+    <pos x="12934950" y="38989000"/>
     <ext cx="1809750" cy="600075"/>
     <pic>
       <nvPicPr>
@@ -1000,7 +1000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="40836850"/>
+    <pos x="7391400" y="40836850"/>
     <ext cx="1809750" cy="1685925"/>
     <pic>
       <nvPicPr>
@@ -1020,7 +1020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="40836850"/>
+    <pos x="9239250" y="40836850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1040,7 +1040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="40836850"/>
+    <pos x="11087100" y="40836850"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1060,7 +1060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="40836850"/>
+    <pos x="12934950" y="40836850"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1080,7 +1080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="42684700"/>
+    <pos x="7391400" y="42684700"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1100,7 +1100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="42684700"/>
+    <pos x="9239250" y="42684700"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1120,7 +1120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="42684700"/>
+    <pos x="11087100" y="42684700"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1140,7 +1140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="42684700"/>
+    <pos x="12934950" y="42684700"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1160,7 +1160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="44532550"/>
+    <pos x="7391400" y="44532550"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1180,7 +1180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="44532550"/>
+    <pos x="9239250" y="44532550"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1200,7 +1200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="44532550"/>
+    <pos x="11087100" y="44532550"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1220,7 +1220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="52692300"/>
+    <pos x="7391400" y="52692300"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1240,7 +1240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="52692300"/>
+    <pos x="9239250" y="52692300"/>
     <ext cx="1809750" cy="1666875"/>
     <pic>
       <nvPicPr>
@@ -1260,7 +1260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="52692300"/>
+    <pos x="11087100" y="52692300"/>
     <ext cx="1809750" cy="904875"/>
     <pic>
       <nvPicPr>
@@ -1280,7 +1280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="52692300"/>
+    <pos x="12934950" y="52692300"/>
     <ext cx="1809750" cy="800100"/>
     <pic>
       <nvPicPr>
@@ -1300,7 +1300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="54540150"/>
+    <pos x="7391400" y="54540150"/>
     <ext cx="1809750" cy="600075"/>
     <pic>
       <nvPicPr>
@@ -1320,7 +1320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="54540150"/>
+    <pos x="9239250" y="54540150"/>
     <ext cx="1809750" cy="1685925"/>
     <pic>
       <nvPicPr>
@@ -1340,7 +1340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="54540150"/>
+    <pos x="11087100" y="54540150"/>
     <ext cx="1809750" cy="1333500"/>
     <pic>
       <nvPicPr>
@@ -1360,7 +1360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="54540150"/>
+    <pos x="12934950" y="54540150"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1380,7 +1380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="56388000"/>
+    <pos x="7391400" y="56388000"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1400,7 +1400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="56388000"/>
+    <pos x="9239250" y="56388000"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1420,7 +1420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="56388000"/>
+    <pos x="11087100" y="56388000"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1440,7 +1440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="56388000"/>
+    <pos x="12934950" y="56388000"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1460,7 +1460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="58235850"/>
+    <pos x="7391400" y="58235850"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1480,7 +1480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="58235850"/>
+    <pos x="9239250" y="58235850"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1500,7 +1500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="58235850"/>
+    <pos x="11087100" y="58235850"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1520,7 +1520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="58235850"/>
+    <pos x="12934950" y="58235850"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1540,7 +1540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="69646800"/>
+    <pos x="7391400" y="69646800"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1560,7 +1560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="69646800"/>
+    <pos x="9239250" y="69646800"/>
     <ext cx="1809750" cy="1419225"/>
     <pic>
       <nvPicPr>
@@ -1580,7 +1580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="69646800"/>
+    <pos x="11087100" y="69646800"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -1600,7 +1600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="69646800"/>
+    <pos x="12934950" y="69646800"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1620,7 +1620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="71494650"/>
+    <pos x="7391400" y="71494650"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1640,7 +1640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="71494650"/>
+    <pos x="9239250" y="71494650"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1660,7 +1660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="71494650"/>
+    <pos x="11087100" y="71494650"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1680,7 +1680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="71494650"/>
+    <pos x="12934950" y="71494650"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1700,7 +1700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="73342500"/>
+    <pos x="7391400" y="73342500"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1720,7 +1720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="73342500"/>
+    <pos x="9239250" y="73342500"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1740,7 +1740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="73342500"/>
+    <pos x="11087100" y="73342500"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1760,7 +1760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="82740500"/>
+    <pos x="7391400" y="82740500"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1780,7 +1780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="82740500"/>
+    <pos x="9239250" y="82740500"/>
     <ext cx="1809750" cy="1533525"/>
     <pic>
       <nvPicPr>
@@ -1800,7 +1800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="82740500"/>
+    <pos x="11087100" y="82740500"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -1820,7 +1820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="82740500"/>
+    <pos x="12934950" y="82740500"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1840,7 +1840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="84588350"/>
+    <pos x="7391400" y="84588350"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1860,7 +1860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="84588350"/>
+    <pos x="9239250" y="84588350"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1880,7 +1880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="84588350"/>
+    <pos x="11087100" y="84588350"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1900,7 +1900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="84588350"/>
+    <pos x="12934950" y="84588350"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1920,7 +1920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="86436200"/>
+    <pos x="7391400" y="86436200"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1940,7 +1940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="86436200"/>
+    <pos x="9239250" y="86436200"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1960,7 +1960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="86436200"/>
+    <pos x="11087100" y="86436200"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1980,7 +1980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="86436200"/>
+    <pos x="12934950" y="86436200"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2000,7 +2000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="94818200"/>
+    <pos x="7391400" y="94818200"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2020,7 +2020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="94818200"/>
+    <pos x="9239250" y="94818200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2040,7 +2040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="94818200"/>
+    <pos x="11087100" y="94818200"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -2060,7 +2060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="94818200"/>
+    <pos x="12934950" y="94818200"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2080,7 +2080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="96666050"/>
+    <pos x="7391400" y="96666050"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2100,7 +2100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="96666050"/>
+    <pos x="9239250" y="96666050"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2120,7 +2120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="96666050"/>
+    <pos x="11087100" y="96666050"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2140,7 +2140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="96666050"/>
+    <pos x="12934950" y="96666050"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2160,7 +2160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="98513900"/>
+    <pos x="7391400" y="98513900"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2180,7 +2180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="98513900"/>
+    <pos x="9239250" y="98513900"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2200,7 +2200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="98513900"/>
+    <pos x="11087100" y="98513900"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2220,7 +2220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="98513900"/>
+    <pos x="12934950" y="98513900"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2240,7 +2240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="100361750"/>
+    <pos x="7391400" y="100361750"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2260,7 +2260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="100361750"/>
+    <pos x="9239250" y="100361750"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2280,7 +2280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="110756700"/>
+    <pos x="7391400" y="110756700"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2300,7 +2300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="110756700"/>
+    <pos x="9239250" y="110756700"/>
     <ext cx="1419225" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2320,7 +2320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="110756700"/>
+    <pos x="11087100" y="110756700"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -2340,7 +2340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="110756700"/>
+    <pos x="12934950" y="110756700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2360,7 +2360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="112604550"/>
+    <pos x="7391400" y="112604550"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2380,7 +2380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="112604550"/>
+    <pos x="9239250" y="112604550"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2400,7 +2400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="112604550"/>
+    <pos x="11087100" y="112604550"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2420,7 +2420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="112604550"/>
+    <pos x="12934950" y="112604550"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2440,7 +2440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="114452400"/>
+    <pos x="7391400" y="114452400"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2460,7 +2460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="114452400"/>
+    <pos x="9239250" y="114452400"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2480,7 +2480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="114452400"/>
+    <pos x="11087100" y="114452400"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2500,7 +2500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="114452400"/>
+    <pos x="12934950" y="114452400"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2520,7 +2520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="124460000"/>
+    <pos x="7391400" y="124460000"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2540,7 +2540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="124460000"/>
+    <pos x="9239250" y="124460000"/>
     <ext cx="1809750" cy="1657350"/>
     <pic>
       <nvPicPr>
@@ -2560,7 +2560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="124460000"/>
+    <pos x="11087100" y="124460000"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -2580,7 +2580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="124460000"/>
+    <pos x="12934950" y="124460000"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2600,7 +2600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="126307850"/>
+    <pos x="7391400" y="126307850"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2620,7 +2620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="126307850"/>
+    <pos x="9239250" y="126307850"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2640,7 +2640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="126307850"/>
+    <pos x="11087100" y="126307850"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2660,7 +2660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="126307850"/>
+    <pos x="12934950" y="126307850"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2680,7 +2680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="128155700"/>
+    <pos x="7391400" y="128155700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2700,7 +2700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="128155700"/>
+    <pos x="9239250" y="128155700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2720,7 +2720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="128155700"/>
+    <pos x="11087100" y="128155700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2740,7 +2740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="128155700"/>
+    <pos x="12934950" y="128155700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2760,7 +2760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="138163300"/>
+    <pos x="7391400" y="138163300"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2780,7 +2780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="138163300"/>
+    <pos x="9239250" y="138163300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2800,7 +2800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="138163300"/>
+    <pos x="11087100" y="138163300"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2820,7 +2820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="138163300"/>
+    <pos x="12934950" y="138163300"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2840,7 +2840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="140011150"/>
+    <pos x="7391400" y="140011150"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2860,7 +2860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="140011150"/>
+    <pos x="9239250" y="140011150"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2880,7 +2880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="140011150"/>
+    <pos x="11087100" y="140011150"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2900,7 +2900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="140011150"/>
+    <pos x="12934950" y="140011150"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2920,7 +2920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="141859000"/>
+    <pos x="7391400" y="141859000"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2940,7 +2940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="141859000"/>
+    <pos x="9239250" y="141859000"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2960,7 +2960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="141859000"/>
+    <pos x="11087100" y="141859000"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2980,7 +2980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="150241000"/>
+    <pos x="7391400" y="150241000"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3000,7 +3000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="150241000"/>
+    <pos x="9239250" y="150241000"/>
     <ext cx="1809750" cy="1657350"/>
     <pic>
       <nvPicPr>
@@ -3020,7 +3020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="150241000"/>
+    <pos x="11087100" y="150241000"/>
     <ext cx="1809750" cy="857250"/>
     <pic>
       <nvPicPr>
@@ -3040,7 +3040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="150241000"/>
+    <pos x="12934950" y="150241000"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3060,7 +3060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="152088850"/>
+    <pos x="7391400" y="152088850"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3080,7 +3080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="152088850"/>
+    <pos x="9239250" y="152088850"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3100,7 +3100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="152088850"/>
+    <pos x="11087100" y="152088850"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3120,7 +3120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="152088850"/>
+    <pos x="12934950" y="152088850"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3140,7 +3140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="153936700"/>
+    <pos x="7391400" y="153936700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3160,7 +3160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="153936700"/>
+    <pos x="9239250" y="153936700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3180,7 +3180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="153936700"/>
+    <pos x="11087100" y="153936700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3200,7 +3200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="153936700"/>
+    <pos x="12934950" y="153936700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3220,7 +3220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="158457900"/>
+    <pos x="7391400" y="158457900"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3240,7 +3240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="158457900"/>
+    <pos x="9239250" y="158457900"/>
     <ext cx="1562100" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3260,7 +3260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="158457900"/>
+    <pos x="11087100" y="158457900"/>
     <ext cx="1809750" cy="904875"/>
     <pic>
       <nvPicPr>
@@ -3280,7 +3280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="158457900"/>
+    <pos x="12934950" y="158457900"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3300,7 +3300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="160305750"/>
+    <pos x="7391400" y="160305750"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3320,7 +3320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="160305750"/>
+    <pos x="9239250" y="160305750"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3340,7 +3340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="160305750"/>
+    <pos x="11087100" y="160305750"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3360,7 +3360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="160305750"/>
+    <pos x="12934950" y="160305750"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3380,7 +3380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="162153600"/>
+    <pos x="7391400" y="162153600"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3400,7 +3400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="162153600"/>
+    <pos x="9239250" y="162153600"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3420,7 +3420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="162153600"/>
+    <pos x="11087100" y="162153600"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3440,7 +3440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="162153600"/>
+    <pos x="12934950" y="162153600"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3460,7 +3460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="164001450"/>
+    <pos x="7391400" y="164001450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3480,7 +3480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="164001450"/>
+    <pos x="9239250" y="164001450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3500,7 +3500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="168097200"/>
+    <pos x="7391400" y="168097200"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3520,7 +3520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="168097200"/>
+    <pos x="9239250" y="168097200"/>
     <ext cx="1447800" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3540,7 +3540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="168097200"/>
+    <pos x="11087100" y="168097200"/>
     <ext cx="1809750" cy="866775"/>
     <pic>
       <nvPicPr>
@@ -3560,7 +3560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="168097200"/>
+    <pos x="12934950" y="168097200"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3580,7 +3580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="169945050"/>
+    <pos x="7391400" y="169945050"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3600,7 +3600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="169945050"/>
+    <pos x="9239250" y="169945050"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3620,7 +3620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="169945050"/>
+    <pos x="11087100" y="169945050"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3640,7 +3640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="169945050"/>
+    <pos x="12934950" y="169945050"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3660,7 +3660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="171792900"/>
+    <pos x="7391400" y="171792900"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3680,7 +3680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="176314100"/>
+    <pos x="7391400" y="176314100"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3700,7 +3700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="176314100"/>
+    <pos x="9239250" y="176314100"/>
     <ext cx="1209675" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3720,7 +3720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="176314100"/>
+    <pos x="11087100" y="176314100"/>
     <ext cx="1809750" cy="1314450"/>
     <pic>
       <nvPicPr>
@@ -3740,7 +3740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="176314100"/>
+    <pos x="12934950" y="176314100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3760,7 +3760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="178161950"/>
+    <pos x="7391400" y="178161950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3780,7 +3780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="178161950"/>
+    <pos x="9239250" y="178161950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3800,7 +3800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="178161950"/>
+    <pos x="11087100" y="178161950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3820,7 +3820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="178161950"/>
+    <pos x="12934950" y="178161950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3840,7 +3840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="180009800"/>
+    <pos x="7391400" y="180009800"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3860,7 +3860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="184531000"/>
+    <pos x="7391400" y="184531000"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3880,7 +3880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="184531000"/>
+    <pos x="9239250" y="184531000"/>
     <ext cx="1352550" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3900,7 +3900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="184531000"/>
+    <pos x="11087100" y="184531000"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3920,7 +3920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="184531000"/>
+    <pos x="12934950" y="184531000"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3940,7 +3940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="186378850"/>
+    <pos x="7391400" y="186378850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3960,7 +3960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="186378850"/>
+    <pos x="9239250" y="186378850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3980,7 +3980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="186378850"/>
+    <pos x="11087100" y="186378850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4000,7 +4000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="186378850"/>
+    <pos x="12934950" y="186378850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4020,7 +4020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="188226700"/>
+    <pos x="7391400" y="188226700"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4040,7 +4040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="188226700"/>
+    <pos x="9239250" y="188226700"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4060,7 +4060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="196811900"/>
+    <pos x="7391400" y="196811900"/>
     <ext cx="1647825" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4080,7 +4080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="196811900"/>
+    <pos x="9239250" y="196811900"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4100,7 +4100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="196811900"/>
+    <pos x="11087100" y="196811900"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4120,7 +4120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="196811900"/>
+    <pos x="12934950" y="196811900"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4140,7 +4140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="198659750"/>
+    <pos x="7391400" y="198659750"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4160,7 +4160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="198659750"/>
+    <pos x="9239250" y="198659750"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4180,7 +4180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="198659750"/>
+    <pos x="11087100" y="198659750"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4200,7 +4200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="198659750"/>
+    <pos x="12934950" y="198659750"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4220,7 +4220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="200507600"/>
+    <pos x="7391400" y="200507600"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4240,7 +4240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="205841600"/>
+    <pos x="7391400" y="205841600"/>
     <ext cx="1809750" cy="1352550"/>
     <pic>
       <nvPicPr>
@@ -4260,7 +4260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="205841600"/>
+    <pos x="9239250" y="205841600"/>
     <ext cx="1809750" cy="523875"/>
     <pic>
       <nvPicPr>
@@ -4280,7 +4280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="205841600"/>
+    <pos x="11087100" y="205841600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4300,7 +4300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="205841600"/>
+    <pos x="12934950" y="205841600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4320,7 +4320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="207689450"/>
+    <pos x="7391400" y="207689450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4340,7 +4340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="207689450"/>
+    <pos x="9239250" y="207689450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4360,7 +4360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="207689450"/>
+    <pos x="11087100" y="207689450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4380,7 +4380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="207689450"/>
+    <pos x="12934950" y="207689450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4400,7 +4400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="209537300"/>
+    <pos x="7391400" y="209537300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4420,7 +4420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="209537300"/>
+    <pos x="9239250" y="209537300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4440,7 +4440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="209537300"/>
+    <pos x="11087100" y="209537300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4460,7 +4460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="209537300"/>
+    <pos x="12934950" y="209537300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4480,7 +4480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="211385150"/>
+    <pos x="7391400" y="211385150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4500,7 +4500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="211385150"/>
+    <pos x="9239250" y="211385150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4520,7 +4520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="216700100"/>
+    <pos x="7391400" y="216700100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4540,7 +4540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="216700100"/>
+    <pos x="9239250" y="216700100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4560,7 +4560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="216700100"/>
+    <pos x="11087100" y="216700100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4580,7 +4580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="216700100"/>
+    <pos x="12934950" y="216700100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4600,7 +4600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="218547950"/>
+    <pos x="7391400" y="218547950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4620,7 +4620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="218547950"/>
+    <pos x="9239250" y="218547950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4640,7 +4640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="218547950"/>
+    <pos x="11087100" y="218547950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4660,7 +4660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="218547950"/>
+    <pos x="12934950" y="218547950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -4680,7 +4680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="226339400"/>
+    <pos x="7391400" y="226339400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4700,7 +4700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="226339400"/>
+    <pos x="9239250" y="226339400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4720,7 +4720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="226339400"/>
+    <pos x="11087100" y="226339400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4740,7 +4740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="226339400"/>
+    <pos x="12934950" y="226339400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4760,7 +4760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="228187250"/>
+    <pos x="7391400" y="228187250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4780,7 +4780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="228187250"/>
+    <pos x="9239250" y="228187250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4800,7 +4800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="228187250"/>
+    <pos x="11087100" y="228187250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4820,7 +4820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="233133900"/>
+    <pos x="7391400" y="233133900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4840,7 +4840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="233133900"/>
+    <pos x="9239250" y="233133900"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -4860,7 +4860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="233133900"/>
+    <pos x="11087100" y="233133900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4880,7 +4880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="233133900"/>
+    <pos x="12934950" y="233133900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4900,7 +4900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="234981750"/>
+    <pos x="7391400" y="234981750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4920,7 +4920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="234981750"/>
+    <pos x="9239250" y="234981750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4940,7 +4940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="234981750"/>
+    <pos x="11087100" y="234981750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4960,7 +4960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="234981750"/>
+    <pos x="12934950" y="234981750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4980,7 +4980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="240741200"/>
+    <pos x="7391400" y="240741200"/>
     <ext cx="1809750" cy="1457325"/>
     <pic>
       <nvPicPr>
@@ -5000,7 +5000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="240741200"/>
+    <pos x="9239250" y="240741200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5020,7 +5020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="240741200"/>
+    <pos x="11087100" y="240741200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5040,7 +5040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="240741200"/>
+    <pos x="12934950" y="240741200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5060,7 +5060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="242589050"/>
+    <pos x="7391400" y="242589050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5080,7 +5080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="242589050"/>
+    <pos x="9239250" y="242589050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5100,7 +5100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="242589050"/>
+    <pos x="11087100" y="242589050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5120,7 +5120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="249567700"/>
+    <pos x="7391400" y="249567700"/>
     <ext cx="1809750" cy="1800225"/>
     <pic>
       <nvPicPr>
@@ -5140,7 +5140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="249567700"/>
+    <pos x="9239250" y="249567700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5160,7 +5160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="249567700"/>
+    <pos x="11087100" y="249567700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5180,7 +5180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="249567700"/>
+    <pos x="12934950" y="249567700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5200,7 +5200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="251415550"/>
+    <pos x="7391400" y="251415550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5220,7 +5220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="251415550"/>
+    <pos x="9239250" y="251415550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5240,7 +5240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="251415550"/>
+    <pos x="11087100" y="251415550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5260,7 +5260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="256590800"/>
+    <pos x="7391400" y="256590800"/>
     <ext cx="1400175" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5280,7 +5280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="256590800"/>
+    <pos x="9239250" y="256590800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5300,7 +5300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="256590800"/>
+    <pos x="11087100" y="256590800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5320,7 +5320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="256590800"/>
+    <pos x="12934950" y="256590800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5340,7 +5340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="258438650"/>
+    <pos x="7391400" y="258438650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5360,7 +5360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="258438650"/>
+    <pos x="9239250" y="258438650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5380,7 +5380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="258438650"/>
+    <pos x="11087100" y="258438650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5400,7 +5400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="263994900"/>
+    <pos x="7391400" y="263994900"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -5420,7 +5420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="263994900"/>
+    <pos x="9239250" y="263994900"/>
     <ext cx="1809750" cy="1533525"/>
     <pic>
       <nvPicPr>
@@ -5440,7 +5440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="263994900"/>
+    <pos x="11087100" y="263994900"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -5460,7 +5460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="263994900"/>
+    <pos x="12934950" y="263994900"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5480,7 +5480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="265842750"/>
+    <pos x="7391400" y="265842750"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5500,7 +5500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="265842750"/>
+    <pos x="9239250" y="265842750"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5520,7 +5520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="265842750"/>
+    <pos x="11087100" y="265842750"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5540,7 +5540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="265842750"/>
+    <pos x="12934950" y="265842750"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5560,7 +5560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="267690600"/>
+    <pos x="7391400" y="267690600"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5580,7 +5580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="267690600"/>
+    <pos x="9239250" y="267690600"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5600,7 +5600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="267690600"/>
+    <pos x="11087100" y="267690600"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5620,7 +5620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="267690600"/>
+    <pos x="12934950" y="267690600"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5640,7 +5640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="276275800"/>
+    <pos x="7391400" y="276275800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5660,7 +5660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="276275800"/>
+    <pos x="9239250" y="276275800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5680,7 +5680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="276275800"/>
+    <pos x="11087100" y="276275800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5700,7 +5700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="276275800"/>
+    <pos x="12934950" y="276275800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5720,7 +5720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="278123650"/>
+    <pos x="7391400" y="278123650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5740,7 +5740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="278123650"/>
+    <pos x="9239250" y="278123650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5760,7 +5760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="278123650"/>
+    <pos x="11087100" y="278123650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5780,7 +5780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="278123650"/>
+    <pos x="12934950" y="278123650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5800,7 +5800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="279971500"/>
+    <pos x="7391400" y="279971500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5820,7 +5820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="279971500"/>
+    <pos x="9239250" y="279971500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5840,7 +5840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="287337500"/>
+    <pos x="7391400" y="287337500"/>
     <ext cx="1809750" cy="1552575"/>
     <pic>
       <nvPicPr>
@@ -5860,7 +5860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="287337500"/>
+    <pos x="9239250" y="287337500"/>
     <ext cx="1809750" cy="1171575"/>
     <pic>
       <nvPicPr>
@@ -5880,7 +5880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="287337500"/>
+    <pos x="11087100" y="287337500"/>
     <ext cx="1809750" cy="561975"/>
     <pic>
       <nvPicPr>
@@ -5900,7 +5900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="302260000"/>
+    <pos x="7391400" y="302260000"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -5920,7 +5920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="302260000"/>
+    <pos x="9239250" y="302260000"/>
     <ext cx="1476375" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5940,7 +5940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="302260000"/>
+    <pos x="11087100" y="302260000"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -5960,7 +5960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="302260000"/>
+    <pos x="12934950" y="302260000"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5980,7 +5980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="304107850"/>
+    <pos x="7391400" y="304107850"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6000,7 +6000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="304107850"/>
+    <pos x="9239250" y="304107850"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6020,7 +6020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="304107850"/>
+    <pos x="11087100" y="304107850"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6040,7 +6040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="304107850"/>
+    <pos x="12934950" y="304107850"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6060,7 +6060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="305955700"/>
+    <pos x="7391400" y="305955700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6080,7 +6080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="305955700"/>
+    <pos x="9239250" y="305955700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6100,7 +6100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="305955700"/>
+    <pos x="11087100" y="305955700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6120,7 +6120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="305955700"/>
+    <pos x="12934950" y="305955700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6140,7 +6140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="318401700"/>
+    <pos x="7391400" y="318401700"/>
     <ext cx="1809750" cy="1419225"/>
     <pic>
       <nvPicPr>
@@ -6160,7 +6160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="318401700"/>
+    <pos x="9239250" y="318401700"/>
     <ext cx="1428750" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6180,7 +6180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="318401700"/>
+    <pos x="11087100" y="318401700"/>
     <ext cx="1428750" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6200,7 +6200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="318401700"/>
+    <pos x="12934950" y="318401700"/>
     <ext cx="1428750" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6220,7 +6220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="320249550"/>
+    <pos x="7391400" y="320249550"/>
     <ext cx="1428750" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6240,7 +6240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="320249550"/>
+    <pos x="9239250" y="320249550"/>
     <ext cx="1809750" cy="1619250"/>
     <pic>
       <nvPicPr>
@@ -6260,7 +6260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="320249550"/>
+    <pos x="11087100" y="320249550"/>
     <ext cx="1428750" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6280,7 +6280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="320249550"/>
+    <pos x="12934950" y="320249550"/>
     <ext cx="1428750" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6300,7 +6300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="328447400"/>
+    <pos x="7391400" y="328447400"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -6320,7 +6320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="328447400"/>
+    <pos x="9239250" y="328447400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6340,7 +6340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="328447400"/>
+    <pos x="11087100" y="328447400"/>
     <ext cx="1714500" cy="1533525"/>
     <pic>
       <nvPicPr>
@@ -6360,7 +6360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="328447400"/>
+    <pos x="12934950" y="328447400"/>
     <ext cx="1714500" cy="1533525"/>
     <pic>
       <nvPicPr>
@@ -6380,7 +6380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="330295250"/>
+    <pos x="7391400" y="330295250"/>
     <ext cx="1714500" cy="1533525"/>
     <pic>
       <nvPicPr>
@@ -6400,7 +6400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="330295250"/>
+    <pos x="9239250" y="330295250"/>
     <ext cx="1714500" cy="1533525"/>
     <pic>
       <nvPicPr>
@@ -6420,7 +6420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="330295250"/>
+    <pos x="11087100" y="330295250"/>
     <ext cx="1714500" cy="1533525"/>
     <pic>
       <nvPicPr>
@@ -6440,7 +6440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="330295250"/>
+    <pos x="12934950" y="330295250"/>
     <ext cx="1714500" cy="1533525"/>
     <pic>
       <nvPicPr>
@@ -6460,7 +6460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="336257900"/>
+    <pos x="7391400" y="336257900"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -6480,7 +6480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="336257900"/>
+    <pos x="9239250" y="336257900"/>
     <ext cx="1809750" cy="1628775"/>
     <pic>
       <nvPicPr>
@@ -6500,7 +6500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="336257900"/>
+    <pos x="11087100" y="336257900"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6520,7 +6520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="336257900"/>
+    <pos x="12934950" y="336257900"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6540,7 +6540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="338105750"/>
+    <pos x="7391400" y="338105750"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6560,7 +6560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="338105750"/>
+    <pos x="9239250" y="338105750"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6580,7 +6580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="338105750"/>
+    <pos x="11087100" y="338105750"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6600,7 +6600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="338105750"/>
+    <pos x="12934950" y="338105750"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6620,7 +6620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="343458800"/>
+    <pos x="7391400" y="343458800"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -6640,7 +6640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="343458800"/>
+    <pos x="9239250" y="343458800"/>
     <ext cx="1809750" cy="1371600"/>
     <pic>
       <nvPicPr>
@@ -6660,7 +6660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="343458800"/>
+    <pos x="11087100" y="343458800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6680,7 +6680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="343458800"/>
+    <pos x="12934950" y="343458800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6700,7 +6700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="345306650"/>
+    <pos x="7391400" y="345306650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6720,7 +6720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="345306650"/>
+    <pos x="9239250" y="345306650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6740,7 +6740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="345306650"/>
+    <pos x="11087100" y="345306650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6760,7 +6760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="345306650"/>
+    <pos x="12934950" y="345306650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6780,7 +6780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="355942900"/>
+    <pos x="7391400" y="355942900"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -6800,7 +6800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="355942900"/>
+    <pos x="9239250" y="355942900"/>
     <ext cx="1809750" cy="1504950"/>
     <pic>
       <nvPicPr>
@@ -6820,7 +6820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="355942900"/>
+    <pos x="11087100" y="355942900"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6840,7 +6840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="355942900"/>
+    <pos x="12934950" y="355942900"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6860,7 +6860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="357790750"/>
+    <pos x="7391400" y="357790750"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6880,7 +6880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="357790750"/>
+    <pos x="9239250" y="357790750"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6900,7 +6900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="357790750"/>
+    <pos x="11087100" y="357790750"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6920,7 +6920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="357790750"/>
+    <pos x="12934950" y="357790750"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6940,7 +6940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="365988600"/>
+    <pos x="7391400" y="365988600"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -6960,7 +6960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="365988600"/>
+    <pos x="9239250" y="365988600"/>
     <ext cx="1809750" cy="1552575"/>
     <pic>
       <nvPicPr>
@@ -6980,7 +6980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="365988600"/>
+    <pos x="11087100" y="365988600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7000,7 +7000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="365988600"/>
+    <pos x="12934950" y="365988600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7020,7 +7020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="367836450"/>
+    <pos x="7391400" y="367836450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7040,7 +7040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="367836450"/>
+    <pos x="9239250" y="367836450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7060,7 +7060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="367836450"/>
+    <pos x="11087100" y="367836450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7080,7 +7080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="367836450"/>
+    <pos x="12934950" y="367836450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7100,7 +7100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="378269500"/>
+    <pos x="7391400" y="378269500"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -7120,7 +7120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="378269500"/>
+    <pos x="9239250" y="378269500"/>
     <ext cx="1809750" cy="1552575"/>
     <pic>
       <nvPicPr>
@@ -7140,7 +7140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="378269500"/>
+    <pos x="11087100" y="378269500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7160,7 +7160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="378269500"/>
+    <pos x="12934950" y="378269500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7180,7 +7180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="380117350"/>
+    <pos x="7391400" y="380117350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7200,7 +7200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="380117350"/>
+    <pos x="9239250" y="380117350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7220,7 +7220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="380117350"/>
+    <pos x="11087100" y="380117350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7240,7 +7240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="380117350"/>
+    <pos x="12934950" y="380117350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7260,7 +7260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="394004800"/>
+    <pos x="7391400" y="394004800"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -7280,7 +7280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="394004800"/>
+    <pos x="9239250" y="394004800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7300,7 +7300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="394004800"/>
+    <pos x="11087100" y="394004800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7320,7 +7320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="394004800"/>
+    <pos x="12934950" y="394004800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7340,7 +7340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="395852650"/>
+    <pos x="7391400" y="395852650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7360,7 +7360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="395852650"/>
+    <pos x="9239250" y="395852650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7380,7 +7380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="395852650"/>
+    <pos x="11087100" y="395852650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7400,7 +7400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="395852650"/>
+    <pos x="12934950" y="395852650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7420,7 +7420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="404050500"/>
+    <pos x="7391400" y="404050500"/>
     <ext cx="1123950" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7440,7 +7440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="415721800"/>
+    <pos x="7391400" y="415721800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7460,7 +7460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="415721800"/>
+    <pos x="9239250" y="415721800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7480,7 +7480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="415721800"/>
+    <pos x="11087100" y="415721800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7500,7 +7500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="415721800"/>
+    <pos x="12934950" y="415721800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7520,7 +7520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="417569650"/>
+    <pos x="7391400" y="417569650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7540,7 +7540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="417569650"/>
+    <pos x="9239250" y="417569650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7560,7 +7560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="417569650"/>
+    <pos x="11087100" y="417569650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7580,7 +7580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="425361100"/>
+    <pos x="7391400" y="425361100"/>
     <ext cx="1809750" cy="1228725"/>
     <pic>
       <nvPicPr>
@@ -7600,7 +7600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="425361100"/>
+    <pos x="9239250" y="425361100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7620,7 +7620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="425361100"/>
+    <pos x="11087100" y="425361100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7640,7 +7640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="425361100"/>
+    <pos x="12934950" y="425361100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7660,7 +7660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="427208950"/>
+    <pos x="7391400" y="427208950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7680,7 +7680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="427208950"/>
+    <pos x="9239250" y="427208950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7700,7 +7700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="427208950"/>
+    <pos x="11087100" y="427208950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7720,7 +7720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="430961800"/>
+    <pos x="7391400" y="430961800"/>
     <ext cx="1190625" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7740,7 +7740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="438594500"/>
+    <pos x="7391400" y="438594500"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -7760,7 +7760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="438594500"/>
+    <pos x="9239250" y="438594500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7780,7 +7780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="438594500"/>
+    <pos x="11087100" y="438594500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7800,7 +7800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="438594500"/>
+    <pos x="12934950" y="438594500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7820,7 +7820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="440442350"/>
+    <pos x="7391400" y="440442350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7840,7 +7840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="440442350"/>
+    <pos x="9239250" y="440442350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7860,7 +7860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="440442350"/>
+    <pos x="11087100" y="440442350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7880,7 +7880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="440442350"/>
+    <pos x="12934950" y="440442350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7900,7 +7900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="442290200"/>
+    <pos x="7391400" y="442290200"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7920,7 +7920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="442290200"/>
+    <pos x="9239250" y="442290200"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7940,7 +7940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="442290200"/>
+    <pos x="11087100" y="442290200"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7960,7 +7960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="442290200"/>
+    <pos x="12934950" y="442290200"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7980,7 +7980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="454736200"/>
+    <pos x="7391400" y="454736200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8000,7 +8000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="454736200"/>
+    <pos x="9239250" y="454736200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8020,7 +8020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="454736200"/>
+    <pos x="11087100" y="454736200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8040,7 +8040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="454736200"/>
+    <pos x="12934950" y="454736200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8060,7 +8060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="456584050"/>
+    <pos x="7391400" y="456584050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8080,7 +8080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="456584050"/>
+    <pos x="9239250" y="456584050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8100,7 +8100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="456584050"/>
+    <pos x="11087100" y="456584050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8120,7 +8120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="456584050"/>
+    <pos x="12934950" y="456584050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8140,7 +8140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="458431900"/>
+    <pos x="7391400" y="458431900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8160,7 +8160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="458431900"/>
+    <pos x="9239250" y="458431900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8180,7 +8180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="465391500"/>
+    <pos x="7391400" y="465391500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8200,7 +8200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="465391500"/>
+    <pos x="9239250" y="465391500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8220,7 +8220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="465391500"/>
+    <pos x="11087100" y="465391500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8240,7 +8240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="465391500"/>
+    <pos x="12934950" y="465391500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8260,7 +8260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="467239350"/>
+    <pos x="7391400" y="467239350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8280,7 +8280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="467239350"/>
+    <pos x="9239250" y="467239350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8300,7 +8300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="467239350"/>
+    <pos x="11087100" y="467239350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8320,7 +8320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="477672400"/>
+    <pos x="7391400" y="477672400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8340,7 +8340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="477672400"/>
+    <pos x="9239250" y="477672400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8360,7 +8360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="477672400"/>
+    <pos x="11087100" y="477672400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8380,7 +8380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="477672400"/>
+    <pos x="12934950" y="477672400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8400,7 +8400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="479520250"/>
+    <pos x="7391400" y="479520250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8420,7 +8420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="479520250"/>
+    <pos x="9239250" y="479520250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8440,7 +8440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="479520250"/>
+    <pos x="11087100" y="479520250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8758,7 +8758,7 @@
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="34" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="2" customWidth="1" min="5" max="5"/>
+    <col width="3" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">

--- a/카드_아키타입/05_로션.xlsx
+++ b/카드_아키타입/05_로션.xlsx
@@ -1076,7 +1076,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="43789600"/>
+    <pos x="7848600" y="43992800"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1096,7 +1096,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="43789600"/>
+    <pos x="9696450" y="43992800"/>
     <ext cx="1809750" cy="1352550"/>
     <pic>
       <nvPicPr>
@@ -1116,7 +1116,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="43789600"/>
+    <pos x="11544300" y="43992800"/>
     <ext cx="1809750" cy="800100"/>
     <pic>
       <nvPicPr>
@@ -1136,7 +1136,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="43789600"/>
+    <pos x="13392150" y="43992800"/>
     <ext cx="1809750" cy="600075"/>
     <pic>
       <nvPicPr>
@@ -1156,7 +1156,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="45637450"/>
+    <pos x="7848600" y="45840650"/>
     <ext cx="1809750" cy="1685925"/>
     <pic>
       <nvPicPr>
@@ -1176,7 +1176,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="45637450"/>
+    <pos x="9696450" y="45840650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1196,7 +1196,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="45637450"/>
+    <pos x="11544300" y="45840650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1216,7 +1216,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="45637450"/>
+    <pos x="13392150" y="45840650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1236,7 +1236,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="47485300"/>
+    <pos x="7848600" y="47688500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1256,7 +1256,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="47485300"/>
+    <pos x="9696450" y="47688500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1276,7 +1276,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="47485300"/>
+    <pos x="11544300" y="47688500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1296,7 +1296,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="47485300"/>
+    <pos x="13392150" y="47688500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1316,7 +1316,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="49333150"/>
+    <pos x="7848600" y="49536350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1336,7 +1336,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="49333150"/>
+    <pos x="9696450" y="49536350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1356,7 +1356,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="49333150"/>
+    <pos x="11544300" y="49536350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1376,7 +1376,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="58889900"/>
+    <pos x="7848600" y="59093100"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1396,7 +1396,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="58889900"/>
+    <pos x="9696450" y="59093100"/>
     <ext cx="1809750" cy="1666875"/>
     <pic>
       <nvPicPr>
@@ -1416,7 +1416,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="58889900"/>
+    <pos x="11544300" y="59093100"/>
     <ext cx="1809750" cy="904875"/>
     <pic>
       <nvPicPr>
@@ -1436,7 +1436,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="58889900"/>
+    <pos x="13392150" y="59093100"/>
     <ext cx="1809750" cy="800100"/>
     <pic>
       <nvPicPr>
@@ -1456,7 +1456,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="60737750"/>
+    <pos x="7848600" y="60940950"/>
     <ext cx="1809750" cy="600075"/>
     <pic>
       <nvPicPr>
@@ -1476,7 +1476,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="60737750"/>
+    <pos x="9696450" y="60940950"/>
     <ext cx="1809750" cy="1685925"/>
     <pic>
       <nvPicPr>
@@ -1496,7 +1496,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="60737750"/>
+    <pos x="11544300" y="60940950"/>
     <ext cx="1809750" cy="1333500"/>
     <pic>
       <nvPicPr>
@@ -1516,7 +1516,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="60737750"/>
+    <pos x="13392150" y="60940950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1536,7 +1536,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="62585600"/>
+    <pos x="7848600" y="62788800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1556,7 +1556,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="62585600"/>
+    <pos x="9696450" y="62788800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1576,7 +1576,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="62585600"/>
+    <pos x="11544300" y="62788800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1596,7 +1596,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="62585600"/>
+    <pos x="13392150" y="62788800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1616,7 +1616,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="64433450"/>
+    <pos x="7848600" y="64636650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1636,7 +1636,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="64433450"/>
+    <pos x="9696450" y="64636650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1656,7 +1656,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="64433450"/>
+    <pos x="11544300" y="64636650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1676,7 +1676,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="64433450"/>
+    <pos x="13392150" y="64636650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1696,7 +1696,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="76835000"/>
+    <pos x="7848600" y="77038200"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1716,7 +1716,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="76835000"/>
+    <pos x="9696450" y="77038200"/>
     <ext cx="1809750" cy="1419225"/>
     <pic>
       <nvPicPr>
@@ -1736,7 +1736,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="76835000"/>
+    <pos x="11544300" y="77038200"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -1756,7 +1756,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="76835000"/>
+    <pos x="13392150" y="77038200"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1776,7 +1776,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="78682850"/>
+    <pos x="7848600" y="78886050"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1796,7 +1796,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="78682850"/>
+    <pos x="9696450" y="78886050"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1816,7 +1816,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="78682850"/>
+    <pos x="11544300" y="78886050"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1836,7 +1836,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="78682850"/>
+    <pos x="13392150" y="78886050"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1856,7 +1856,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="80530700"/>
+    <pos x="7848600" y="80733900"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1876,7 +1876,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="80530700"/>
+    <pos x="9696450" y="80733900"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1896,7 +1896,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="80530700"/>
+    <pos x="11544300" y="80733900"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1916,7 +1916,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="91122500"/>
+    <pos x="7848600" y="91325700"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1936,7 +1936,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="91122500"/>
+    <pos x="9696450" y="91325700"/>
     <ext cx="1809750" cy="1533525"/>
     <pic>
       <nvPicPr>
@@ -1956,7 +1956,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="91122500"/>
+    <pos x="11544300" y="91325700"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -1976,7 +1976,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="91122500"/>
+    <pos x="13392150" y="91325700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1996,7 +1996,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="92970350"/>
+    <pos x="7848600" y="93173550"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2016,7 +2016,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="92970350"/>
+    <pos x="9696450" y="93173550"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2036,7 +2036,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="92970350"/>
+    <pos x="11544300" y="93173550"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2056,7 +2056,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="92970350"/>
+    <pos x="13392150" y="93173550"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2076,7 +2076,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="94818200"/>
+    <pos x="7848600" y="95021400"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2096,7 +2096,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="94818200"/>
+    <pos x="9696450" y="95021400"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2116,7 +2116,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="94818200"/>
+    <pos x="11544300" y="95021400"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2136,7 +2136,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="94818200"/>
+    <pos x="13392150" y="95021400"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2156,7 +2156,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="104190800"/>
+    <pos x="7848600" y="104394000"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2176,7 +2176,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="104190800"/>
+    <pos x="9696450" y="104394000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2196,7 +2196,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="104190800"/>
+    <pos x="11544300" y="104394000"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -2216,7 +2216,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="104190800"/>
+    <pos x="13392150" y="104394000"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2236,7 +2236,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="106038650"/>
+    <pos x="7848600" y="106241850"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2256,7 +2256,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="106038650"/>
+    <pos x="9696450" y="106241850"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2276,7 +2276,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="106038650"/>
+    <pos x="11544300" y="106241850"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2296,7 +2296,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="106038650"/>
+    <pos x="13392150" y="106241850"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2316,7 +2316,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="107886500"/>
+    <pos x="7848600" y="108089700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2336,7 +2336,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="107886500"/>
+    <pos x="9696450" y="108089700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2356,7 +2356,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="107886500"/>
+    <pos x="11544300" y="108089700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2376,7 +2376,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="107886500"/>
+    <pos x="13392150" y="108089700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2396,7 +2396,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="109734350"/>
+    <pos x="7848600" y="109937550"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2416,7 +2416,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="109734350"/>
+    <pos x="9696450" y="109937550"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2436,7 +2436,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="121526300"/>
+    <pos x="7848600" y="121729500"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2456,7 +2456,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="121526300"/>
+    <pos x="9696450" y="121729500"/>
     <ext cx="1419225" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2476,7 +2476,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="121526300"/>
+    <pos x="11544300" y="121729500"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -2496,7 +2496,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="121526300"/>
+    <pos x="13392150" y="121729500"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2516,7 +2516,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="123374150"/>
+    <pos x="7848600" y="123577350"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2536,7 +2536,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="123374150"/>
+    <pos x="9696450" y="123577350"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2556,7 +2556,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="123374150"/>
+    <pos x="11544300" y="123577350"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2576,7 +2576,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="123374150"/>
+    <pos x="13392150" y="123577350"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2596,7 +2596,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="125222000"/>
+    <pos x="7848600" y="125425200"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2616,7 +2616,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="125222000"/>
+    <pos x="9696450" y="125425200"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2636,7 +2636,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="125222000"/>
+    <pos x="11544300" y="125425200"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2656,7 +2656,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="125222000"/>
+    <pos x="13392150" y="125425200"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2676,7 +2676,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="136423400"/>
+    <pos x="7848600" y="136626600"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2696,7 +2696,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="136423400"/>
+    <pos x="9696450" y="136626600"/>
     <ext cx="1809750" cy="1657350"/>
     <pic>
       <nvPicPr>
@@ -2716,7 +2716,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="136423400"/>
+    <pos x="11544300" y="136626600"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -2736,7 +2736,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="136423400"/>
+    <pos x="13392150" y="136626600"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2756,7 +2756,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="138271250"/>
+    <pos x="7848600" y="138474450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2776,7 +2776,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="138271250"/>
+    <pos x="9696450" y="138474450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2796,7 +2796,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="138271250"/>
+    <pos x="11544300" y="138474450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2816,7 +2816,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="138271250"/>
+    <pos x="13392150" y="138474450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2836,7 +2836,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="140119100"/>
+    <pos x="7848600" y="140322300"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2856,7 +2856,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="140119100"/>
+    <pos x="9696450" y="140322300"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2876,7 +2876,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="140119100"/>
+    <pos x="11544300" y="140322300"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2896,7 +2896,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="140119100"/>
+    <pos x="13392150" y="140322300"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5276,7 +5276,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="271970500"/>
+    <pos x="7848600" y="271767300"/>
     <ext cx="1809750" cy="1800225"/>
     <pic>
       <nvPicPr>
@@ -5296,7 +5296,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="271970500"/>
+    <pos x="9696450" y="271767300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5316,7 +5316,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="271970500"/>
+    <pos x="11544300" y="271767300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5336,7 +5336,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="271970500"/>
+    <pos x="13392150" y="271767300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5356,7 +5356,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="273818350"/>
+    <pos x="7848600" y="273615150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5376,7 +5376,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="273818350"/>
+    <pos x="9696450" y="273615150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5396,7 +5396,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="273818350"/>
+    <pos x="11544300" y="273615150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5416,7 +5416,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="279171400"/>
+    <pos x="7848600" y="278968200"/>
     <ext cx="1400175" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5436,7 +5436,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="279171400"/>
+    <pos x="9696450" y="278968200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5456,7 +5456,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="279171400"/>
+    <pos x="11544300" y="278968200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5476,7 +5476,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="279171400"/>
+    <pos x="13392150" y="278968200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5496,7 +5496,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="281019250"/>
+    <pos x="7848600" y="280816050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5516,7 +5516,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="281019250"/>
+    <pos x="9696450" y="280816050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5536,7 +5536,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="281019250"/>
+    <pos x="11544300" y="280816050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5556,7 +5556,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="287566100"/>
+    <pos x="7848600" y="287159700"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -5576,7 +5576,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="287566100"/>
+    <pos x="9696450" y="287159700"/>
     <ext cx="1809750" cy="1533525"/>
     <pic>
       <nvPicPr>
@@ -5596,7 +5596,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="287566100"/>
+    <pos x="11544300" y="287159700"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -5616,7 +5616,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="287566100"/>
+    <pos x="13392150" y="287159700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5636,7 +5636,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="289413950"/>
+    <pos x="7848600" y="289007550"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5656,7 +5656,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="289413950"/>
+    <pos x="9696450" y="289007550"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5676,7 +5676,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="289413950"/>
+    <pos x="11544300" y="289007550"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5696,7 +5696,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="289413950"/>
+    <pos x="13392150" y="289007550"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5716,7 +5716,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="291261800"/>
+    <pos x="7848600" y="290855400"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5736,7 +5736,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="291261800"/>
+    <pos x="9696450" y="290855400"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5756,7 +5756,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="291261800"/>
+    <pos x="11544300" y="290855400"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5776,7 +5776,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="291261800"/>
+    <pos x="13392150" y="290855400"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5796,7 +5796,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="300634400"/>
+    <pos x="7848600" y="300228000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5816,7 +5816,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="300634400"/>
+    <pos x="9696450" y="300228000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5836,7 +5836,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="300634400"/>
+    <pos x="11544300" y="300228000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5856,7 +5856,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="300634400"/>
+    <pos x="13392150" y="300228000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5876,7 +5876,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="302482250"/>
+    <pos x="7848600" y="302075850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5896,7 +5896,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="302482250"/>
+    <pos x="9696450" y="302075850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5916,7 +5916,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="302482250"/>
+    <pos x="11544300" y="302075850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5936,7 +5936,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="302482250"/>
+    <pos x="13392150" y="302075850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5956,7 +5956,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="304330100"/>
+    <pos x="7848600" y="303923700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5976,7 +5976,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="304330100"/>
+    <pos x="9696450" y="303923700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5996,7 +5996,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="312077100"/>
+    <pos x="7848600" y="311670700"/>
     <ext cx="1809750" cy="1552575"/>
     <pic>
       <nvPicPr>
@@ -6016,7 +6016,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="312077100"/>
+    <pos x="9696450" y="311670700"/>
     <ext cx="1809750" cy="1171575"/>
     <pic>
       <nvPicPr>
@@ -6036,7 +6036,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="312077100"/>
+    <pos x="11544300" y="311670700"/>
     <ext cx="1809750" cy="561975"/>
     <pic>
       <nvPicPr>
@@ -6056,7 +6056,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="328193400"/>
+    <pos x="7848600" y="327787000"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -6076,7 +6076,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="328193400"/>
+    <pos x="9696450" y="327787000"/>
     <ext cx="1476375" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6096,7 +6096,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="328193400"/>
+    <pos x="11544300" y="327787000"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -6116,7 +6116,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="328193400"/>
+    <pos x="13392150" y="327787000"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6136,7 +6136,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="330041250"/>
+    <pos x="7848600" y="329634850"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6156,7 +6156,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="330041250"/>
+    <pos x="9696450" y="329634850"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6176,7 +6176,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="330041250"/>
+    <pos x="11544300" y="329634850"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6196,7 +6196,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="330041250"/>
+    <pos x="13392150" y="329634850"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6216,7 +6216,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="331889100"/>
+    <pos x="7848600" y="331482700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6236,7 +6236,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="331889100"/>
+    <pos x="9696450" y="331482700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6256,7 +6256,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="331889100"/>
+    <pos x="11544300" y="331482700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6276,7 +6276,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="331889100"/>
+    <pos x="13392150" y="331482700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6296,7 +6296,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="344716100"/>
+    <pos x="7848600" y="344309700"/>
     <ext cx="1809750" cy="1419225"/>
     <pic>
       <nvPicPr>
@@ -6316,7 +6316,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="344716100"/>
+    <pos x="9696450" y="344309700"/>
     <ext cx="1428750" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6336,7 +6336,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="344716100"/>
+    <pos x="11544300" y="344309700"/>
     <ext cx="1428750" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6356,7 +6356,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="344716100"/>
+    <pos x="13392150" y="344309700"/>
     <ext cx="1428750" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6376,7 +6376,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="346563950"/>
+    <pos x="7848600" y="346157550"/>
     <ext cx="1428750" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6396,7 +6396,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="346563950"/>
+    <pos x="9696450" y="346157550"/>
     <ext cx="1809750" cy="1619250"/>
     <pic>
       <nvPicPr>
@@ -6416,7 +6416,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="346563950"/>
+    <pos x="11544300" y="346157550"/>
     <ext cx="1428750" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6436,7 +6436,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="346563950"/>
+    <pos x="13392150" y="346157550"/>
     <ext cx="1428750" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -6456,7 +6456,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="355549200"/>
+    <pos x="7848600" y="355142800"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -6476,7 +6476,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="355549200"/>
+    <pos x="9696450" y="355142800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6496,7 +6496,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="355549200"/>
+    <pos x="11544300" y="355142800"/>
     <ext cx="1714500" cy="1533525"/>
     <pic>
       <nvPicPr>
@@ -6516,7 +6516,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="355549200"/>
+    <pos x="13392150" y="355142800"/>
     <ext cx="1714500" cy="1533525"/>
     <pic>
       <nvPicPr>
@@ -6536,7 +6536,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="357397050"/>
+    <pos x="7848600" y="356990650"/>
     <ext cx="1714500" cy="1533525"/>
     <pic>
       <nvPicPr>
@@ -6556,7 +6556,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="357397050"/>
+    <pos x="9696450" y="356990650"/>
     <ext cx="1714500" cy="1533525"/>
     <pic>
       <nvPicPr>
@@ -6576,7 +6576,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="357397050"/>
+    <pos x="11544300" y="356990650"/>
     <ext cx="1714500" cy="1533525"/>
     <pic>
       <nvPicPr>
@@ -6596,7 +6596,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="357397050"/>
+    <pos x="13392150" y="356990650"/>
     <ext cx="1714500" cy="1533525"/>
     <pic>
       <nvPicPr>
@@ -6616,7 +6616,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="363131100"/>
+    <pos x="7848600" y="362724700"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -6636,7 +6636,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="363131100"/>
+    <pos x="9696450" y="362724700"/>
     <ext cx="1809750" cy="1628775"/>
     <pic>
       <nvPicPr>
@@ -6656,7 +6656,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="363131100"/>
+    <pos x="11544300" y="362724700"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6676,7 +6676,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="363131100"/>
+    <pos x="13392150" y="362724700"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6696,7 +6696,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="364978950"/>
+    <pos x="7848600" y="364572550"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6716,7 +6716,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="364978950"/>
+    <pos x="9696450" y="364572550"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6736,7 +6736,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="364978950"/>
+    <pos x="11544300" y="364572550"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6756,7 +6756,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="364978950"/>
+    <pos x="13392150" y="364572550"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6776,7 +6776,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="371729000"/>
+    <pos x="7848600" y="371322600"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -6796,7 +6796,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="371729000"/>
+    <pos x="9696450" y="371322600"/>
     <ext cx="1809750" cy="1371600"/>
     <pic>
       <nvPicPr>
@@ -6816,7 +6816,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="371729000"/>
+    <pos x="11544300" y="371322600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6836,7 +6836,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="371729000"/>
+    <pos x="13392150" y="371322600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6856,7 +6856,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="373576850"/>
+    <pos x="7848600" y="373170450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6876,7 +6876,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="373576850"/>
+    <pos x="9696450" y="373170450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6896,7 +6896,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="373576850"/>
+    <pos x="11544300" y="373170450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6916,7 +6916,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="373576850"/>
+    <pos x="13392150" y="373170450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6936,7 +6936,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="384390900"/>
+    <pos x="7848600" y="383984500"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -6956,7 +6956,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="384390900"/>
+    <pos x="9696450" y="383984500"/>
     <ext cx="1809750" cy="1504950"/>
     <pic>
       <nvPicPr>
@@ -6976,7 +6976,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="384390900"/>
+    <pos x="11544300" y="383984500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6996,7 +6996,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="384390900"/>
+    <pos x="13392150" y="383984500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7016,7 +7016,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="386238750"/>
+    <pos x="7848600" y="385832350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7036,7 +7036,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="386238750"/>
+    <pos x="9696450" y="385832350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7056,7 +7056,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="386238750"/>
+    <pos x="11544300" y="385832350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7076,7 +7076,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="386238750"/>
+    <pos x="13392150" y="385832350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7096,7 +7096,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="395020800"/>
+    <pos x="7848600" y="394614400"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -7116,7 +7116,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="395020800"/>
+    <pos x="9696450" y="394614400"/>
     <ext cx="1809750" cy="1552575"/>
     <pic>
       <nvPicPr>
@@ -7136,7 +7136,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="395020800"/>
+    <pos x="11544300" y="394614400"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7156,7 +7156,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="395020800"/>
+    <pos x="13392150" y="394614400"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7176,7 +7176,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="396868650"/>
+    <pos x="7848600" y="396462250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7196,7 +7196,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="396868650"/>
+    <pos x="9696450" y="396462250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7216,7 +7216,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="396868650"/>
+    <pos x="11544300" y="396462250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7236,7 +7236,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="396868650"/>
+    <pos x="13392150" y="396462250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7256,7 +7256,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="407885900"/>
+    <pos x="7848600" y="407479500"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -7276,7 +7276,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="407885900"/>
+    <pos x="9696450" y="407479500"/>
     <ext cx="1809750" cy="1552575"/>
     <pic>
       <nvPicPr>
@@ -7296,7 +7296,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="407885900"/>
+    <pos x="11544300" y="407479500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7316,7 +7316,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="407885900"/>
+    <pos x="13392150" y="407479500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7336,7 +7336,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="409733750"/>
+    <pos x="7848600" y="409327350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7356,7 +7356,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="409733750"/>
+    <pos x="9696450" y="409327350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7376,7 +7376,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="409733750"/>
+    <pos x="11544300" y="409327350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7396,7 +7396,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="409733750"/>
+    <pos x="13392150" y="409327350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7416,7 +7416,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="424408600"/>
+    <pos x="7848600" y="424002200"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -7436,7 +7436,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="424408600"/>
+    <pos x="9696450" y="424002200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7456,7 +7456,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="424408600"/>
+    <pos x="11544300" y="424002200"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7476,7 +7476,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="424408600"/>
+    <pos x="13392150" y="424002200"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7496,7 +7496,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="426256450"/>
+    <pos x="7848600" y="425850050"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7516,7 +7516,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="426256450"/>
+    <pos x="9696450" y="425850050"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7536,7 +7536,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="426256450"/>
+    <pos x="11544300" y="425850050"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7556,7 +7556,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="426256450"/>
+    <pos x="13392150" y="425850050"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7576,7 +7576,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="435241700"/>
+    <pos x="7848600" y="434835300"/>
     <ext cx="1123950" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7596,7 +7596,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="447725800"/>
+    <pos x="7848600" y="447319400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7616,7 +7616,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="447725800"/>
+    <pos x="9696450" y="447319400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7636,7 +7636,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="447725800"/>
+    <pos x="11544300" y="447319400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7656,7 +7656,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="447725800"/>
+    <pos x="13392150" y="447319400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7676,7 +7676,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="449573650"/>
+    <pos x="7848600" y="449167250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7696,7 +7696,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="449573650"/>
+    <pos x="9696450" y="449167250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7716,7 +7716,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="449573650"/>
+    <pos x="11544300" y="449167250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7736,7 +7736,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="457949300"/>
+    <pos x="7848600" y="457542900"/>
     <ext cx="1809750" cy="1228725"/>
     <pic>
       <nvPicPr>
@@ -7756,7 +7756,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="457949300"/>
+    <pos x="9696450" y="457542900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7776,7 +7776,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="457949300"/>
+    <pos x="11544300" y="457542900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7796,7 +7796,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="457949300"/>
+    <pos x="13392150" y="457542900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7816,7 +7816,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="459797150"/>
+    <pos x="7848600" y="459390750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7836,7 +7836,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="459797150"/>
+    <pos x="9696450" y="459390750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7856,7 +7856,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="459797150"/>
+    <pos x="11544300" y="459390750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7876,7 +7876,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="464134200"/>
+    <pos x="7848600" y="463727800"/>
     <ext cx="1190625" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7896,7 +7896,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="472376500"/>
+    <pos x="7848600" y="471970100"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -7916,7 +7916,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="472376500"/>
+    <pos x="9696450" y="471970100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7936,7 +7936,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="472376500"/>
+    <pos x="11544300" y="471970100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -7956,7 +7956,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="472376500"/>
+    <pos x="13392150" y="471970100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7976,7 +7976,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="474224350"/>
+    <pos x="7848600" y="473817950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -7996,7 +7996,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="474224350"/>
+    <pos x="9696450" y="473817950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -8016,7 +8016,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="474224350"/>
+    <pos x="11544300" y="473817950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -8036,7 +8036,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="474224350"/>
+    <pos x="13392150" y="473817950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -8056,7 +8056,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="476072200"/>
+    <pos x="7848600" y="475665800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -8076,7 +8076,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="476072200"/>
+    <pos x="9696450" y="475665800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -8096,7 +8096,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="476072200"/>
+    <pos x="11544300" y="475665800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -8116,7 +8116,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="476072200"/>
+    <pos x="13392150" y="475665800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -8136,7 +8136,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="489305600"/>
+    <pos x="7848600" y="488899200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8156,7 +8156,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="489305600"/>
+    <pos x="9696450" y="488899200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8176,7 +8176,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="489305600"/>
+    <pos x="11544300" y="488899200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8196,7 +8196,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="489305600"/>
+    <pos x="13392150" y="488899200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8216,7 +8216,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="491153450"/>
+    <pos x="7848600" y="490747050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8236,7 +8236,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="491153450"/>
+    <pos x="9696450" y="490747050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8256,7 +8256,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="491153450"/>
+    <pos x="11544300" y="490747050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8276,7 +8276,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="491153450"/>
+    <pos x="13392150" y="490747050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8296,7 +8296,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="493001300"/>
+    <pos x="7848600" y="492594900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8316,7 +8316,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="493001300"/>
+    <pos x="9696450" y="492594900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8336,7 +8336,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="500341900"/>
+    <pos x="7848600" y="499935500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8356,7 +8356,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="500341900"/>
+    <pos x="9696450" y="499935500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8376,7 +8376,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="500341900"/>
+    <pos x="11544300" y="499935500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8396,7 +8396,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="500341900"/>
+    <pos x="13392150" y="499935500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8416,7 +8416,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="502189750"/>
+    <pos x="7848600" y="501783350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8436,7 +8436,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="502189750"/>
+    <pos x="9696450" y="501783350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8456,7 +8456,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="502189750"/>
+    <pos x="11544300" y="501783350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8476,7 +8476,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="513816600"/>
+    <pos x="7848600" y="513410200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8496,7 +8496,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="513816600"/>
+    <pos x="9696450" y="513410200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8516,7 +8516,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="513816600"/>
+    <pos x="11544300" y="513410200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8536,7 +8536,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="513816600"/>
+    <pos x="13392150" y="513410200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8556,7 +8556,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="515664450"/>
+    <pos x="7848600" y="515258050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8576,7 +8576,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="515664450"/>
+    <pos x="9696450" y="515258050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -8596,7 +8596,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="515664450"/>
+    <pos x="11544300" y="515258050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -9075,7 +9075,7 @@
       </c>
       <c r="F9" s="10" t="inlineStr">
         <is>
-          <t>올리브유화왁스4g / (빠른 유화, 점도를 원할시)</t>
+          <t>올리브유화왁스4g · (빠른 유화, 점도를 원할시)</t>
         </is>
       </c>
     </row>
@@ -9169,7 +9169,7 @@
           <t>사탕수수 채취, 점증제</t>
         </is>
       </c>
-      <c r="F12" s="10" t="n"/>
+      <c r="F12" s="10" t="inlineStr"/>
     </row>
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="10" t="inlineStr">
@@ -9327,7 +9327,7 @@
       </c>
       <c r="F17" s="10" t="inlineStr">
         <is>
-          <t>천연한방보존제1g / (네롤리워터의 양을 59g으로 늘려주세요.)</t>
+          <t>천연한방보존제1g · (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
@@ -9354,7 +9354,7 @@
       </c>
       <c r="E18" s="10" t="inlineStr">
         <is>
-          <t>무향을 원하면 생략가능, / 네롤리, 일링일랑, 프랑킨센스, / 버가못FCF 블렌딩</t>
+          <t>무향을 원하면 생략가능 · 네롤리, 일링일랑, 프랑킨센스 · 버가못FCF 블렌딩</t>
         </is>
       </c>
       <c r="F18" s="10" t="inlineStr">
@@ -9539,10 +9539,10 @@
       </c>
       <c r="E28" s="25" t="inlineStr">
         <is>
-          <t>올리브오일 지방산 함유, / O/W유화제</t>
-        </is>
-      </c>
-      <c r="F28" s="25" t="n"/>
+          <t>올리브오일 지방산 함유 · O · W유화제</t>
+        </is>
+      </c>
+      <c r="F28" s="25" t="inlineStr"/>
     </row>
     <row r="29" ht="32" customHeight="1">
       <c r="A29" s="25" t="inlineStr">
@@ -9567,7 +9567,7 @@
       </c>
       <c r="E29" s="25" t="inlineStr">
         <is>
-          <t>피지성분과비슷, / 빠른흡수</t>
+          <t>피지성분과비슷 · 빠른흡수</t>
         </is>
       </c>
       <c r="F29" s="25" t="inlineStr">
@@ -9599,10 +9599,10 @@
       </c>
       <c r="E30" s="25" t="inlineStr">
         <is>
-          <t>세틸알코올+지방산 유도체를 반응시켜 / 만든 에스테르오일, / 끈적임이 없고 가볍고 산뜻한 사용감</t>
-        </is>
-      </c>
-      <c r="F30" s="25" t="n"/>
+          <t>세틸알코올+지방산 유도체를 반응시켜 · 만든 에스테르오일 · 끈적임이 없고 가볍고 산뜻한 사용감</t>
+        </is>
+      </c>
+      <c r="F30" s="25" t="inlineStr"/>
     </row>
     <row r="31" ht="32" customHeight="1">
       <c r="A31" s="25" t="inlineStr">
@@ -9664,7 +9664,7 @@
       </c>
       <c r="F32" s="25" t="inlineStr">
         <is>
-          <t>세라마이드, / 알란토인분말 사용시 0.2g</t>
+          <t>세라마이드 · 알란토인분말 사용시 0.2g</t>
         </is>
       </c>
     </row>
@@ -9696,7 +9696,7 @@
       </c>
       <c r="F33" s="25" t="inlineStr">
         <is>
-          <t>비피다발효용해물 / 사카로미세스발효여과물</t>
+          <t>비피다발효용해물 · 사카로미세스발효여과물</t>
         </is>
       </c>
     </row>
@@ -9755,12 +9755,12 @@
       </c>
       <c r="E35" s="25" t="inlineStr">
         <is>
-          <t>5종 세라마이드, / 피부 장벽 강화</t>
+          <t>5종 세라마이드 · 피부 장벽 강화</t>
         </is>
       </c>
       <c r="F35" s="25" t="inlineStr">
         <is>
-          <t>스쿠알란, / 보르피린</t>
+          <t>스쿠알란 · 보르피린</t>
         </is>
       </c>
     </row>
@@ -9792,7 +9792,7 @@
       </c>
       <c r="F36" s="25" t="inlineStr">
         <is>
-          <t>천연한방보존제1g / (네롤리워터의 양을 59g으로 늘려주세요.)</t>
+          <t>천연한방보존제1g · (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
@@ -10008,12 +10008,12 @@
       </c>
       <c r="E47" s="10" t="inlineStr">
         <is>
-          <t>물과 오일 분리 저지, / 유화제</t>
+          <t>물과 오일 분리 저지 · 유화제</t>
         </is>
       </c>
       <c r="F47" s="10" t="inlineStr">
         <is>
-          <t>올리브유화왁스4g / (빠른 유화, 점도를 원할시)</t>
+          <t>올리브유화왁스4g · (빠른 유화, 점도를 원할시)</t>
         </is>
       </c>
     </row>
@@ -10072,7 +10072,7 @@
       </c>
       <c r="E49" s="10" t="inlineStr">
         <is>
-          <t>균번식 억제제, / 황금, 자몽씨추출물 등</t>
+          <t>균번식 억제제 · 황금, 자몽씨추출물 등</t>
         </is>
       </c>
       <c r="F49" s="10" t="inlineStr">
@@ -10109,7 +10109,7 @@
       </c>
       <c r="F50" s="10" t="inlineStr">
         <is>
-          <t>에코보습제, / 낫또모이스트 등 / 촉촉함을 원한다면 히아루론산을 더 / 추가해주세요.</t>
+          <t>에코보습제 · 낫또모이스트 등 · 촉촉함을 원한다면 히아루론산을 더 · 추가해주세요.</t>
         </is>
       </c>
     </row>
@@ -10141,7 +10141,7 @@
       </c>
       <c r="F51" s="10" t="inlineStr">
         <is>
-          <t>녹차, 어성초, / 오이추출물</t>
+          <t>녹차, 어성초 · 오이추출물</t>
         </is>
       </c>
     </row>
@@ -10168,7 +10168,7 @@
       </c>
       <c r="E52" s="10" t="inlineStr">
         <is>
-          <t>목련과허브, / 꽃에서 추출,</t>
+          <t>목련과허브 · 꽃에서 추출</t>
         </is>
       </c>
       <c r="F52" s="10" t="inlineStr">
@@ -10352,7 +10352,7 @@
       </c>
       <c r="F61" s="25" t="inlineStr">
         <is>
-          <t>아르간, 아보카도, 달맞이, 보리지오일 등. / 단, 좀더 촉촉함을 원한다면 코포아수버터와 같은 버터류로 대체할 것.</t>
+          <t>아르간, 아보카도, 달맞이, 보리지오일 등. · 단, 좀더 촉촉함을 원한다면 코포아수버터와 같은 버터류로 대체할 것.</t>
         </is>
       </c>
     </row>
@@ -10384,7 +10384,7 @@
       </c>
       <c r="F62" s="25" t="inlineStr">
         <is>
-          <t>올리브유화왁스4g / (빠른 유화, 점도를 원할시)</t>
+          <t>올리브유화왁스4g · (빠른 유화, 점도를 원할시)</t>
         </is>
       </c>
     </row>
@@ -10443,12 +10443,12 @@
       </c>
       <c r="E64" s="25" t="inlineStr">
         <is>
-          <t>천연한방보존제는 생약 중 항균력이 우수한 오배자, 가자, 석곡, 산초를 초음파 방식으로 / 추출하여 조합한 화장품용 천연유래 항균제입니다</t>
+          <t>천연한방보존제는 생약 중 항균력이 우수한 오배자, 가자, 석곡, 산초를 초음파 방식으로 · 추출하여 조합한 화장품용 천연유래 항균제입니다</t>
         </is>
       </c>
       <c r="F64" s="25" t="inlineStr">
         <is>
-          <t>1,2-헥산디올0.6g / (갈락토미세스 발효여과물의 양을 12.4g로 줄여주세요.)</t>
+          <t>1,2-헥산디올0.6g · (갈락토미세스 발효여과물의 양을 12.4g로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -10484,7 +10484,7 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="80" customHeight="1">
+    <row r="66" ht="96" customHeight="1">
       <c r="A66" s="25" t="inlineStr">
         <is>
           <t>유기농 카밍 5 솔루션</t>
@@ -10507,12 +10507,12 @@
       </c>
       <c r="E66" s="25" t="inlineStr">
         <is>
-          <t>피부진정에 좋은 5가지 / 유기농 허브 유효성분을 유기농 글리세린에 추출. / (유기농 알로에베라잎/라벤더꽃/캐모마일꽃추출물/ 병풀추출물/녹차추출물)</t>
+          <t>피부진정에 좋은 5가지 · 유기농 허브 유효성분을 유기농 글리세린에 추출. · (유기농 알로에베라잎 · 라벤더꽃 · 캐모마일꽃추출물 · 병풀추출물 · 녹차추출물)</t>
         </is>
       </c>
       <c r="F66" s="25" t="inlineStr">
         <is>
-          <t>오가닉 7 솔루션, / 유기농 프레쉬 5 솔루션</t>
+          <t>오가닉 7 솔루션 · 유기농 프레쉬 5 솔루션</t>
         </is>
       </c>
     </row>
@@ -10757,12 +10757,12 @@
       </c>
       <c r="E78" s="10" t="inlineStr">
         <is>
-          <t>프랑스 세더마, / 하이드로제네이티드 폴리이소부텐+지모추출물=보르피린, 보르피린 5% 임상실험에서 볼륨 반응 , 지용성 원료. / 열안정성.</t>
+          <t>프랑스 세더마 · 하이드로제네이티드 폴리이소부텐+지모추출물=보르피린, 보르피린 5% 임상실험에서 볼륨 반응 , 지용성 원료. · 열안정성.</t>
         </is>
       </c>
       <c r="F78" s="10" t="inlineStr">
         <is>
-          <t>10g(10%)을 원한다면 / 오일을 5g 줄일 것.</t>
+          <t>10g(10%)을 원한다면 · 오일을 5g 줄일 것.</t>
         </is>
       </c>
     </row>
@@ -10789,12 +10789,12 @@
       </c>
       <c r="E79" s="10" t="inlineStr">
         <is>
-          <t>에코인증, 올리브오일유래. / 물과 오일 분리저지</t>
+          <t>에코인증, 올리브오일유래. · 물과 오일 분리저지</t>
         </is>
       </c>
       <c r="F79" s="10" t="inlineStr">
         <is>
-          <t>올리브유화왁스4g / (빠른 유화, 점도를 원할시)</t>
+          <t>올리브유화왁스4g · (빠른 유화, 점도를 원할시)</t>
         </is>
       </c>
     </row>
@@ -10821,7 +10821,7 @@
       </c>
       <c r="E80" s="10" t="inlineStr">
         <is>
-          <t>올리브유화왁스 보조. / 흡수력이 좋게.백탁을 적게.</t>
+          <t>올리브유화왁스 보조. · 흡수력이 좋게.백탁을 적게.</t>
         </is>
       </c>
       <c r="F80" s="10" t="inlineStr">
@@ -10853,7 +10853,7 @@
       </c>
       <c r="E81" s="10" t="inlineStr">
         <is>
-          <t>진정, 불가리안 장미를수증기 증류 / 수용성 성분을 다량 함유.</t>
+          <t>진정, 불가리안 장미를수증기 증류 · 수용성 성분을 다량 함유.</t>
         </is>
       </c>
       <c r="F81" s="10" t="inlineStr">
@@ -10885,7 +10885,7 @@
       </c>
       <c r="E82" s="10" t="inlineStr">
         <is>
-          <t>고중저분자 히아루론산 / 가볍고 흡수력</t>
+          <t>고중저분자 히아루론산 · 가볍고 흡수력</t>
         </is>
       </c>
       <c r="F82" s="10" t="inlineStr">
@@ -10922,7 +10922,7 @@
       </c>
       <c r="F83" s="10" t="inlineStr">
         <is>
-          <t>1,2-헥산디올 2g / (로즈워터의 양을 57g으로 줄여주세요.)</t>
+          <t>1,2-헥산디올 2g · (로즈워터의 양을 57g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -10949,7 +10949,7 @@
       </c>
       <c r="E84" s="10" t="inlineStr">
         <is>
-          <t>비타민B3, 녹황색채소, / 식약처 인증 미백원료</t>
+          <t>비타민B3, 녹황색채소 · 식약처 인증 미백원료</t>
         </is>
       </c>
       <c r="F84" s="10" t="inlineStr">
@@ -10981,7 +10981,7 @@
       </c>
       <c r="E85" s="10" t="inlineStr">
         <is>
-          <t>수분공급,진정, / 점도상승, 유화안정.</t>
+          <t>수분공급,진정 · 점도상승, 유화안정.</t>
         </is>
       </c>
       <c r="F85" s="10" t="inlineStr">
@@ -11206,7 +11206,7 @@
       </c>
       <c r="E96" s="25" t="inlineStr">
         <is>
-          <t>프랑스 세더마, / 하이드로제네이티드 폴리이소부텐+지모추출물=보르피린, 보르피린 5% 임상실험에서 볼륨 반응 , 지용성 원료. / 열안정성.(80℃에서 4시간 견딤)</t>
+          <t>프랑스 세더마 · 하이드로제네이티드 폴리이소부텐+지모추출물=보르피린, 보르피린 5% 임상실험에서 볼륨 반응 , 지용성 원료. · 열안정성.(80℃에서 4시간 견딤)</t>
         </is>
       </c>
       <c r="F96" s="25" t="inlineStr">
@@ -11238,10 +11238,10 @@
       </c>
       <c r="E97" s="25" t="inlineStr">
         <is>
-          <t>에코인증, 가장 저점도. / 올리브오일 유래. / 물과 오일 분리저지.</t>
-        </is>
-      </c>
-      <c r="F97" s="25" t="n"/>
+          <t>에코인증, 가장 저점도. · 올리브오일 유래. · 물과 오일 분리저지.</t>
+        </is>
+      </c>
+      <c r="F97" s="25" t="inlineStr"/>
     </row>
     <row r="98" ht="32" customHeight="1">
       <c r="A98" s="25" t="inlineStr">
@@ -11266,7 +11266,7 @@
       </c>
       <c r="E98" s="25" t="inlineStr">
         <is>
-          <t>보조 유화제. / 입자를 작고 흡수력이 좋게. / 백탁을 적게.</t>
+          <t>보조 유화제. · 입자를 작고 흡수력이 좋게. · 백탁을 적게.</t>
         </is>
       </c>
       <c r="F98" s="25" t="inlineStr">
@@ -11298,7 +11298,7 @@
       </c>
       <c r="E99" s="25" t="inlineStr">
         <is>
-          <t>로사 다마스크 장미수, / 수증기 증류법 추출.</t>
+          <t>로사 다마스크 장미수 · 수증기 증류법 추출.</t>
         </is>
       </c>
       <c r="F99" s="25" t="inlineStr">
@@ -11330,7 +11330,7 @@
       </c>
       <c r="E100" s="25" t="inlineStr">
         <is>
-          <t>청국장의 끈적한 성분 , / 천연보습제, 감마 PGA, / 끈적임없는 보습.</t>
+          <t>청국장의 끈적한 성분 · 천연보습제, 감마 PGA · 끈적임없는 보습.</t>
         </is>
       </c>
       <c r="F100" s="25" t="inlineStr">
@@ -11367,7 +11367,7 @@
       </c>
       <c r="F101" s="25" t="inlineStr">
         <is>
-          <t>1,2-헥산디올 2g / (로즈워터의 양을 72g으로 줄여주세요.)</t>
+          <t>1,2-헥산디올 2g · (로즈워터의 양을 72g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -11394,7 +11394,7 @@
       </c>
       <c r="E102" s="25" t="inlineStr">
         <is>
-          <t>비타민B3,, / 식약처 인증 미백 원료</t>
+          <t>비타민B3 · 식약처 인증 미백 원료</t>
         </is>
       </c>
       <c r="F102" s="25" t="inlineStr">
@@ -11631,7 +11631,7 @@
       </c>
       <c r="F113" s="10" t="inlineStr">
         <is>
-          <t>동백, 아보카도, / 로즈힙오일 등</t>
+          <t>동백, 아보카도 · 로즈힙오일 등</t>
         </is>
       </c>
     </row>
@@ -11658,12 +11658,12 @@
       </c>
       <c r="E114" s="10" t="inlineStr">
         <is>
-          <t>에코인증. 올리브오일에서 유래, / 오일과 물이 분리저지</t>
+          <t>에코인증. 올리브오일에서 유래 · 오일과 물이 분리저지</t>
         </is>
       </c>
       <c r="F114" s="10" t="inlineStr">
         <is>
-          <t>올리브유화왁스4g / (빠른 유화, 점도를 원할시)</t>
+          <t>올리브유화왁스4g · (빠른 유화, 점도를 원할시)</t>
         </is>
       </c>
     </row>
@@ -11727,7 +11727,7 @@
       </c>
       <c r="F116" s="10" t="inlineStr">
         <is>
-          <t>프리미엄 / 녹차워터</t>
+          <t>프리미엄 · 녹차워터</t>
         </is>
       </c>
     </row>
@@ -11759,7 +11759,7 @@
       </c>
       <c r="F117" s="10" t="inlineStr">
         <is>
-          <t>히아루론산, / 리피듀어, 식물성글리세린</t>
+          <t>히아루론산 · 리피듀어, 식물성글리세린</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       </c>
       <c r="E118" s="10" t="inlineStr">
         <is>
-          <t>저온 감압, 성분 파괴 최소. / 폴리페놀 풍부</t>
+          <t>저온 감압, 성분 파괴 최소. · 폴리페놀 풍부</t>
         </is>
       </c>
       <c r="F118" s="10" t="inlineStr">
@@ -11823,7 +11823,7 @@
       </c>
       <c r="F119" s="10" t="inlineStr">
         <is>
-          <t>로즈플라워겔, / 네롤리플라워겔</t>
+          <t>로즈플라워겔 · 네롤리플라워겔</t>
         </is>
       </c>
     </row>
@@ -11887,7 +11887,7 @@
       </c>
       <c r="F121" s="10" t="inlineStr">
         <is>
-          <t>1,2-헥산디올2g / (로즈마리워터의 양을 53g으로 줄여주세요.)</t>
+          <t>1,2-헥산디올2g · (로즈마리워터의 양을 53g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -11914,7 +11914,7 @@
       </c>
       <c r="E122" s="10" t="inlineStr">
         <is>
-          <t>감귤류, 버가못껍질, / 광독성을 유발하는 버갑텐 프리</t>
+          <t>감귤류, 버가못껍질 · 광독성을 유발하는 버갑텐 프리</t>
         </is>
       </c>
       <c r="F122" s="10" t="inlineStr">
@@ -12075,7 +12075,7 @@
       </c>
       <c r="E131" s="25" t="inlineStr">
         <is>
-          <t>카모마일 꽃 인퓨즈오일, / 캐모마일꽃의 유효성분 함유</t>
+          <t>카모마일 꽃 인퓨즈오일 · 캐모마일꽃의 유효성분 함유</t>
         </is>
       </c>
       <c r="F131" s="25" t="inlineStr">
@@ -12139,12 +12139,12 @@
       </c>
       <c r="E133" s="25" t="inlineStr">
         <is>
-          <t>물과 오일이 분리되지 않게 함, / 에코인증,</t>
+          <t>물과 오일이 분리되지 않게 함 · 에코인증</t>
         </is>
       </c>
       <c r="F133" s="25" t="inlineStr">
         <is>
-          <t>올리브유화왁스4g / (빠른 유화, 점도를 원할시)</t>
+          <t>올리브유화왁스4g · (빠른 유화, 점도를 원할시)</t>
         </is>
       </c>
     </row>
@@ -12171,7 +12171,7 @@
       </c>
       <c r="E134" s="25" t="inlineStr">
         <is>
-          <t>보조유화제, 에코인증 / 백탁현상을 줄이고 유화안정,</t>
+          <t>보조유화제, 에코인증 · 백탁현상을 줄이고 유화안정</t>
         </is>
       </c>
       <c r="F134" s="25" t="inlineStr">
@@ -12240,7 +12240,7 @@
       </c>
       <c r="F136" s="25" t="inlineStr">
         <is>
-          <t>히아루론산, 리피듀어, / 식물성글리세린</t>
+          <t>히아루론산, 리피듀어 · 식물성글리세린</t>
         </is>
       </c>
     </row>
@@ -12267,12 +12267,12 @@
       </c>
       <c r="E137" s="25" t="inlineStr">
         <is>
-          <t>자몽씨, 목단피, 황금 등 / 균번식 억제 복합성분</t>
+          <t>자몽씨, 목단피, 황금 등 · 균번식 억제 복합성분</t>
         </is>
       </c>
       <c r="F137" s="25" t="inlineStr">
         <is>
-          <t>수용성 천연 방부제, / 나트로 틱스의 경우(2g, 워터는 67g 넣어주세요.)</t>
+          <t>수용성 천연 방부제 · 나트로 틱스의 경우(2g, 워터는 67g 넣어주세요.)</t>
         </is>
       </c>
     </row>
@@ -12304,7 +12304,7 @@
       </c>
       <c r="F138" s="25" t="inlineStr">
         <is>
-          <t>캐모마일, 병풀, / 카렌듈라, 황금추출물</t>
+          <t>캐모마일, 병풀 · 카렌듈라, 황금추출물</t>
         </is>
       </c>
     </row>
@@ -12536,7 +12536,7 @@
       </c>
       <c r="F149" s="10" t="inlineStr">
         <is>
-          <t>포도씨오일, / 해바라기오일, 아몬드오일 등 / 가벼운 오일</t>
+          <t>포도씨오일 · 해바라기오일, 아몬드오일 등 · 가벼운 오일</t>
         </is>
       </c>
     </row>
@@ -12563,10 +12563,10 @@
       </c>
       <c r="E150" s="10" t="inlineStr">
         <is>
-          <t>저점도, 에코인증. 올리브오일에서 유래, / 오일과 물이 분리저지</t>
-        </is>
-      </c>
-      <c r="F150" s="10" t="n"/>
+          <t>저점도, 에코인증. 올리브오일에서 유래 · 오일과 물이 분리저지</t>
+        </is>
+      </c>
+      <c r="F150" s="10" t="inlineStr"/>
     </row>
     <row r="151" ht="32" customHeight="1">
       <c r="A151" s="10" t="inlineStr">
@@ -12628,7 +12628,7 @@
       </c>
       <c r="F152" s="10" t="inlineStr">
         <is>
-          <t>프리미엄 / 녹차워터</t>
+          <t>프리미엄 · 녹차워터</t>
         </is>
       </c>
     </row>
@@ -12660,7 +12660,7 @@
       </c>
       <c r="F153" s="10" t="inlineStr">
         <is>
-          <t>히아루론산, / 리피듀어, 식물성글리세린</t>
+          <t>히아루론산 · 리피듀어, 식물성글리세린</t>
         </is>
       </c>
     </row>
@@ -12687,7 +12687,7 @@
       </c>
       <c r="E154" s="10" t="inlineStr">
         <is>
-          <t>저온 감압, 성분 파괴 최소. / 폴리페놀 풍부</t>
+          <t>저온 감압, 성분 파괴 최소. · 폴리페놀 풍부</t>
         </is>
       </c>
       <c r="F154" s="10" t="inlineStr">
@@ -12783,7 +12783,7 @@
       </c>
       <c r="E157" s="10" t="inlineStr">
         <is>
-          <t>감귤류, 버가못껍질, / 광독성을 유발하는 버갑텐 프리</t>
+          <t>감귤류, 버가못껍질 · 광독성을 유발하는 버갑텐 프리</t>
         </is>
       </c>
       <c r="F157" s="10" t="inlineStr">
@@ -12971,12 +12971,12 @@
       </c>
       <c r="E168" s="25" t="inlineStr">
         <is>
-          <t>대마씨오일.피부정화, / 풍부한 필수지방산 함유</t>
+          <t>대마씨오일.피부정화 · 풍부한 필수지방산 함유</t>
         </is>
       </c>
       <c r="F168" s="25" t="inlineStr">
         <is>
-          <t>아르간오일, / 마카다미아넛오일</t>
+          <t>아르간오일 · 마카다미아넛오일</t>
         </is>
       </c>
     </row>
@@ -13003,7 +13003,7 @@
       </c>
       <c r="E169" s="25" t="inlineStr">
         <is>
-          <t>리놀렌산풍부, / 주름노화관리 도움</t>
+          <t>리놀렌산풍부 · 주름노화관리 도움</t>
         </is>
       </c>
       <c r="F169" s="25" t="inlineStr">
@@ -13035,12 +13035,12 @@
       </c>
       <c r="E170" s="25" t="inlineStr">
         <is>
-          <t>에코인증, / 물과 오일이 분리되지 않게 함</t>
+          <t>에코인증 · 물과 오일이 분리되지 않게 함</t>
         </is>
       </c>
       <c r="F170" s="25" t="inlineStr">
         <is>
-          <t>올리브유화왁스4g / (빠른 유화, 점도를 원할시)</t>
+          <t>올리브유화왁스4g · (빠른 유화, 점도를 원할시)</t>
         </is>
       </c>
     </row>
@@ -13067,7 +13067,7 @@
       </c>
       <c r="E171" s="25" t="inlineStr">
         <is>
-          <t>보조유화제, 에코인증 / 백탁현상 줄이고 유화안정</t>
+          <t>보조유화제, 에코인증 · 백탁현상 줄이고 유화안정</t>
         </is>
       </c>
       <c r="F171" s="25" t="inlineStr">
@@ -13163,12 +13163,12 @@
       </c>
       <c r="E174" s="25" t="inlineStr">
         <is>
-          <t>천연유래복합, / 균번식 억제제</t>
+          <t>천연유래복합 · 균번식 억제제</t>
         </is>
       </c>
       <c r="F174" s="25" t="inlineStr">
         <is>
-          <t>수용성보존제, / 나트로틱스2g(워터 67g으로 줄이기)</t>
+          <t>수용성보존제 · 나트로틱스2g(워터 67g으로 줄이기)</t>
         </is>
       </c>
     </row>
@@ -13230,7 +13230,7 @@
           <t>피부톤을 밝고 매끄럽게 하는데 도움</t>
         </is>
       </c>
-      <c r="F176" s="25" t="n"/>
+      <c r="F176" s="25" t="inlineStr"/>
     </row>
     <row r="177" ht="32" customHeight="1">
       <c r="A177" s="25" t="inlineStr">
@@ -13443,7 +13443,7 @@
           <t>피부트러블에 좋은 8종약재를 유효성분을 오일 우려냄.</t>
         </is>
       </c>
-      <c r="F187" s="10" t="n"/>
+      <c r="F187" s="10" t="inlineStr"/>
     </row>
     <row r="188" ht="48" customHeight="1">
       <c r="A188" s="10" t="inlineStr">
@@ -13468,16 +13468,16 @@
       </c>
       <c r="E188" s="10" t="inlineStr">
         <is>
-          <t>에코인증. 올리브오일에서 유래, / 오일과 물이 분리 저지.</t>
+          <t>에코인증. 올리브오일에서 유래 · 오일과 물이 분리 저지.</t>
         </is>
       </c>
       <c r="F188" s="10" t="inlineStr">
         <is>
-          <t>올리브유화왁스4g / (빠른 유화, 점도를 원할시)</t>
-        </is>
-      </c>
-    </row>
-    <row r="189" ht="48" customHeight="1">
+          <t>올리브유화왁스4g · (빠른 유화, 점도를 원할시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="32" customHeight="1">
       <c r="A189" s="10" t="inlineStr">
         <is>
           <t>올리왁스LC</t>
@@ -13500,7 +13500,7 @@
       </c>
       <c r="E189" s="10" t="inlineStr">
         <is>
-          <t>에코인증, 올리브유화왁스 보조, / 백탁현상 줄이고 유화 안정.</t>
+          <t>에코인증, 올리브유화왁스 보조 · 백탁현상 줄이고 유화 안정.</t>
         </is>
       </c>
       <c r="F189" s="10" t="inlineStr">
@@ -13564,7 +13564,7 @@
       </c>
       <c r="E191" s="10" t="inlineStr">
         <is>
-          <t>샴푸베이스에 이미 있지만 추가 보습을 원하면 모발 보습제로 넣어주세요. / 모발, 두피 보습제, / 좀더 모발을 부드럽게, 많은 양을 넣을 경우 점도가 묽어짐.</t>
+          <t>샴푸베이스에 이미 있지만 추가 보습을 원하면 모발 보습제로 넣어주세요. · 모발, 두피 보습제 · 좀더 모발을 부드럽게, 많은 양을 넣을 경우 점도가 묽어짐.</t>
         </is>
       </c>
       <c r="F191" s="10" t="inlineStr">
@@ -13596,12 +13596,12 @@
       </c>
       <c r="E192" s="10" t="inlineStr">
         <is>
-          <t>비타민성분이 함유된 펩타이드, / 화이트 원료.</t>
+          <t>비타민성분이 함유된 펩타이드 · 화이트 원료.</t>
         </is>
       </c>
       <c r="F192" s="10" t="inlineStr">
         <is>
-          <t>노화주름 관리를 원하면 EGF, FGF로 / 대체가능</t>
+          <t>노화주름 관리를 원하면 EGF, FGF로 · 대체가능</t>
         </is>
       </c>
     </row>
@@ -13665,7 +13665,7 @@
       </c>
       <c r="F194" s="10" t="inlineStr">
         <is>
-          <t>1,2-헥산디올2g / (로즈워터의 양을 64g으로 줄여주세요.)</t>
+          <t>1,2-헥산디올2g · (로즈워터의 양을 64g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -13884,7 +13884,7 @@
       </c>
       <c r="E205" s="25" t="inlineStr">
         <is>
-          <t>제주산 발효 마유, / 마유 중 비중이 가벼운 부분 , / 팔마톨레익산 등 불포화지방산 풍부, / 특이취 거의 없음</t>
+          <t>제주산 발효 마유 · 마유 중 비중이 가벼운 부분 · 팔마톨레익산 등 불포화지방산 풍부 · 특이취 거의 없음</t>
         </is>
       </c>
       <c r="F205" s="25" t="inlineStr">
@@ -13916,12 +13916,12 @@
       </c>
       <c r="E206" s="25" t="inlineStr">
         <is>
-          <t>에코인증. 올리브오일에서 유래 / 오일과 물이 분리 저지</t>
+          <t>에코인증. 올리브오일에서 유래 · 오일과 물이 분리 저지</t>
         </is>
       </c>
       <c r="F206" s="25" t="inlineStr">
         <is>
-          <t>올리브유화왁스4g / (빠른 유화, 점도를 원할시)</t>
+          <t>올리브유화왁스4g · (빠른 유화, 점도를 원할시)</t>
         </is>
       </c>
     </row>
@@ -13948,7 +13948,7 @@
       </c>
       <c r="E207" s="25" t="inlineStr">
         <is>
-          <t>에코인증, 올리브유화왁스 보조 / 백탁현상 줄이고 유화 안정</t>
+          <t>에코인증, 올리브유화왁스 보조 · 백탁현상 줄이고 유화 안정</t>
         </is>
       </c>
       <c r="F207" s="25" t="inlineStr">
@@ -13980,7 +13980,7 @@
       </c>
       <c r="E208" s="25" t="inlineStr">
         <is>
-          <t>순수한 물 , / 완성품의 색을 고르게.</t>
+          <t>순수한 물 · 완성품의 색을 고르게.</t>
         </is>
       </c>
       <c r="F208" s="25" t="inlineStr">
@@ -14044,10 +14044,10 @@
       </c>
       <c r="E210" s="25" t="inlineStr">
         <is>
-          <t>점증제. / 양을 지켜주세요. / 계량스푼 작은 쪽 깍아서 한개^ / 많은 양이 들어가면 사용시 미끌거림</t>
-        </is>
-      </c>
-      <c r="F210" s="25" t="n"/>
+          <t>점증제. · 양을 지켜주세요. · 계량스푼 작은 쪽 깍아서 한개^ · 많은 양이 들어가면 사용시 미끌거림</t>
+        </is>
+      </c>
+      <c r="F210" s="25" t="inlineStr"/>
     </row>
     <row r="211" ht="16" customHeight="1">
       <c r="A211" s="25" t="inlineStr">
@@ -14104,7 +14104,7 @@
       </c>
       <c r="E212" s="25" t="inlineStr">
         <is>
-          <t>장미향 나는 제라늄, 균형의 오일 / 피지균형 등 모든 피부</t>
+          <t>장미향 나는 제라늄, 균형의 오일 · 피지균형 등 모든 피부</t>
         </is>
       </c>
       <c r="F212" s="25" t="inlineStr">
@@ -14273,12 +14273,12 @@
       </c>
       <c r="E221" s="10" t="inlineStr">
         <is>
-          <t>에코인증, / 올리브오일유래, 보습, 점증</t>
+          <t>에코인증 · 올리브오일유래, 보습, 점증</t>
         </is>
       </c>
       <c r="F221" s="10" t="inlineStr">
         <is>
-          <t>올리브유화왁스4g / (빠른 유화, 점도를 원할시)</t>
+          <t>올리브유화왁스4g · (빠른 유화, 점도를 원할시)</t>
         </is>
       </c>
     </row>
@@ -14310,7 +14310,7 @@
       </c>
       <c r="F222" s="10" t="inlineStr">
         <is>
-          <t>원하는 / 플로럴 워터</t>
+          <t>원하는 · 플로럴 워터</t>
         </is>
       </c>
     </row>
@@ -14342,7 +14342,7 @@
       </c>
       <c r="F223" s="10" t="inlineStr">
         <is>
-          <t>인삼줄기세포, / 장미줄기세포 등</t>
+          <t>인삼줄기세포 · 장미줄기세포 등</t>
         </is>
       </c>
     </row>
@@ -14374,7 +14374,7 @@
       </c>
       <c r="F224" s="10" t="inlineStr">
         <is>
-          <t>낫또모이스트, / 판테놀, / 리피듀어, / 히아루론산 등</t>
+          <t>낫또모이스트 · 판테놀 · 리피듀어 · 히아루론산 등</t>
         </is>
       </c>
     </row>
@@ -14401,7 +14401,7 @@
       </c>
       <c r="E225" s="10" t="inlineStr">
         <is>
-          <t>오일, 에코인증, / 미백 트러블진정 성분 / Candeia Tree에서 추출</t>
+          <t>오일, 에코인증 · 미백 트러블진정 성분 · Candeia Tree에서 추출</t>
         </is>
       </c>
       <c r="F225" s="10" t="inlineStr">
@@ -14438,7 +14438,7 @@
       </c>
       <c r="F226" s="10" t="inlineStr">
         <is>
-          <t>1,2-헥산디올2g / (네롤리워터의 양을 84g으로 줄여주세요.)</t>
+          <t>1,2-헥산디올2g · (네롤리워터의 양을 84g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -14607,7 +14607,7 @@
       </c>
       <c r="E236" s="25" t="inlineStr">
         <is>
-          <t>모유에 들어있는 라우릭산이 / 자연식품 중에서는 가장 많이 들어있음. 달콤한 향</t>
+          <t>모유에 들어있는 라우릭산이 · 자연식품 중에서는 가장 많이 들어있음. 달콤한 향</t>
         </is>
       </c>
       <c r="F236" s="25" t="inlineStr">
@@ -14644,7 +14644,7 @@
       </c>
       <c r="F237" s="25" t="inlineStr">
         <is>
-          <t>올리브유화왁스4g / (빠른 유화, 점도를 원할시)</t>
+          <t>올리브유화왁스4g · (빠른 유화, 점도를 원할시)</t>
         </is>
       </c>
     </row>
@@ -14671,12 +14671,12 @@
       </c>
       <c r="E238" s="25" t="inlineStr">
         <is>
-          <t>순수한 물 , / 완성품의 색을 고르게.</t>
+          <t>순수한 물 · 완성품의 색을 고르게.</t>
         </is>
       </c>
       <c r="F238" s="25" t="inlineStr">
         <is>
-          <t>라벤더워터, / 로즈워터 등</t>
+          <t>라벤더워터 · 로즈워터 등</t>
         </is>
       </c>
     </row>
@@ -15003,7 +15003,7 @@
       </c>
       <c r="F252" s="10" t="inlineStr">
         <is>
-          <t>올리브유화왁스4g / (빠른 유화, 점도를 원할시)</t>
+          <t>올리브유화왁스4g · (빠른 유화, 점도를 원할시)</t>
         </is>
       </c>
     </row>
@@ -15062,12 +15062,12 @@
       </c>
       <c r="E254" s="10" t="inlineStr">
         <is>
-          <t>비타민B5, / 보습</t>
+          <t>비타민B5 · 보습</t>
         </is>
       </c>
       <c r="F254" s="10" t="inlineStr">
         <is>
-          <t>히아루론산, / 글리세린 등</t>
+          <t>히아루론산 · 글리세린 등</t>
         </is>
       </c>
     </row>
@@ -15094,12 +15094,12 @@
       </c>
       <c r="E255" s="10" t="inlineStr">
         <is>
-          <t>수분, / 자체점증.</t>
+          <t>수분 · 자체점증.</t>
         </is>
       </c>
       <c r="F255" s="10" t="inlineStr">
         <is>
-          <t>로즈플라워겔, / 네롤리플라워겔</t>
+          <t>로즈플라워겔 · 네롤리플라워겔</t>
         </is>
       </c>
     </row>
@@ -15131,7 +15131,7 @@
       </c>
       <c r="F256" s="10" t="inlineStr">
         <is>
-          <t>1,2-헥산디올2g / (네롤리워터의 양을 22g으로 줄여주세요.)</t>
+          <t>1,2-헥산디올2g · (네롤리워터의 양을 22g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -15302,7 +15302,7 @@
           <t>자초, 당귀 등 피부 트러블에 좋은 약재를 식물성 오일에 담궈 유효성분을 우려냄</t>
         </is>
       </c>
-      <c r="F266" s="25" t="n"/>
+      <c r="F266" s="25" t="inlineStr"/>
     </row>
     <row r="267" ht="32" customHeight="1">
       <c r="A267" s="25" t="inlineStr">
@@ -15327,10 +15327,10 @@
       </c>
       <c r="E267" s="25" t="inlineStr">
         <is>
-          <t>해바라기오일로 만든 / 천연 바세린. 고보습.</t>
-        </is>
-      </c>
-      <c r="F267" s="25" t="n"/>
+          <t>해바라기오일로 만든 · 천연 바세린. 고보습.</t>
+        </is>
+      </c>
+      <c r="F267" s="25" t="inlineStr"/>
     </row>
     <row r="268" ht="32" customHeight="1">
       <c r="A268" s="25" t="inlineStr">
@@ -15355,10 +15355,10 @@
       </c>
       <c r="E268" s="25" t="inlineStr">
         <is>
-          <t>올리뱀 800, / 끈적임 없고 유분감없는 유화제</t>
-        </is>
-      </c>
-      <c r="F268" s="25" t="n"/>
+          <t>올리뱀 800 · 끈적임 없고 유분감없는 유화제</t>
+        </is>
+      </c>
+      <c r="F268" s="25" t="inlineStr"/>
     </row>
     <row r="269" ht="32" customHeight="1">
       <c r="A269" s="25" t="inlineStr">
@@ -15450,7 +15450,7 @@
           <t>피부 수분 장벽</t>
         </is>
       </c>
-      <c r="F271" s="25" t="n"/>
+      <c r="F271" s="25" t="inlineStr"/>
     </row>
     <row r="272" ht="64" customHeight="1">
       <c r="A272" s="25" t="inlineStr">
@@ -15480,7 +15480,7 @@
       </c>
       <c r="F272" s="25" t="inlineStr">
         <is>
-          <t>1,2-헥산디올2g / (로먼캐모마일워터의 양을 70g으로 줄여주세요.)</t>
+          <t>1,2-헥산디올2g · (로먼캐모마일워터의 양을 70g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -15512,7 +15512,7 @@
       </c>
       <c r="F273" s="25" t="inlineStr">
         <is>
-          <t>원하는 / 에센셜오일</t>
+          <t>원하는 · 에센셜오일</t>
         </is>
       </c>
     </row>
@@ -15661,7 +15661,7 @@
       </c>
       <c r="E282" s="10" t="inlineStr">
         <is>
-          <t>들장미 씨앗추출, / 비타민 풍부</t>
+          <t>들장미 씨앗추출 · 비타민 풍부</t>
         </is>
       </c>
       <c r="F282" s="10" t="inlineStr">
@@ -15693,12 +15693,12 @@
       </c>
       <c r="E283" s="10" t="inlineStr">
         <is>
-          <t>에코인증, / 물과 오일 분리저지</t>
+          <t>에코인증 · 물과 오일 분리저지</t>
         </is>
       </c>
       <c r="F283" s="10" t="inlineStr">
         <is>
-          <t>올리브유화왁스4g / (빠른 유화, 점도를 원할시)</t>
+          <t>올리브유화왁스4g · (빠른 유화, 점도를 원할시)</t>
         </is>
       </c>
     </row>
@@ -15757,12 +15757,12 @@
       </c>
       <c r="E285" s="10" t="inlineStr">
         <is>
-          <t>불가리아 로즈워터, / 피부진정, 보습</t>
+          <t>불가리아 로즈워터 · 피부진정, 보습</t>
         </is>
       </c>
       <c r="F285" s="10" t="inlineStr">
         <is>
-          <t>원하는 / 플로럴워터</t>
+          <t>원하는 · 플로럴워터</t>
         </is>
       </c>
     </row>
@@ -15794,7 +15794,7 @@
       </c>
       <c r="F286" s="10" t="inlineStr">
         <is>
-          <t>로즈 / 플라워겔, / 허브누리 / 베라겔</t>
+          <t>로즈 · 플라워겔 · 허브누리 · 베라겔</t>
         </is>
       </c>
     </row>
@@ -15826,7 +15826,7 @@
       </c>
       <c r="F287" s="10" t="inlineStr">
         <is>
-          <t>화이트 / 펩타이드</t>
+          <t>화이트 · 펩타이드</t>
         </is>
       </c>
     </row>
@@ -15885,10 +15885,10 @@
       </c>
       <c r="E289" s="10" t="inlineStr">
         <is>
-          <t>네롤리, 일랑일랑, 버가못FCF, / 프랑킨센스EO 블렌딩</t>
-        </is>
-      </c>
-      <c r="F289" s="10" t="n"/>
+          <t>네롤리, 일랑일랑, 버가못FCF · 프랑킨센스EO 블렌딩</t>
+        </is>
+      </c>
+      <c r="F289" s="10" t="inlineStr"/>
     </row>
     <row r="290" ht="64" customHeight="1">
       <c r="A290" s="10" t="inlineStr">
@@ -15918,7 +15918,7 @@
       </c>
       <c r="F290" s="10" t="inlineStr">
         <is>
-          <t>1,2-헥산디올2g / (로즈워터의양을 65g으로 늘려주세요.)</t>
+          <t>1,2-헥산디올2g · (로즈워터의양을 65g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
@@ -16116,7 +16116,7 @@
       </c>
       <c r="F301" s="25" t="inlineStr">
         <is>
-          <t>시어버터, / 망고버터</t>
+          <t>시어버터 · 망고버터</t>
         </is>
       </c>
     </row>
@@ -16143,12 +16143,12 @@
       </c>
       <c r="E302" s="25" t="inlineStr">
         <is>
-          <t>에코인증, / 물/오일분리 저지</t>
+          <t>에코인증 · 물 · 오일분리 저지</t>
         </is>
       </c>
       <c r="F302" s="25" t="inlineStr">
         <is>
-          <t>올리브유화왁스4g / (빠른 유화, 점도를 원할시)</t>
+          <t>올리브유화왁스4g · (빠른 유화, 점도를 원할시)</t>
         </is>
       </c>
     </row>
@@ -16175,7 +16175,7 @@
       </c>
       <c r="E303" s="25" t="inlineStr">
         <is>
-          <t>유화 보조제, / 백탁 현상 완화</t>
+          <t>유화 보조제 · 백탁 현상 완화</t>
         </is>
       </c>
       <c r="F303" s="25" t="inlineStr">
@@ -16239,10 +16239,10 @@
       </c>
       <c r="E305" s="25" t="inlineStr">
         <is>
-          <t>점증제 / 계량스푼 작은 쪽 깍아서 한번</t>
-        </is>
-      </c>
-      <c r="F305" s="25" t="n"/>
+          <t>점증제 · 계량스푼 작은 쪽 깍아서 한번</t>
+        </is>
+      </c>
+      <c r="F305" s="25" t="inlineStr"/>
     </row>
     <row r="306" ht="32" customHeight="1">
       <c r="A306" s="25" t="inlineStr">
@@ -16267,7 +16267,7 @@
       </c>
       <c r="E306" s="25" t="inlineStr">
         <is>
-          <t>5차 필터링, / UV살균처리 정제수</t>
+          <t>5차 필터링 · UV살균처리 정제수</t>
         </is>
       </c>
       <c r="F306" s="25" t="inlineStr">
@@ -16299,10 +16299,10 @@
       </c>
       <c r="E307" s="25" t="inlineStr">
         <is>
-          <t>로즈마리, 캐모마일, 녹차, / 병풀, 감초, 호장근, 황금 / 복합추출물</t>
-        </is>
-      </c>
-      <c r="F307" s="25" t="n"/>
+          <t>로즈마리, 캐모마일, 녹차 · 병풀, 감초, 호장근, 황금 · 복합추출물</t>
+        </is>
+      </c>
+      <c r="F307" s="25" t="inlineStr"/>
     </row>
     <row r="308" ht="32" customHeight="1">
       <c r="A308" s="25" t="inlineStr">
@@ -16332,7 +16332,7 @@
       </c>
       <c r="F308" s="25" t="inlineStr">
         <is>
-          <t>스쿠알란, / 보르피린</t>
+          <t>스쿠알란 · 보르피린</t>
         </is>
       </c>
     </row>
@@ -16396,7 +16396,7 @@
       </c>
       <c r="F310" s="25" t="inlineStr">
         <is>
-          <t>1,2-헥산디올2g / (정제수의 양을 58g으로 줄여주세요.)</t>
+          <t>1,2-헥산디올2g · (정제수의 양을 58g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -16423,12 +16423,12 @@
       </c>
       <c r="E311" s="25" t="inlineStr">
         <is>
-          <t>라벤더. 만다린 / 로먼캐모마일 에센셜오일, / 민감피부를 위한 블렌딩</t>
+          <t>라벤더. 만다린 · 로먼캐모마일 에센셜오일 · 민감피부를 위한 블렌딩</t>
         </is>
       </c>
       <c r="F311" s="25" t="inlineStr">
         <is>
-          <t>원하는 / 에센셜오일</t>
+          <t>원하는 · 에센셜오일</t>
         </is>
       </c>
     </row>
@@ -16578,7 +16578,7 @@
       </c>
       <c r="E320" s="10" t="inlineStr">
         <is>
-          <t>자외선차단, 커버력, 광채에 / 에센스효과까지 올인원. / 레시피는 여기 참고</t>
+          <t>자외선차단, 커버력, 광채에 · 에센스효과까지 올인원. · 레시피는 여기 참고</t>
         </is>
       </c>
       <c r="F320" s="10" t="inlineStr">
@@ -16789,7 +16789,7 @@
           <t>쌀눈, 비타민B, E 등 함유</t>
         </is>
       </c>
-      <c r="F331" s="25" t="n"/>
+      <c r="F331" s="25" t="inlineStr"/>
     </row>
     <row r="332" ht="48" customHeight="1">
       <c r="A332" s="25" t="inlineStr">
@@ -16814,12 +16814,12 @@
       </c>
       <c r="E332" s="25" t="inlineStr">
         <is>
-          <t>에코인증, / 물/오일분리 저지</t>
+          <t>에코인증 · 물 · 오일분리 저지</t>
         </is>
       </c>
       <c r="F332" s="25" t="inlineStr">
         <is>
-          <t>올리브유화왁스4g / (빠른 유화, 점도를 원할시)</t>
+          <t>올리브유화왁스4g · (빠른 유화, 점도를 원할시)</t>
         </is>
       </c>
     </row>
@@ -16846,7 +16846,7 @@
       </c>
       <c r="E333" s="25" t="inlineStr">
         <is>
-          <t>유화안정, / 백탁 현상 완화</t>
+          <t>유화안정 · 백탁 현상 완화</t>
         </is>
       </c>
       <c r="F333" s="25" t="inlineStr">
@@ -16883,7 +16883,7 @@
       </c>
       <c r="F334" s="25" t="inlineStr">
         <is>
-          <t>정제수, / 원하는 워터</t>
+          <t>정제수 · 원하는 워터</t>
         </is>
       </c>
     </row>
@@ -16942,7 +16942,7 @@
       </c>
       <c r="E336" s="25" t="inlineStr">
         <is>
-          <t>퀴노아, 오트밀, 쌀 3가지 복합 프로테인, / 거칠어진 피부에 도움</t>
+          <t>퀴노아, 오트밀, 쌀 3가지 복합 프로테인 · 거칠어진 피부에 도움</t>
         </is>
       </c>
       <c r="F336" s="25" t="inlineStr">
@@ -16974,7 +16974,7 @@
       </c>
       <c r="E337" s="25" t="inlineStr">
         <is>
-          <t>식약처 미백인증 / 멜라닌 색소 전단계 억제 도움과량 사용시 자극,</t>
+          <t>식약처 미백인증 · 멜라닌 색소 전단계 억제 도움과량 사용시 자극</t>
         </is>
       </c>
       <c r="F337" s="25" t="inlineStr">
@@ -17043,7 +17043,7 @@
       </c>
       <c r="F339" s="25" t="inlineStr">
         <is>
-          <t>1,2-헥산디올2g / (네롤리워터의 양을 57g으로 줄여주세요.)</t>
+          <t>1,2-헥산디올2g · (네롤리워터의 양을 57g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -17231,7 +17231,7 @@
       </c>
       <c r="F349" s="10" t="inlineStr">
         <is>
-          <t>로즈힙, / 아르간오일등</t>
+          <t>로즈힙 · 아르간오일등</t>
         </is>
       </c>
     </row>
@@ -17258,7 +17258,7 @@
       </c>
       <c r="E350" s="10" t="inlineStr">
         <is>
-          <t>고보습, / 망고씨에서 유래 식물성 버터</t>
+          <t>고보습 · 망고씨에서 유래 식물성 버터</t>
         </is>
       </c>
       <c r="F350" s="10" t="inlineStr">
@@ -17290,12 +17290,12 @@
       </c>
       <c r="E351" s="10" t="inlineStr">
         <is>
-          <t>물과 오일 분리 저지, / 주유화제</t>
+          <t>물과 오일 분리 저지 · 주유화제</t>
         </is>
       </c>
       <c r="F351" s="10" t="inlineStr">
         <is>
-          <t>올리브유화왁스4g / (빠른 유화, 점도를 원할시)</t>
+          <t>올리브유화왁스4g · (빠른 유화, 점도를 원할시)</t>
         </is>
       </c>
     </row>
@@ -17391,7 +17391,7 @@
       </c>
       <c r="F354" s="10" t="inlineStr">
         <is>
-          <t>스쿠알란, / 보르피린</t>
+          <t>스쿠알란 · 보르피린</t>
         </is>
       </c>
     </row>
@@ -17418,10 +17418,10 @@
       </c>
       <c r="E355" s="10" t="inlineStr">
         <is>
-          <t>진정 수분공급. / 참마, 흰목이버섯, 미역, 알로에 / 복합추출성분</t>
-        </is>
-      </c>
-      <c r="F355" s="10" t="n"/>
+          <t>진정 수분공급. · 참마, 흰목이버섯, 미역, 알로에 · 복합추출성분</t>
+        </is>
+      </c>
+      <c r="F355" s="10" t="inlineStr"/>
     </row>
     <row r="356" ht="16" customHeight="1">
       <c r="A356" s="10" t="inlineStr">
@@ -17483,7 +17483,7 @@
       </c>
       <c r="F357" s="10" t="inlineStr">
         <is>
-          <t>천연한방보존제1g / (네롤리워터의 양을 59g으로 늘려주세요.)</t>
+          <t>천연한방보존제1g · (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
@@ -17510,7 +17510,7 @@
       </c>
       <c r="E358" s="10" t="inlineStr">
         <is>
-          <t>은은한 벚꽃향, / 프탈레이트 프리</t>
+          <t>은은한 벚꽃향 · 프탈레이트 프리</t>
         </is>
       </c>
       <c r="F358" s="10" t="inlineStr">
@@ -17646,7 +17646,7 @@
       </c>
       <c r="E367" s="25" t="inlineStr">
         <is>
-          <t>피지성분과 비슷, / 빠른흡수</t>
+          <t>피지성분과 비슷 · 빠른흡수</t>
         </is>
       </c>
       <c r="F367" s="25" t="inlineStr">
@@ -17779,7 +17779,7 @@
       </c>
       <c r="F371" s="25" t="inlineStr">
         <is>
-          <t>피부타입별 워터 / 트러블, 남성-편백 / 민감, 베이비-캐모마일 / 노화-로즈 / 남성-로즈마리</t>
+          <t>피부타입별 워터 · 트러블, 남성-편백 · 민감, 베이비-캐모마일 · 노화-로즈 · 남성-로즈마리</t>
         </is>
       </c>
     </row>
@@ -17806,12 +17806,12 @@
       </c>
       <c r="E372" s="25" t="inlineStr">
         <is>
-          <t>불가리아 다마스크 / 장미수 함유 / 점증, 수분공급, 진정</t>
+          <t>불가리아 다마스크 · 장미수 함유 · 점증, 수분공급, 진정</t>
         </is>
       </c>
       <c r="F372" s="25" t="inlineStr">
         <is>
-          <t>허브누리 / 알로에베라겔, / 네롤리플라워젤</t>
+          <t>허브누리 · 알로에베라겔 · 네롤리플라워젤</t>
         </is>
       </c>
     </row>
@@ -17838,12 +17838,12 @@
       </c>
       <c r="E373" s="25" t="inlineStr">
         <is>
-          <t>비타민류가 다량 함유 되어있는 7가지 / 유기농 과일, 야채 추출물</t>
+          <t>비타민류가 다량 함유 되어있는 7가지 · 유기농 과일, 야채 추출물</t>
         </is>
       </c>
       <c r="F373" s="25" t="inlineStr">
         <is>
-          <t>유기농 / 브라이트닝 / 솔루션</t>
+          <t>유기농 · 브라이트닝 · 솔루션</t>
         </is>
       </c>
     </row>
@@ -17875,7 +17875,7 @@
       </c>
       <c r="F374" s="25" t="inlineStr">
         <is>
-          <t>세라마이드, / 알란토인분말 사용시 0.2g</t>
+          <t>세라마이드 · 알란토인분말 사용시 0.2g</t>
         </is>
       </c>
     </row>
@@ -18083,7 +18083,7 @@
       </c>
       <c r="E385" s="10" t="inlineStr">
         <is>
-          <t>리놀렌산풍부, / 주름노화관리 도움</t>
+          <t>리놀렌산풍부 · 주름노화관리 도움</t>
         </is>
       </c>
       <c r="F385" s="10" t="inlineStr">
@@ -18115,7 +18115,7 @@
       </c>
       <c r="E386" s="10" t="inlineStr">
         <is>
-          <t>피지성분과 비슷, / 빠른흡수</t>
+          <t>피지성분과 비슷 · 빠른흡수</t>
         </is>
       </c>
       <c r="F386" s="10" t="inlineStr">
@@ -18150,7 +18150,7 @@
           <t>유화보조제</t>
         </is>
       </c>
-      <c r="F387" s="10" t="n"/>
+      <c r="F387" s="10" t="inlineStr"/>
     </row>
     <row r="388" ht="48" customHeight="1">
       <c r="A388" s="10" t="inlineStr">
@@ -18180,11 +18180,11 @@
       </c>
       <c r="F388" s="10" t="inlineStr">
         <is>
-          <t>올리브유화왁스4g / (빠른 유화, 점도를 원할시)</t>
-        </is>
-      </c>
-    </row>
-    <row r="389" ht="32" customHeight="1">
+          <t>올리브유화왁스4g · (빠른 유화, 점도를 원할시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="389" ht="16" customHeight="1">
       <c r="A389" s="10" t="inlineStr">
         <is>
           <t>GMS</t>
@@ -18207,10 +18207,10 @@
       </c>
       <c r="E389" s="10" t="inlineStr">
         <is>
-          <t>유화보조제, / 피부를 매끄럽게.</t>
-        </is>
-      </c>
-      <c r="F389" s="10" t="n"/>
+          <t>유화보조제 · 피부를 매끄럽게.</t>
+        </is>
+      </c>
+      <c r="F389" s="10" t="inlineStr"/>
     </row>
     <row r="390" ht="96" customHeight="1">
       <c r="A390" s="10" t="inlineStr">
@@ -18240,7 +18240,7 @@
       </c>
       <c r="F390" s="10" t="inlineStr">
         <is>
-          <t>피부타입별 워터 / 트러블, 남성-편백 / 민감, 베이비-캐모마일 / 노화-로즈 / 남성-로즈마리</t>
+          <t>피부타입별 워터 · 트러블, 남성-편백 · 민감, 베이비-캐모마일 · 노화-로즈 · 남성-로즈마리</t>
         </is>
       </c>
     </row>
@@ -18299,12 +18299,12 @@
       </c>
       <c r="E392" s="10" t="inlineStr">
         <is>
-          <t>불가리아 다마스크 / 장미수 함유 / 점증, 수분공급, 진정</t>
+          <t>불가리아 다마스크 · 장미수 함유 · 점증, 수분공급, 진정</t>
         </is>
       </c>
       <c r="F392" s="10" t="inlineStr">
         <is>
-          <t>허브누리 / 알로에베라겔, / 네롤리플라워젤</t>
+          <t>허브누리 · 알로에베라겔 · 네롤리플라워젤</t>
         </is>
       </c>
     </row>
@@ -18336,7 +18336,7 @@
       </c>
       <c r="F393" s="10" t="inlineStr">
         <is>
-          <t>스쿠알란, / 보르피린</t>
+          <t>스쿠알란 · 보르피린</t>
         </is>
       </c>
     </row>
@@ -18363,7 +18363,7 @@
       </c>
       <c r="E394" s="10" t="inlineStr">
         <is>
-          <t>락토바실러스 람노서스, 비피다발효용해물, 락토코쿠스발효용해물 / 3가지 유산균 복합 성분</t>
+          <t>락토바실러스 람노서스, 비피다발효용해물, 락토코쿠스발효용해물 · 3가지 유산균 복합 성분</t>
         </is>
       </c>
       <c r="F394" s="10" t="inlineStr">
@@ -18432,7 +18432,7 @@
       </c>
       <c r="F396" s="10" t="inlineStr">
         <is>
-          <t>로즈파워 / 블렌딩오일</t>
+          <t>로즈파워 · 블렌딩오일</t>
         </is>
       </c>
     </row>
@@ -18601,7 +18601,7 @@
       </c>
       <c r="E406" s="25" t="inlineStr">
         <is>
-          <t>피지성분과 비슷, / 빠른흡수</t>
+          <t>피지성분과 비슷 · 빠른흡수</t>
         </is>
       </c>
       <c r="F406" s="25" t="inlineStr">
@@ -18636,7 +18636,7 @@
           <t>유화안정, 보조</t>
         </is>
       </c>
-      <c r="F407" s="25" t="n"/>
+      <c r="F407" s="25" t="inlineStr"/>
     </row>
     <row r="408" ht="48" customHeight="1">
       <c r="A408" s="25" t="inlineStr">
@@ -18666,7 +18666,7 @@
       </c>
       <c r="F408" s="25" t="inlineStr">
         <is>
-          <t>올리브유화왁스4g / (빠른 유화, 점도를 원할시)</t>
+          <t>올리브유화왁스4g · (빠른 유화, 점도를 원할시)</t>
         </is>
       </c>
     </row>
@@ -18696,7 +18696,7 @@
           <t>유화안정, 보조, 보습</t>
         </is>
       </c>
-      <c r="F409" s="25" t="n"/>
+      <c r="F409" s="25" t="inlineStr"/>
     </row>
     <row r="410" ht="16" customHeight="1">
       <c r="A410" s="25" t="inlineStr">
@@ -18785,7 +18785,7 @@
       </c>
       <c r="E412" s="25" t="inlineStr">
         <is>
-          <t>불가리아 다마스크 장미수 함유 / 점증, 수분공급, 진정</t>
+          <t>불가리아 다마스크 장미수 함유 · 점증, 수분공급, 진정</t>
         </is>
       </c>
       <c r="F412" s="25" t="inlineStr">
@@ -18817,12 +18817,12 @@
       </c>
       <c r="E413" s="25" t="inlineStr">
         <is>
-          <t>비타민류가 다량 함유 되어있는 7가지 / 유기농 과일, 야채 추출물</t>
+          <t>비타민류가 다량 함유 되어있는 7가지 · 유기농 과일, 야채 추출물</t>
         </is>
       </c>
       <c r="F413" s="25" t="inlineStr">
         <is>
-          <t>유기농 / 브라이트닝 / 솔루션</t>
+          <t>유기농 · 브라이트닝 · 솔루션</t>
         </is>
       </c>
     </row>
@@ -18849,10 +18849,10 @@
       </c>
       <c r="E414" s="25" t="inlineStr">
         <is>
-          <t>피부 생기를 위해 엄선된 / 11가지 비타민 컴플렉스</t>
-        </is>
-      </c>
-      <c r="F414" s="25" t="n"/>
+          <t>피부 생기를 위해 엄선된 · 11가지 비타민 컴플렉스</t>
+        </is>
+      </c>
+      <c r="F414" s="25" t="inlineStr"/>
     </row>
     <row r="415" ht="64" customHeight="1">
       <c r="A415" s="25" t="inlineStr">
@@ -18882,7 +18882,7 @@
       </c>
       <c r="F415" s="25" t="inlineStr">
         <is>
-          <t>천연한방보존제1g / (네롤리워터를 52g으로 늘려주세요.)</t>
+          <t>천연한방보존제1g · (네롤리워터를 52g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
@@ -18914,7 +18914,7 @@
       </c>
       <c r="F416" s="25" t="inlineStr">
         <is>
-          <t>베베보 / 블렌딩오일</t>
+          <t>베베보 · 블렌딩오일</t>
         </is>
       </c>
     </row>
@@ -19061,12 +19061,12 @@
       </c>
       <c r="E424" s="10" t="inlineStr">
         <is>
-          <t>에코인증, / 물/오일분리 저지</t>
+          <t>에코인증 · 물 · 오일분리 저지</t>
         </is>
       </c>
       <c r="F424" s="10" t="inlineStr">
         <is>
-          <t>올리브유화왁스4g / (빠른 유화, 점도를 원할시)</t>
+          <t>올리브유화왁스4g · (빠른 유화, 점도를 원할시)</t>
         </is>
       </c>
     </row>
@@ -19134,7 +19134,7 @@
         </is>
       </c>
     </row>
-    <row r="427" ht="64" customHeight="1">
+    <row r="427" ht="48" customHeight="1">
       <c r="A427" s="10" t="inlineStr">
         <is>
           <t>프로바이오틱스 3</t>
@@ -19157,7 +19157,7 @@
       </c>
       <c r="E427" s="10" t="inlineStr">
         <is>
-          <t>락토바실러스 람노서스, / 비피다발효용해물, 락토코쿠스발효용해물 / 3가지 유산균 복합 성분</t>
+          <t>락토바실러스 람노서스 · 비피다발효용해물, 락토코쿠스발효용해물 · 3가지 유산균 복합 성분</t>
         </is>
       </c>
       <c r="F427" s="10" t="inlineStr">
@@ -19192,7 +19192,7 @@
           <t>로즈마리, 캐모마일, 녹차, 병풀, 감초, 호장근, 황금 복합추출물</t>
         </is>
       </c>
-      <c r="F428" s="10" t="n"/>
+      <c r="F428" s="10" t="inlineStr"/>
     </row>
     <row r="429" ht="16" customHeight="1">
       <c r="A429" s="10" t="inlineStr">
@@ -19249,12 +19249,12 @@
       </c>
       <c r="E430" s="10" t="inlineStr">
         <is>
-          <t>보습제이면서 / 균번식 억제</t>
+          <t>보습제이면서 · 균번식 억제</t>
         </is>
       </c>
       <c r="F430" s="10" t="inlineStr">
         <is>
-          <t>천연한방보존제1g / (네롤리워터의 양을 46g으로 늘려주세요.)</t>
+          <t>천연한방보존제1g · (네롤리워터의 양을 46g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
@@ -19390,7 +19390,7 @@
       </c>
       <c r="E439" s="25" t="inlineStr">
         <is>
-          <t>카모마일 꽃 인퓨즈오일, / 캐모마일꽃의 유효성분 함유</t>
+          <t>카모마일 꽃 인퓨즈오일 · 캐모마일꽃의 유효성분 함유</t>
         </is>
       </c>
       <c r="F439" s="25" t="inlineStr">
@@ -19454,12 +19454,12 @@
       </c>
       <c r="E441" s="25" t="inlineStr">
         <is>
-          <t>에코인증, / 물과 오일이 분리되지 않게 함</t>
+          <t>에코인증 · 물과 오일이 분리되지 않게 함</t>
         </is>
       </c>
       <c r="F441" s="25" t="inlineStr">
         <is>
-          <t>올리브유화왁스4g / (빠른 유화, 점도를 원할시)</t>
+          <t>올리브유화왁스4g · (빠른 유화, 점도를 원할시)</t>
         </is>
       </c>
     </row>
@@ -19486,7 +19486,7 @@
       </c>
       <c r="E442" s="25" t="inlineStr">
         <is>
-          <t>보조유화제, 에코인증 / 백탁현상을 줄이고 유화안정</t>
+          <t>보조유화제, 에코인증 · 백탁현상을 줄이고 유화안정</t>
         </is>
       </c>
       <c r="F442" s="25" t="inlineStr">
@@ -19518,7 +19518,7 @@
       </c>
       <c r="E443" s="25" t="inlineStr">
         <is>
-          <t>라벤더 꽃잎의 수용성 성분, / 증기 추출법하는 과정에서 나옴</t>
+          <t>라벤더 꽃잎의 수용성 성분 · 증기 추출법하는 과정에서 나옴</t>
         </is>
       </c>
       <c r="F443" s="25" t="inlineStr">
@@ -19555,7 +19555,7 @@
       </c>
       <c r="F444" s="25" t="inlineStr">
         <is>
-          <t>히아루론산, 리피듀어, / 식물성글리세린</t>
+          <t>히아루론산, 리피듀어 · 식물성글리세린</t>
         </is>
       </c>
     </row>
@@ -19582,12 +19582,12 @@
       </c>
       <c r="E445" s="25" t="inlineStr">
         <is>
-          <t>자몽씨, 목단피, 황금 등 / 균번식 억제 복합성분</t>
+          <t>자몽씨, 목단피, 황금 등 · 균번식 억제 복합성분</t>
         </is>
       </c>
       <c r="F445" s="25" t="inlineStr">
         <is>
-          <t>수용성 천연 방부제, / 나트로 틱스의 경우(2g, 워터는 67g 넣어주세요.)</t>
+          <t>수용성 천연 방부제 · 나트로 틱스의 경우(2g, 워터는 67g 넣어주세요.)</t>
         </is>
       </c>
     </row>
@@ -19619,7 +19619,7 @@
       </c>
       <c r="F446" s="25" t="inlineStr">
         <is>
-          <t>캐모마일, 병풀, / 카렌듈라, 황금추출물</t>
+          <t>캐모마일, 병풀 · 카렌듈라, 황금추출물</t>
         </is>
       </c>
     </row>
@@ -19845,10 +19845,10 @@
       </c>
       <c r="E457" s="10" t="inlineStr">
         <is>
-          <t>코코넛 유래, / 가볍고 빠른 흡수력</t>
-        </is>
-      </c>
-      <c r="F457" s="10" t="n"/>
+          <t>코코넛 유래 · 가볍고 빠른 흡수력</t>
+        </is>
+      </c>
+      <c r="F457" s="10" t="inlineStr"/>
     </row>
     <row r="458" ht="16" customHeight="1">
       <c r="A458" s="10" t="inlineStr">
@@ -19876,7 +19876,7 @@
           <t>유화 보조제</t>
         </is>
       </c>
-      <c r="F458" s="10" t="n"/>
+      <c r="F458" s="10" t="inlineStr"/>
     </row>
     <row r="459" ht="32" customHeight="1">
       <c r="A459" s="10" t="inlineStr">
@@ -19901,10 +19901,10 @@
       </c>
       <c r="E459" s="10" t="inlineStr">
         <is>
-          <t>유화제, 정전기 방지, / 물과 오일 섞임을 도와줌</t>
-        </is>
-      </c>
-      <c r="F459" s="10" t="n"/>
+          <t>유화제, 정전기 방지 · 물과 오일 섞임을 도와줌</t>
+        </is>
+      </c>
+      <c r="F459" s="10" t="inlineStr"/>
     </row>
     <row r="460" ht="32" customHeight="1">
       <c r="A460" s="10" t="inlineStr">
@@ -19932,7 +19932,7 @@
           <t>양이온계면활성제, 정전기 방지, 모발을 부드럽게</t>
         </is>
       </c>
-      <c r="F460" s="10" t="n"/>
+      <c r="F460" s="10" t="inlineStr"/>
     </row>
     <row r="461" ht="16" customHeight="1">
       <c r="A461" s="10" t="inlineStr">
@@ -19994,7 +19994,7 @@
       </c>
       <c r="F462" s="10" t="inlineStr">
         <is>
-          <t>프리미엄 / 녹차워터</t>
+          <t>프리미엄 · 녹차워터</t>
         </is>
       </c>
     </row>
@@ -20021,7 +20021,7 @@
       </c>
       <c r="E463" s="10" t="inlineStr">
         <is>
-          <t>퀴노아, 오트밀, 쌀 / 3가지 복합 프로테인</t>
+          <t>퀴노아, 오트밀, 쌀 · 3가지 복합 프로테인</t>
         </is>
       </c>
       <c r="F463" s="10" t="inlineStr">
@@ -20053,10 +20053,10 @@
       </c>
       <c r="E464" s="10" t="inlineStr">
         <is>
-          <t>단백질의 최소단위, / 17가지 아미노산</t>
-        </is>
-      </c>
-      <c r="F464" s="10" t="n"/>
+          <t>단백질의 최소단위 · 17가지 아미노산</t>
+        </is>
+      </c>
+      <c r="F464" s="10" t="inlineStr"/>
     </row>
     <row r="465" ht="64" customHeight="1">
       <c r="A465" s="10" t="inlineStr">
@@ -20086,7 +20086,7 @@
       </c>
       <c r="F465" s="10" t="inlineStr">
         <is>
-          <t>천연한방보존제1g / (네롤리워터의 양을 59g으로 늘려주세요.)</t>
+          <t>천연한방보존제1g · (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
@@ -20113,7 +20113,7 @@
       </c>
       <c r="E466" s="10" t="inlineStr">
         <is>
-          <t>바다의 이슬이란 뜻에서 유래, / 혈액순환에 도움</t>
+          <t>바다의 이슬이란 뜻에서 유래 · 혈액순환에 도움</t>
         </is>
       </c>
       <c r="F466" s="10" t="inlineStr">
@@ -20268,7 +20268,7 @@
       </c>
       <c r="E475" s="25" t="inlineStr">
         <is>
-          <t>보습성분,올레인산함유, / 서양에 올리브유~동양엔 동백유~</t>
+          <t>보습성분,올레인산함유 · 서양에 올리브유~동양엔 동백유</t>
         </is>
       </c>
       <c r="F475" s="25" t="inlineStr">
@@ -20300,12 +20300,12 @@
       </c>
       <c r="E476" s="25" t="inlineStr">
         <is>
-          <t>올레인산함유 동백과비슷, / 카테킨함유</t>
+          <t>올레인산함유 동백과비슷 · 카테킨함유</t>
         </is>
       </c>
       <c r="F476" s="25" t="inlineStr">
         <is>
-          <t>동백유, 호호바, / 아몬드, 마카다미아넛</t>
+          <t>동백유, 호호바 · 아몬드, 마카다미아넛</t>
         </is>
       </c>
     </row>
@@ -20332,12 +20332,12 @@
       </c>
       <c r="E477" s="25" t="inlineStr">
         <is>
-          <t>올리브오일추출, / 물과 오일분리저지</t>
+          <t>올리브오일추출 · 물과 오일분리저지</t>
         </is>
       </c>
       <c r="F477" s="25" t="inlineStr">
         <is>
-          <t>올리브유화왁스4g / (빠른 유화, 점도를 원할시)</t>
+          <t>올리브유화왁스4g · (빠른 유화, 점도를 원할시)</t>
         </is>
       </c>
     </row>
@@ -20364,7 +20364,7 @@
       </c>
       <c r="E478" s="25" t="inlineStr">
         <is>
-          <t>라벤더에센셜오일 수증기 추출하는 / 과정에서 생기는 부산물</t>
+          <t>라벤더에센셜오일 수증기 추출하는 · 과정에서 생기는 부산물</t>
         </is>
       </c>
       <c r="F478" s="25" t="inlineStr">
@@ -20401,7 +20401,7 @@
       </c>
       <c r="F479" s="25" t="inlineStr">
         <is>
-          <t>로즈플라워겔, / 네롤리플라워겔</t>
+          <t>로즈플라워겔 · 네롤리플라워겔</t>
         </is>
       </c>
     </row>
@@ -20433,7 +20433,7 @@
       </c>
       <c r="F480" s="25" t="inlineStr">
         <is>
-          <t>1,2-헥산디올0.6g / (갈락토미세스 발효여과물의 양을 12.4g로 줄여주세요.)</t>
+          <t>1,2-헥산디올0.6g · (갈락토미세스 발효여과물의 양을 12.4g로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -20527,7 +20527,7 @@
           <t>피부보호막, 보습</t>
         </is>
       </c>
-      <c r="F483" s="25" t="n"/>
+      <c r="F483" s="25" t="inlineStr"/>
     </row>
     <row r="484" ht="32" customHeight="1">
       <c r="A484" s="25" t="inlineStr">
@@ -20778,7 +20778,7 @@
       </c>
       <c r="E495" s="10" t="inlineStr">
         <is>
-          <t>카리테나무열매에서 채취, / 강력 보습</t>
+          <t>카리테나무열매에서 채취 · 강력 보습</t>
         </is>
       </c>
       <c r="F495" s="10" t="inlineStr">
@@ -20810,12 +20810,12 @@
       </c>
       <c r="E496" s="10" t="inlineStr">
         <is>
-          <t>올리브오일에서 유래, / 오일과 물이 분리저지</t>
+          <t>올리브오일에서 유래 · 오일과 물이 분리저지</t>
         </is>
       </c>
       <c r="F496" s="10" t="inlineStr">
         <is>
-          <t>올리브유화왁스4g / (빠른 유화, 점도를 원할시)</t>
+          <t>올리브유화왁스4g · (빠른 유화, 점도를 원할시)</t>
         </is>
       </c>
     </row>
@@ -20842,7 +20842,7 @@
       </c>
       <c r="E497" s="10" t="inlineStr">
         <is>
-          <t>올리브유화왁스 보조, 백탁현상줄이고 / 유화 안정.</t>
+          <t>올리브유화왁스 보조, 백탁현상줄이고 · 유화 안정.</t>
         </is>
       </c>
       <c r="F497" s="10" t="inlineStr">
@@ -20879,7 +20879,7 @@
       </c>
       <c r="F498" s="10" t="inlineStr">
         <is>
-          <t>(프리미엄) / 캐모마일, 로즈워터</t>
+          <t>(프리미엄) · 캐모마일, 로즈워터</t>
         </is>
       </c>
     </row>
@@ -20911,7 +20911,7 @@
       </c>
       <c r="F499" s="10" t="inlineStr">
         <is>
-          <t>히아루론산, / 리피듀어, 식물성글리세린</t>
+          <t>히아루론산 · 리피듀어, 식물성글리세린</t>
         </is>
       </c>
     </row>
@@ -20938,12 +20938,12 @@
       </c>
       <c r="E500" s="10" t="inlineStr">
         <is>
-          <t>특허 등록된 '복합천연방부제' / 폭넓은 항균스펙트럽 효과 / 강력한 항산화 효과 및 보습효과 제공 / 권장량 2%, 민감피부의 경우 최소 1%.</t>
+          <t>특허 등록된 '복합천연방부제' · 폭넓은 항균스펙트럽 효과 · 강력한 항산화 효과 및 보습효과 제공 · 권장량 2%, 민감피부의 경우 최소 1%.</t>
         </is>
       </c>
       <c r="F500" s="10" t="inlineStr">
         <is>
-          <t>수용성보존제, 천연한방보존제로 대체 / (이때 1g씩 넣고 대신 워터양을 80g으로 할 것)</t>
+          <t>수용성보존제, 천연한방보존제로 대체 · (이때 1g씩 넣고 대신 워터양을 80g으로 할 것)</t>
         </is>
       </c>
     </row>
@@ -20975,7 +20975,7 @@
       </c>
       <c r="F501" s="10" t="inlineStr">
         <is>
-          <t>유기농 카밍 5솔루션, / 캐모마일, 카렌듈라 등.</t>
+          <t>유기농 카밍 5솔루션 · 캐모마일, 카렌듈라 등.</t>
         </is>
       </c>
     </row>
@@ -21007,7 +21007,7 @@
       </c>
       <c r="F502" s="10" t="inlineStr">
         <is>
-          <t>스쿠알란, / 보르피린</t>
+          <t>스쿠알란 · 보르피린</t>
         </is>
       </c>
     </row>
@@ -21210,7 +21210,7 @@
       </c>
       <c r="E513" s="25" t="inlineStr">
         <is>
-          <t>모로코에서만 나는 아르간나무열매, / 토코페롤, 폴리페놀, 스쿠알렌 등 / 다량 함유</t>
+          <t>모로코에서만 나는 아르간나무열매 · 토코페롤, 폴리페놀, 스쿠알렌 등 · 다량 함유</t>
         </is>
       </c>
       <c r="F513" s="25" t="inlineStr">
@@ -21247,7 +21247,7 @@
       </c>
       <c r="F514" s="25" t="inlineStr">
         <is>
-          <t>올리브유화왁스4g / (빠른 유화, 점도를 원할시)</t>
+          <t>올리브유화왁스4g · (빠른 유화, 점도를 원할시)</t>
         </is>
       </c>
     </row>
@@ -21311,7 +21311,7 @@
       </c>
       <c r="F516" s="25" t="inlineStr">
         <is>
-          <t>로즈플라워겔, / 네롤리플라워겔</t>
+          <t>로즈플라워겔 · 네롤리플라워겔</t>
         </is>
       </c>
     </row>
@@ -21375,7 +21375,7 @@
       </c>
       <c r="F518" s="25" t="inlineStr">
         <is>
-          <t>1,2-헥산디올2g / (네롤리워터의 양을 54g으로 줄여주세요.)</t>
+          <t>1,2-헥산디올2g · (네롤리워터의 양을 54g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -21629,7 +21629,7 @@
           <t>푸에라리아인퓨즈오일</t>
         </is>
       </c>
-      <c r="F530" s="10" t="n"/>
+      <c r="F530" s="10" t="inlineStr"/>
     </row>
     <row r="531" ht="48" customHeight="1">
       <c r="A531" s="10" t="inlineStr">
@@ -21659,7 +21659,7 @@
       </c>
       <c r="F531" s="10" t="inlineStr">
         <is>
-          <t>올리브유화왁스4g / (빠른 유화, 점도를 원할시)</t>
+          <t>올리브유화왁스4g · (빠른 유화, 점도를 원할시)</t>
         </is>
       </c>
     </row>
@@ -21721,7 +21721,7 @@
           <t>푸에라리아추출물</t>
         </is>
       </c>
-      <c r="F533" s="10" t="n"/>
+      <c r="F533" s="10" t="inlineStr"/>
     </row>
     <row r="534" ht="32" customHeight="1">
       <c r="A534" s="10" t="inlineStr">
@@ -21751,7 +21751,7 @@
       </c>
       <c r="F534" s="10" t="inlineStr">
         <is>
-          <t>(아카시아,마린) / 콜라겐 등</t>
+          <t>(아카시아,마린) · 콜라겐 등</t>
         </is>
       </c>
     </row>
@@ -22055,7 +22055,7 @@
       </c>
       <c r="F548" s="25" t="inlineStr">
         <is>
-          <t>올리브유화왁스4g / (빠른 유화, 점도를 원할시)</t>
+          <t>올리브유화왁스4g · (빠른 유화, 점도를 원할시)</t>
         </is>
       </c>
     </row>
@@ -22119,7 +22119,7 @@
       </c>
       <c r="F550" s="25" t="inlineStr">
         <is>
-          <t>1,2-헥산디올2g / (로즈워터의 양을 86g으로 줄여주세요.)</t>
+          <t>1,2-헥산디올2g · (로즈워터의 양을 86g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -22394,12 +22394,12 @@
       </c>
       <c r="E563" s="10" t="inlineStr">
         <is>
-          <t>아몬드열매에서 채취, / 가벼운 오일</t>
+          <t>아몬드열매에서 채취 · 가벼운 오일</t>
         </is>
       </c>
       <c r="F563" s="10" t="inlineStr">
         <is>
-          <t>골든호호바, / 아보카도 등</t>
+          <t>골든호호바 · 아보카도 등</t>
         </is>
       </c>
     </row>
@@ -22426,7 +22426,7 @@
       </c>
       <c r="E564" s="10" t="inlineStr">
         <is>
-          <t>카리테나무열매에서 추출하는 / 식물성 버터, 고보습</t>
+          <t>카리테나무열매에서 추출하는 · 식물성 버터, 고보습</t>
         </is>
       </c>
       <c r="F564" s="10" t="inlineStr">
@@ -22458,12 +22458,12 @@
       </c>
       <c r="E565" s="10" t="inlineStr">
         <is>
-          <t>오일과 물이 분리되지 않도록 함. / 올리브오일에서 유래.</t>
+          <t>오일과 물이 분리되지 않도록 함. · 올리브오일에서 유래.</t>
         </is>
       </c>
       <c r="F565" s="10" t="inlineStr">
         <is>
-          <t>올리브유화왁스4g / (빠른 유화, 점도를 원할시)</t>
+          <t>올리브유화왁스4g · (빠른 유화, 점도를 원할시)</t>
         </is>
       </c>
     </row>
@@ -22490,12 +22490,12 @@
       </c>
       <c r="E566" s="10" t="inlineStr">
         <is>
-          <t>라벤더를 증기추출, / 라벤더의 수용성성분, 진정</t>
+          <t>라벤더를 증기추출 · 라벤더의 수용성성분, 진정</t>
         </is>
       </c>
       <c r="F566" s="10" t="inlineStr">
         <is>
-          <t>원하는 / 플로랄워터</t>
+          <t>원하는 · 플로랄워터</t>
         </is>
       </c>
     </row>
@@ -22527,7 +22527,7 @@
       </c>
       <c r="F567" s="10" t="inlineStr">
         <is>
-          <t>로즈플라워겔, / 네롤리플라워겔</t>
+          <t>로즈플라워겔 · 네롤리플라워겔</t>
         </is>
       </c>
     </row>
@@ -22554,10 +22554,10 @@
       </c>
       <c r="E568" s="10" t="inlineStr">
         <is>
-          <t>박하뇌, 박하의 알콜성분, / 마취, 혈액순환 등등..</t>
-        </is>
-      </c>
-      <c r="F568" s="10" t="n"/>
+          <t>박하뇌, 박하의 알콜성분 · 마취, 혈액순환 등등..</t>
+        </is>
+      </c>
+      <c r="F568" s="10" t="inlineStr"/>
     </row>
     <row r="569" ht="64" customHeight="1">
       <c r="A569" s="10" t="inlineStr">
@@ -22587,7 +22587,7 @@
       </c>
       <c r="F569" s="10" t="inlineStr">
         <is>
-          <t>1,2-헥산디올2g / (라벤더워터의 양을 69g으로 줄여주세요.)</t>
+          <t>1,2-헥산디올2g · (라벤더워터의 양을 69g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -22646,10 +22646,10 @@
       </c>
       <c r="E571" s="10" t="inlineStr">
         <is>
-          <t>인간의 피부나 모발을 구성하는 아미노산 조성비 와 유사하는 것으로부터 , 피부나 모발에 높은 친화성을 가지고 있습니다. / 실크 파우더는 누에에서는 나오는 실크를 가수 분해하여 고분자로 만든 것입니다.</t>
-        </is>
-      </c>
-      <c r="F571" s="10" t="n"/>
+          <t>인간의 피부나 모발을 구성하는 아미노산 조성비 와 유사하는 것으로부터 , 피부나 모발에 높은 친화성을 가지고 있습니다. · 실크 파우더는 누에에서는 나오는 실크를 가수 분해하여 고분자로 만든 것입니다.</t>
+        </is>
+      </c>
+      <c r="F571" s="10" t="inlineStr"/>
     </row>
     <row r="572" ht="14" customHeight="1">
       <c r="A572" s="20" t="inlineStr">
@@ -22873,7 +22873,7 @@
       </c>
       <c r="F583" s="25" t="inlineStr">
         <is>
-          <t>올리브유화왁스4g / (빠른 유화, 점도를 원할시)</t>
+          <t>올리브유화왁스4g · (빠른 유화, 점도를 원할시)</t>
         </is>
       </c>
     </row>
@@ -22905,7 +22905,7 @@
       </c>
       <c r="F584" s="25" t="inlineStr">
         <is>
-          <t>피부타입별 워터 / 트러블, 남성-편백 / 민감, 베이비-캐모마일 / 노화-로즈 / 남성-로즈마리</t>
+          <t>피부타입별 워터 · 트러블, 남성-편백 · 민감, 베이비-캐모마일 · 노화-로즈 · 남성-로즈마리</t>
         </is>
       </c>
     </row>
@@ -23286,7 +23286,7 @@
       </c>
       <c r="F600" s="10" t="inlineStr">
         <is>
-          <t>올리브유화왁스4g / (빠른 유화, 점도를 원할시)</t>
+          <t>올리브유화왁스4g · (빠른 유화, 점도를 원할시)</t>
         </is>
       </c>
     </row>
@@ -23313,7 +23313,7 @@
       </c>
       <c r="E601" s="10" t="inlineStr">
         <is>
-          <t>장미꽃잎을 수증기증류법으로 추출, / 수용성 장미유효성분함유</t>
+          <t>장미꽃잎을 수증기증류법으로 추출 · 수용성 장미유효성분함유</t>
         </is>
       </c>
       <c r="F601" s="10" t="inlineStr">
@@ -23345,12 +23345,12 @@
       </c>
       <c r="E602" s="10" t="inlineStr">
         <is>
-          <t>자몽씨추출물, 황금 등 한방복합 / 균번식억제</t>
+          <t>자몽씨추출물, 황금 등 한방복합 · 균번식억제</t>
         </is>
       </c>
       <c r="F602" s="10" t="inlineStr">
         <is>
-          <t>1,2-헥산디올0.6g / (갈락토미세스 발효여과물의 양을 12.4g로 줄여주세요.)</t>
+          <t>1,2-헥산디올0.6g · (갈락토미세스 발효여과물의 양을 12.4g로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -23380,7 +23380,7 @@
           <t>피부보호막, 보습유지</t>
         </is>
       </c>
-      <c r="F603" s="10" t="n"/>
+      <c r="F603" s="10" t="inlineStr"/>
     </row>
     <row r="604" ht="112" customHeight="1">
       <c r="A604" s="10" t="inlineStr">
@@ -23692,7 +23692,7 @@
       </c>
       <c r="F617" s="25" t="inlineStr">
         <is>
-          <t>올리브유화왁스4g / (빠른 유화, 점도를 원할시)</t>
+          <t>올리브유화왁스4g · (빠른 유화, 점도를 원할시)</t>
         </is>
       </c>
     </row>
@@ -23719,12 +23719,12 @@
       </c>
       <c r="E618" s="25" t="inlineStr">
         <is>
-          <t>오렌지꽃을 수증기추출법으로 추출, / 수분공급,진정</t>
+          <t>오렌지꽃을 수증기추출법으로 추출 · 수분공급,진정</t>
         </is>
       </c>
       <c r="F618" s="25" t="inlineStr">
         <is>
-          <t>피부타입별 워터 / 트러블, 남성-편백 / 민감, 베이비-캐모마일 / 노화-로즈 / 남성-로즈마리</t>
+          <t>피부타입별 워터 · 트러블, 남성-편백 · 민감, 베이비-캐모마일 · 노화-로즈 · 남성-로즈마리</t>
         </is>
       </c>
     </row>
@@ -23788,7 +23788,7 @@
       </c>
       <c r="F620" s="25" t="inlineStr">
         <is>
-          <t>FGF10/1ppm,아세틸헥사펩타이드, 쿠퍼펩타이드 등</t>
+          <t>FGF10 · 1ppm,아세틸헥사펩타이드, 쿠퍼펩타이드 등</t>
         </is>
       </c>
     </row>
@@ -23820,7 +23820,7 @@
       </c>
       <c r="F621" s="25" t="inlineStr">
         <is>
-          <t>1,2-헥산디올2g / (네롤리워터의 양을 69g으로 줄여주세요.)</t>
+          <t>1,2-헥산디올2g · (네롤리워터의 양을 69g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -23852,7 +23852,7 @@
       </c>
       <c r="F622" s="25" t="inlineStr">
         <is>
-          <t>네롤리에센셜오일 / 2방울</t>
+          <t>네롤리에센셜오일 · 2방울</t>
         </is>
       </c>
     </row>
@@ -24071,12 +24071,12 @@
       </c>
       <c r="E633" s="10" t="inlineStr">
         <is>
-          <t>에코인증, 올리브오일유래. / 물과 오일 분리저지</t>
+          <t>에코인증, 올리브오일유래. · 물과 오일 분리저지</t>
         </is>
       </c>
       <c r="F633" s="10" t="inlineStr">
         <is>
-          <t>올리브유화왁스4g / (빠른 유화, 점도를 원할시)</t>
+          <t>올리브유화왁스4g · (빠른 유화, 점도를 원할시)</t>
         </is>
       </c>
     </row>
@@ -24172,7 +24172,7 @@
       </c>
       <c r="F636" s="10" t="inlineStr">
         <is>
-          <t>1,2-헥산디올2g / (편백워터의 양을 73g으로 줄여주세요.)</t>
+          <t>1,2-헥산디올2g · (편백워터의 양을 73g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -24231,12 +24231,12 @@
       </c>
       <c r="E638" s="10" t="inlineStr">
         <is>
-          <t>USDA Organic 유기농 인증. / 유기농 청호추출물, 카렌듈라꽃추출물, 컴프리잎추출물, 에버라스팅추출물, / 님잎추출물. 허브 5 가지 추출물 / 각종 트러블 증상에 효과적이고 독성이나 자극이 없음. 피부면역력 강화와 피부개선</t>
+          <t>USDA Organic 유기농 인증. · 유기농 청호추출물, 카렌듈라꽃추출물, 컴프리잎추출물, 에버라스팅추출물 · 님잎추출물. 허브 5 가지 추출물 · 각종 트러블 증상에 효과적이고 독성이나 자극이 없음. 피부면역력 강화와 피부개선</t>
         </is>
       </c>
       <c r="F638" s="10" t="inlineStr">
         <is>
-          <t>피부타입에 맞는 / 추출물 대체가능</t>
+          <t>피부타입에 맞는 · 추출물 대체가능</t>
         </is>
       </c>
     </row>
@@ -24461,7 +24461,7 @@
       </c>
       <c r="E650" s="25" t="inlineStr">
         <is>
-          <t>6 IN ONE / 피부결 개선, 보습, 맑은 피부, / 윤기, 영양공급, 피부정화 / 스크럽제를 만들기 위한 / 최적의 베이스</t>
+          <t>6 IN ONE · 피부결 개선, 보습, 맑은 피부 · 윤기, 영양공급, 피부정화 · 스크럽제를 만들기 위한 · 최적의 베이스</t>
         </is>
       </c>
       <c r="F650" s="25" t="inlineStr">
@@ -24494,7 +24494,7 @@
       </c>
       <c r="F651" s="25" t="inlineStr">
         <is>
-          <t>올리브유화왁스4g / (빠른 유화, 점도를 원할시)</t>
+          <t>올리브유화왁스4g · (빠른 유화, 점도를 원할시)</t>
         </is>
       </c>
     </row>
@@ -24517,10 +24517,10 @@
       </c>
       <c r="E652" s="25" t="inlineStr">
         <is>
-          <t>유화보조제, / 코코넛오일에서 얻어짐</t>
-        </is>
-      </c>
-      <c r="F652" s="25" t="n"/>
+          <t>유화보조제 · 코코넛오일에서 얻어짐</t>
+        </is>
+      </c>
+      <c r="F652" s="25" t="inlineStr"/>
     </row>
     <row r="653" ht="96" customHeight="1">
       <c r="A653" s="25" t="inlineStr">
@@ -24541,7 +24541,7 @@
       </c>
       <c r="E653" s="25" t="inlineStr">
         <is>
-          <t>캐모마일 꽃을 수증기증류해 얻음. / 민감한 두피진정 / [주의] 캐모마일을 우린 물이나 한방약재를 우린 물을 넣을 경우 거품용기가 막히는 경우가 자주있습니다.</t>
+          <t>캐모마일 꽃을 수증기증류해 얻음. · 민감한 두피진정 · [주의] 캐모마일을 우린 물이나 한방약재를 우린 물을 넣을 경우 거품용기가 막히는 경우가 자주있습니다.</t>
         </is>
       </c>
       <c r="F653" s="25" t="inlineStr">
@@ -24569,7 +24569,7 @@
       </c>
       <c r="E654" s="25" t="inlineStr">
         <is>
-          <t>거제산 생알로에잎을 껍질제거한 후 갈아만듬. / 남은 재료 활용 팁 : 젤타입스킨으로 사용가능, / 헤어에센스로 사용가능.</t>
+          <t>거제산 생알로에잎을 껍질제거한 후 갈아만듬. · 남은 재료 활용 팁 : 젤타입스킨으로 사용가능 · 헤어에센스로 사용가능.</t>
         </is>
       </c>
       <c r="F654" s="25" t="inlineStr">
@@ -24597,7 +24597,7 @@
       </c>
       <c r="E655" s="25" t="inlineStr">
         <is>
-          <t>피부에 자연적으로 존재하는 성분, / 피부결 개선, 보습 / 장벽 강화, 우수한 흡수력</t>
+          <t>피부에 자연적으로 존재하는 성분 · 피부결 개선, 보습 · 장벽 강화, 우수한 흡수력</t>
         </is>
       </c>
       <c r="F655" s="25" t="inlineStr">
@@ -24625,7 +24625,7 @@
       </c>
       <c r="E656" s="25" t="inlineStr">
         <is>
-          <t>보습, 피부타입에따라 줄이거나 늘려서 첨가 / ※3g이상 들어가면 스프레이보다는 펌핑용기에 담아사용하세요.</t>
+          <t>보습, 피부타입에따라 줄이거나 늘려서 첨가 · ※3g이상 들어가면 스프레이보다는 펌핑용기에 담아사용하세요.</t>
         </is>
       </c>
       <c r="F656" s="25" t="inlineStr">
@@ -24653,12 +24653,12 @@
       </c>
       <c r="E657" s="25" t="inlineStr">
         <is>
-          <t>천연한방보존제는 생약 중 항균력이 우수한 오배자, 가자, 석곡, 산초를 초음파 방식으로 / 추출하여 조합한 화장품용 천연유래 항균제입니다</t>
+          <t>천연한방보존제는 생약 중 항균력이 우수한 오배자, 가자, 석곡, 산초를 초음파 방식으로 · 추출하여 조합한 화장품용 천연유래 항균제입니다</t>
         </is>
       </c>
       <c r="F657" s="25" t="inlineStr">
         <is>
-          <t>1,2-헥산디올0.6g / (갈락토미세스 발효여과물의 양을 12.4g로 줄여주세요.)</t>
+          <t>1,2-헥산디올0.6g · (갈락토미세스 발효여과물의 양을 12.4g로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -24681,7 +24681,7 @@
       </c>
       <c r="E658" s="25" t="inlineStr">
         <is>
-          <t>귤껍질오일, / 임신기간 영아에게 안전하게 사용, / 모든 피부사용</t>
+          <t>귤껍질오일 · 임신기간 영아에게 안전하게 사용 · 모든 피부사용</t>
         </is>
       </c>
       <c r="F658" s="25" t="inlineStr">
@@ -24714,7 +24714,7 @@
       </c>
       <c r="F659" s="25" t="inlineStr">
         <is>
-          <t>네롤리,카모마일저먼 / (:일때 양을줄임-2방울), / 로먼카모마일 등</t>
+          <t>네롤리,카모마일저먼 · (:일때 양을줄임-2방울) · 로먼카모마일 등</t>
         </is>
       </c>
     </row>
@@ -24841,12 +24841,12 @@
       </c>
       <c r="E667" s="10" t="inlineStr">
         <is>
-          <t>사람피지구조, / 가볍고 끈적임이 없음</t>
+          <t>사람피지구조 · 가볍고 끈적임이 없음</t>
         </is>
       </c>
       <c r="F667" s="10" t="inlineStr">
         <is>
-          <t>아르간오일, / 모링가오일 등</t>
+          <t>아르간오일 · 모링가오일 등</t>
         </is>
       </c>
     </row>
@@ -24873,12 +24873,12 @@
       </c>
       <c r="E668" s="10" t="inlineStr">
         <is>
-          <t>물과 오일 분리 저지, / 유화제</t>
+          <t>물과 오일 분리 저지 · 유화제</t>
         </is>
       </c>
       <c r="F668" s="10" t="inlineStr">
         <is>
-          <t>올리브유화왁스4g / (빠른 유화, 점도를 원할시)</t>
+          <t>올리브유화왁스4g · (빠른 유화, 점도를 원할시)</t>
         </is>
       </c>
     </row>
@@ -24908,7 +24908,7 @@
           <t>보조유화제</t>
         </is>
       </c>
-      <c r="F669" s="10" t="n"/>
+      <c r="F669" s="10" t="inlineStr"/>
     </row>
     <row r="670" ht="16" customHeight="1">
       <c r="A670" s="10" t="inlineStr">
@@ -24933,7 +24933,7 @@
       </c>
       <c r="E670" s="10" t="inlineStr">
         <is>
-          <t>허브의 여왕, / 수증기증류추출</t>
+          <t>허브의 여왕 · 수증기증류추출</t>
         </is>
       </c>
       <c r="F670" s="10" t="inlineStr">
@@ -25002,7 +25002,7 @@
       </c>
       <c r="F672" s="10" t="inlineStr">
         <is>
-          <t>글리세린, / 낫또모이스트</t>
+          <t>글리세린 · 낫또모이스트</t>
         </is>
       </c>
     </row>
@@ -25029,7 +25029,7 @@
       </c>
       <c r="E673" s="10" t="inlineStr">
         <is>
-          <t>균번식 억제제, / 황금, 자몽씨추출물 등</t>
+          <t>균번식 억제제 · 황금, 자몽씨추출물 등</t>
         </is>
       </c>
       <c r="F673" s="10" t="inlineStr">
@@ -25066,7 +25066,7 @@
       </c>
       <c r="F674" s="10" t="inlineStr">
         <is>
-          <t>스쿠알란, / 보르피린</t>
+          <t>스쿠알란 · 보르피린</t>
         </is>
       </c>
     </row>
@@ -25093,12 +25093,12 @@
       </c>
       <c r="E675" s="10" t="inlineStr">
         <is>
-          <t>저온 감압, 성분 파괴 최소. / 폴리페놀 풍부</t>
+          <t>저온 감압, 성분 파괴 최소. · 폴리페놀 풍부</t>
         </is>
       </c>
       <c r="F675" s="10" t="inlineStr">
         <is>
-          <t>녹소초 추출물, / 유기농 브라이트닝 5 등.</t>
+          <t>녹소초 추출물 · 유기농 브라이트닝 5 등.</t>
         </is>
       </c>
     </row>
@@ -25125,12 +25125,12 @@
       </c>
       <c r="E676" s="10" t="inlineStr">
         <is>
-          <t>오렌지꽃 에센셜오일, / 노화피부관리</t>
+          <t>오렌지꽃 에센셜오일 · 노화피부관리</t>
         </is>
       </c>
       <c r="F676" s="10" t="inlineStr">
         <is>
-          <t>원하는 / 에센셜오일</t>
+          <t>원하는 · 에센셜오일</t>
         </is>
       </c>
     </row>
@@ -25272,12 +25272,12 @@
       </c>
       <c r="E685" s="25" t="inlineStr">
         <is>
-          <t>사람피지구조, / 가볍고 끈적임이 없음</t>
+          <t>사람피지구조 · 가볍고 끈적임이 없음</t>
         </is>
       </c>
       <c r="F685" s="25" t="inlineStr">
         <is>
-          <t>아르간오일, / 동백오일 등</t>
+          <t>아르간오일 · 동백오일 등</t>
         </is>
       </c>
     </row>
@@ -25304,12 +25304,12 @@
       </c>
       <c r="E686" s="25" t="inlineStr">
         <is>
-          <t>물과 오일 분리 저지, / 유화제</t>
+          <t>물과 오일 분리 저지 · 유화제</t>
         </is>
       </c>
       <c r="F686" s="25" t="inlineStr">
         <is>
-          <t>올리브유화왁스4g / (빠른 유화, 점도를 원할시)</t>
+          <t>올리브유화왁스4g · (빠른 유화, 점도를 원할시)</t>
         </is>
       </c>
     </row>
@@ -25339,7 +25339,7 @@
           <t>보조유화제</t>
         </is>
       </c>
-      <c r="F687" s="25" t="n"/>
+      <c r="F687" s="25" t="inlineStr"/>
     </row>
     <row r="688" ht="16" customHeight="1">
       <c r="A688" s="25" t="inlineStr">
@@ -25364,7 +25364,7 @@
       </c>
       <c r="E688" s="25" t="inlineStr">
         <is>
-          <t>허브의 여왕, / 수증기증류추출</t>
+          <t>허브의 여왕 · 수증기증류추출</t>
         </is>
       </c>
       <c r="F688" s="25" t="inlineStr">
@@ -25401,7 +25401,7 @@
       </c>
       <c r="F689" s="25" t="inlineStr">
         <is>
-          <t>스쿠알란, / 보르피린</t>
+          <t>스쿠알란 · 보르피린</t>
         </is>
       </c>
     </row>
@@ -25428,7 +25428,7 @@
       </c>
       <c r="E690" s="25" t="inlineStr">
         <is>
-          <t>균번식 억제제, / 황금, 자몽씨추출물 등</t>
+          <t>균번식 억제제 · 황금, 자몽씨추출물 등</t>
         </is>
       </c>
       <c r="F690" s="25" t="inlineStr">
@@ -25465,7 +25465,7 @@
       </c>
       <c r="F691" s="25" t="inlineStr">
         <is>
-          <t>에코보습제, / 낫또모이스트 등 / 촉촉함을 원한다면 히아루론산을 더 / 추가해주세요.</t>
+          <t>에코보습제 · 낫또모이스트 등 · 촉촉함을 원한다면 히아루론산을 더 · 추가해주세요.</t>
         </is>
       </c>
     </row>
@@ -25497,7 +25497,7 @@
       </c>
       <c r="F692" s="25" t="inlineStr">
         <is>
-          <t>원하는 / 에센셜오일</t>
+          <t>원하는 · 에센셜오일</t>
         </is>
       </c>
     </row>
@@ -25608,7 +25608,7 @@
       </c>
       <c r="E699" s="10" t="inlineStr">
         <is>
-          <t>롤볼 기준 높이 5.5cm까지 골든 호호바오일을 넣어주시면 8.6g(=10ml) / 골든 호호바오일,사람피지성분과 비슷, 끈적임없이 흡수, 액상왁스, 비타민E함유.</t>
+          <t>롤볼 기준 높이 5.5cm까지 골든 호호바오일을 넣어주시면 8.6g(=10ml) · 골든 호호바오일,사람피지성분과 비슷, 끈적임없이 흡수, 액상왁스, 비타민E함유.</t>
         </is>
       </c>
       <c r="F699" s="10" t="inlineStr">
@@ -25641,7 +25641,7 @@
       </c>
       <c r="F700" s="10" t="inlineStr">
         <is>
-          <t>올리브유화왁스4g / (빠른 유화, 점도를 원할시)</t>
+          <t>올리브유화왁스4g · (빠른 유화, 점도를 원할시)</t>
         </is>
       </c>
     </row>
@@ -25695,7 +25695,7 @@
           <t>식물 유래 셀룰로오스, 점증·각질 케어</t>
         </is>
       </c>
-      <c r="F702" s="10" t="n"/>
+      <c r="F702" s="10" t="inlineStr"/>
     </row>
     <row r="703" ht="64" customHeight="1">
       <c r="A703" s="10" t="inlineStr">
@@ -25716,7 +25716,7 @@
       </c>
       <c r="E703" s="10" t="inlineStr">
         <is>
-          <t>보습, 피부타입에따라 줄이거나 늘려서 첨가 / ※3g이상 들어가면 스프레이보다는 펌핑용기에 담아사용하세요.</t>
+          <t>보습, 피부타입에따라 줄이거나 늘려서 첨가 · ※3g이상 들어가면 스프레이보다는 펌핑용기에 담아사용하세요.</t>
         </is>
       </c>
       <c r="F703" s="10" t="inlineStr">
@@ -25777,7 +25777,7 @@
       </c>
       <c r="F705" s="10" t="inlineStr">
         <is>
-          <t>네롤리,카모마일저먼 / (:일때 양을줄임-2방울), / 로먼카모마일 등</t>
+          <t>네롤리,카모마일저먼 · (:일때 양을줄임-2방울) · 로먼카모마일 등</t>
         </is>
       </c>
     </row>
@@ -25901,12 +25901,12 @@
       </c>
       <c r="E712" s="25" t="inlineStr">
         <is>
-          <t>올레인산 풍부 고보습, / 청정 섬 국내 제주산 야생동백씨 압착.</t>
+          <t>올레인산 풍부 고보습 · 청정 섬 국내 제주산 야생동백씨 압착.</t>
         </is>
       </c>
       <c r="F712" s="25" t="inlineStr">
         <is>
-          <t>아르간, 로즈힙, / 마카다미아넛오일 등 / 추천</t>
+          <t>아르간, 로즈힙 · 마카다미아넛오일 등 · 추천</t>
         </is>
       </c>
     </row>
@@ -25933,12 +25933,12 @@
       </c>
       <c r="E713" s="25" t="inlineStr">
         <is>
-          <t>에코인증. / 오일과 물이 분리되지 않도록 도와줌.</t>
+          <t>에코인증. · 오일과 물이 분리되지 않도록 도와줌.</t>
         </is>
       </c>
       <c r="F713" s="25" t="inlineStr">
         <is>
-          <t>올리브유화왁스4g / (빠른 유화, 점도를 원할시)</t>
+          <t>올리브유화왁스4g · (빠른 유화, 점도를 원할시)</t>
         </is>
       </c>
     </row>
@@ -26034,7 +26034,7 @@
       </c>
       <c r="F716" s="25" t="inlineStr">
         <is>
-          <t>로즈플라워겔, / 네롤리플라워겔</t>
+          <t>로즈플라워겔 · 네롤리플라워겔</t>
         </is>
       </c>
     </row>
@@ -26066,7 +26066,7 @@
       </c>
       <c r="F717" s="25" t="inlineStr">
         <is>
-          <t>콜라겐, 석류,토마토,</t>
+          <t>콜라겐, 석류,토마토</t>
         </is>
       </c>
     </row>
@@ -26093,10 +26093,10 @@
       </c>
       <c r="E718" s="25" t="inlineStr">
         <is>
-          <t>독사에게 물리면 피부,근육이 마비되는 점을 착안해 만든 단백질. 독사의 독을 모방하여 만든 펩타이드. 2~4% 사용. / 임상시 아세틸헥사펩타이드보다 효과적. / 2006년 스위스 테크놀로지 어워드 바이오부분 수상, 유럽특허를 획득. / '바르는 보톡스' 등으로 인기</t>
-        </is>
-      </c>
-      <c r="F718" s="25" t="n"/>
+          <t>독사에게 물리면 피부,근육이 마비되는 점을 착안해 만든 단백질. 독사의 독을 모방하여 만든 펩타이드. 2~4% 사용. · 임상시 아세틸헥사펩타이드보다 효과적. · 2006년 스위스 테크놀로지 어워드 바이오부분 수상, 유럽특허를 획득. · '바르는 보톡스' 등으로 인기</t>
+        </is>
+      </c>
+      <c r="F718" s="25" t="inlineStr"/>
     </row>
     <row r="719" ht="48" customHeight="1">
       <c r="A719" s="25" t="inlineStr">
@@ -26217,7 +26217,7 @@
       </c>
       <c r="E722" s="25" t="inlineStr">
         <is>
-          <t>아로마테라피, / 장미향이 나는 제라늄, 모든 피부</t>
+          <t>아로마테라피 · 장미향이 나는 제라늄, 모든 피부</t>
         </is>
       </c>
       <c r="F722" s="25" t="inlineStr">
@@ -26406,7 +26406,7 @@
       </c>
       <c r="E732" s="10" t="inlineStr">
         <is>
-          <t>피부에 자연적으로 존재하는 성분, / 피부결 개선, 보습 / 장벽 강화, 우수한 흡수력</t>
+          <t>피부에 자연적으로 존재하는 성분 · 피부결 개선, 보습 · 장벽 강화, 우수한 흡수력</t>
         </is>
       </c>
       <c r="F732" s="10" t="inlineStr">
@@ -26443,7 +26443,7 @@
       </c>
       <c r="F733" s="10" t="inlineStr">
         <is>
-          <t>올리브유화왁스4g / (빠른 유화, 점도를 원할시)</t>
+          <t>올리브유화왁스4g · (빠른 유화, 점도를 원할시)</t>
         </is>
       </c>
     </row>
@@ -26598,7 +26598,7 @@
       </c>
       <c r="E738" s="10" t="inlineStr">
         <is>
-          <t>천연 다당류 / (귀리, 효모, 버섯류, 해조류) / 피부 보습, 보호막 형성</t>
+          <t>천연 다당류 · (귀리, 효모, 버섯류, 해조류) · 피부 보습, 보호막 형성</t>
         </is>
       </c>
       <c r="F738" s="10" t="inlineStr">
@@ -26630,12 +26630,12 @@
       </c>
       <c r="E739" s="10" t="inlineStr">
         <is>
-          <t>피부 장벽 강화, / 5종 세라마이드</t>
+          <t>피부 장벽 강화 · 5종 세라마이드</t>
         </is>
       </c>
       <c r="F739" s="10" t="inlineStr">
         <is>
-          <t>스쿠알란, / 보르피린</t>
+          <t>스쿠알란 · 보르피린</t>
         </is>
       </c>
     </row>
@@ -26667,7 +26667,7 @@
       </c>
       <c r="F740" s="10" t="inlineStr">
         <is>
-          <t>천연한방보존제1g / (네롤리워터의 양을 59g으로 늘려주세요.)</t>
+          <t>천연한방보존제1g · (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
@@ -26850,7 +26850,7 @@
           <t>물과 오일 분리 저지, 유화제</t>
         </is>
       </c>
-      <c r="F750" s="25" t="n"/>
+      <c r="F750" s="25" t="inlineStr"/>
     </row>
     <row r="751" ht="48" customHeight="1">
       <c r="A751" s="25" t="inlineStr">
@@ -27070,7 +27070,7 @@
           <t>미백 효과, 항산화 효과</t>
         </is>
       </c>
-      <c r="F757" s="25" t="n"/>
+      <c r="F757" s="25" t="inlineStr"/>
     </row>
     <row r="758" ht="64" customHeight="1">
       <c r="A758" s="25" t="inlineStr">
@@ -27100,7 +27100,7 @@
       </c>
       <c r="F758" s="25" t="inlineStr">
         <is>
-          <t>천연한방보존제1g / (네롤리워터의 양을 59g으로 늘려주세요.)</t>
+          <t>천연한방보존제1g · (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
@@ -27280,7 +27280,7 @@
       </c>
       <c r="E768" s="10" t="inlineStr">
         <is>
-          <t>피부에 자연적으로 존재하는 성분, / 피부결 개선, 보습 / 장벽 강화, 우수한 흡수력</t>
+          <t>피부에 자연적으로 존재하는 성분 · 피부결 개선, 보습 · 장벽 강화, 우수한 흡수력</t>
         </is>
       </c>
       <c r="F768" s="10" t="inlineStr">
@@ -27312,12 +27312,12 @@
       </c>
       <c r="E769" s="10" t="inlineStr">
         <is>
-          <t>코코넛, 팜 등에서 유래, / 카프릴릭산(C8)와 카프릭산(C10)을 / 글리세린과 합성시켜 만든 원료, / 가볍고 빠른 흡수력</t>
+          <t>코코넛, 팜 등에서 유래 · 카프릴릭산(C8)와 카프릭산(C10)을 · 글리세린과 합성시켜 만든 원료 · 가볍고 빠른 흡수력</t>
         </is>
       </c>
       <c r="F769" s="10" t="inlineStr">
         <is>
-          <t>유기농 세티올 / 에스터오일</t>
+          <t>유기농 세티올 · 에스터오일</t>
         </is>
       </c>
     </row>
@@ -27347,7 +27347,7 @@
           <t>유화 보조</t>
         </is>
       </c>
-      <c r="F770" s="10" t="n"/>
+      <c r="F770" s="10" t="inlineStr"/>
     </row>
     <row r="771" ht="48" customHeight="1">
       <c r="A771" s="10" t="inlineStr">
@@ -27377,7 +27377,7 @@
       </c>
       <c r="F771" s="10" t="inlineStr">
         <is>
-          <t>올리브유화왁스4g / (빠른 유화, 점도를 원할시)</t>
+          <t>올리브유화왁스4g · (빠른 유화, 점도를 원할시)</t>
         </is>
       </c>
     </row>
@@ -27473,7 +27473,7 @@
       </c>
       <c r="F774" s="10" t="inlineStr">
         <is>
-          <t>로즈플라워겔, / 알로에베라겔</t>
+          <t>로즈플라워겔 · 알로에베라겔</t>
         </is>
       </c>
     </row>
@@ -27505,7 +27505,7 @@
       </c>
       <c r="F775" s="10" t="inlineStr">
         <is>
-          <t>스쿠알란, / 보르피린</t>
+          <t>스쿠알란 · 보르피린</t>
         </is>
       </c>
     </row>
@@ -27532,10 +27532,10 @@
       </c>
       <c r="E776" s="10" t="inlineStr">
         <is>
-          <t>맑고 밝은 피부 도움 / (비타민나무 열매, 유자, 오미자 복합)</t>
-        </is>
-      </c>
-      <c r="F776" s="10" t="n"/>
+          <t>맑고 밝은 피부 도움 · (비타민나무 열매, 유자, 오미자 복합)</t>
+        </is>
+      </c>
+      <c r="F776" s="10" t="inlineStr"/>
     </row>
     <row r="777" ht="48" customHeight="1">
       <c r="A777" s="10" t="inlineStr">
@@ -27560,10 +27560,10 @@
       </c>
       <c r="E777" s="10" t="inlineStr">
         <is>
-          <t>비타민C의 장점은 살리고 단점은 보완, / 식약처 미백 고시 원료, 미백, 탄력</t>
-        </is>
-      </c>
-      <c r="F777" s="10" t="n"/>
+          <t>비타민C의 장점은 살리고 단점은 보완 · 식약처 미백 고시 원료, 미백, 탄력</t>
+        </is>
+      </c>
+      <c r="F777" s="10" t="inlineStr"/>
     </row>
     <row r="778" ht="32" customHeight="1">
       <c r="A778" s="10" t="inlineStr">
@@ -27588,10 +27588,10 @@
       </c>
       <c r="E778" s="10" t="inlineStr">
         <is>
-          <t>미백 효과 / 강력한 항산화 효과</t>
-        </is>
-      </c>
-      <c r="F778" s="10" t="n"/>
+          <t>미백 효과 · 강력한 항산화 효과</t>
+        </is>
+      </c>
+      <c r="F778" s="10" t="inlineStr"/>
     </row>
     <row r="779" ht="64" customHeight="1">
       <c r="A779" s="10" t="inlineStr">
@@ -27621,7 +27621,7 @@
       </c>
       <c r="F779" s="10" t="inlineStr">
         <is>
-          <t>천연한방보존제1g / (네롤리워터의 양을 59g으로 늘려주세요.)</t>
+          <t>천연한방보존제1g · (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
